--- a/Gantt Chart - Software Design.xlsx
+++ b/Gantt Chart - Software Design.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\compu\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\justi\AppData\Local\Temp\MicrosoftEdgeDownloads\036c8592-3e1f-4e00-8c00-3f1c17c1c1a9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA209E30-8780-4F51-B1EA-137748C66251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41F1F5F5-E4E7-45B5-8A1C-7BB25F1484A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MRS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="201">
   <si>
     <t>DEPARTMENT</t>
   </si>
@@ -416,9 +416,6 @@
   </si>
   <si>
     <t>On Going</t>
-  </si>
-  <si>
-    <t>02/28/2026</t>
   </si>
   <si>
     <t>2/01</t>
@@ -1171,6 +1168,14 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1197,14 +1202,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1490,109 +1487,109 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:EB1003"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" customWidth="1"/>
+    <col min="2" max="2" width="9.5546875" customWidth="1"/>
     <col min="3" max="3" width="49" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" customWidth="1"/>
-    <col min="5" max="6" width="13.7109375" customWidth="1"/>
-    <col min="7" max="12" width="7.140625" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" customWidth="1"/>
+    <col min="5" max="6" width="13.6640625" customWidth="1"/>
+    <col min="7" max="12" width="7.109375" customWidth="1"/>
     <col min="13" max="13" width="7" customWidth="1"/>
-    <col min="14" max="19" width="7.140625" customWidth="1"/>
-    <col min="20" max="20" width="7.28515625" customWidth="1"/>
-    <col min="21" max="22" width="6.85546875" customWidth="1"/>
+    <col min="14" max="19" width="7.109375" customWidth="1"/>
+    <col min="20" max="20" width="7.33203125" customWidth="1"/>
+    <col min="21" max="22" width="6.88671875" customWidth="1"/>
     <col min="23" max="23" width="7" customWidth="1"/>
-    <col min="24" max="24" width="7.28515625" customWidth="1"/>
+    <col min="24" max="24" width="7.33203125" customWidth="1"/>
     <col min="25" max="25" width="7" customWidth="1"/>
-    <col min="26" max="26" width="7.140625" customWidth="1"/>
-    <col min="27" max="27" width="6.5703125" customWidth="1"/>
-    <col min="28" max="28" width="6.7109375" customWidth="1"/>
-    <col min="29" max="29" width="7.28515625" customWidth="1"/>
-    <col min="30" max="30" width="6.85546875" customWidth="1"/>
-    <col min="31" max="32" width="7.140625" customWidth="1"/>
+    <col min="26" max="26" width="7.109375" customWidth="1"/>
+    <col min="27" max="27" width="6.5546875" customWidth="1"/>
+    <col min="28" max="28" width="6.6640625" customWidth="1"/>
+    <col min="29" max="29" width="7.33203125" customWidth="1"/>
+    <col min="30" max="30" width="6.88671875" customWidth="1"/>
+    <col min="31" max="32" width="7.109375" customWidth="1"/>
     <col min="33" max="33" width="7" customWidth="1"/>
-    <col min="34" max="34" width="7.85546875" customWidth="1"/>
-    <col min="35" max="35" width="6.7109375" customWidth="1"/>
-    <col min="36" max="41" width="4.7109375" customWidth="1"/>
-    <col min="42" max="42" width="5.140625" customWidth="1"/>
-    <col min="43" max="43" width="4.85546875" customWidth="1"/>
-    <col min="44" max="44" width="5.28515625" customWidth="1"/>
-    <col min="45" max="45" width="4.5703125" customWidth="1"/>
-    <col min="46" max="48" width="5.140625" customWidth="1"/>
-    <col min="49" max="49" width="4.42578125" customWidth="1"/>
-    <col min="50" max="50" width="4.85546875" customWidth="1"/>
-    <col min="51" max="52" width="4.42578125" customWidth="1"/>
-    <col min="53" max="53" width="4.140625" customWidth="1"/>
+    <col min="34" max="34" width="7.88671875" customWidth="1"/>
+    <col min="35" max="35" width="6.6640625" customWidth="1"/>
+    <col min="36" max="41" width="4.6640625" customWidth="1"/>
+    <col min="42" max="42" width="5.109375" customWidth="1"/>
+    <col min="43" max="43" width="4.88671875" customWidth="1"/>
+    <col min="44" max="44" width="5.33203125" customWidth="1"/>
+    <col min="45" max="45" width="4.5546875" customWidth="1"/>
+    <col min="46" max="48" width="5.109375" customWidth="1"/>
+    <col min="49" max="49" width="4.44140625" customWidth="1"/>
+    <col min="50" max="50" width="4.88671875" customWidth="1"/>
+    <col min="51" max="52" width="4.44140625" customWidth="1"/>
+    <col min="53" max="53" width="4.109375" customWidth="1"/>
     <col min="54" max="54" width="5" customWidth="1"/>
-    <col min="55" max="55" width="4.28515625" customWidth="1"/>
-    <col min="56" max="56" width="4.85546875" customWidth="1"/>
-    <col min="57" max="57" width="5.28515625" customWidth="1"/>
-    <col min="58" max="58" width="4.85546875" customWidth="1"/>
+    <col min="55" max="55" width="4.33203125" customWidth="1"/>
+    <col min="56" max="56" width="4.88671875" customWidth="1"/>
+    <col min="57" max="57" width="5.33203125" customWidth="1"/>
+    <col min="58" max="58" width="4.88671875" customWidth="1"/>
     <col min="59" max="59" width="5" customWidth="1"/>
-    <col min="60" max="61" width="4.85546875" customWidth="1"/>
-    <col min="62" max="62" width="5.7109375" customWidth="1"/>
+    <col min="60" max="61" width="4.88671875" customWidth="1"/>
+    <col min="62" max="62" width="5.6640625" customWidth="1"/>
     <col min="63" max="63" width="5" customWidth="1"/>
-    <col min="64" max="64" width="4.7109375" customWidth="1"/>
-    <col min="65" max="65" width="4.5703125" customWidth="1"/>
-    <col min="66" max="66" width="4.7109375" customWidth="1"/>
-    <col min="67" max="67" width="4.42578125" customWidth="1"/>
-    <col min="68" max="69" width="4.7109375" customWidth="1"/>
-    <col min="70" max="70" width="5.7109375" customWidth="1"/>
-    <col min="71" max="72" width="5.5703125" customWidth="1"/>
-    <col min="73" max="73" width="4.42578125" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="5.42578125" customWidth="1"/>
-    <col min="75" max="76" width="4.85546875" customWidth="1"/>
-    <col min="77" max="77" width="5.28515625" customWidth="1"/>
-    <col min="78" max="78" width="4.42578125" customWidth="1"/>
-    <col min="79" max="80" width="5.28515625" customWidth="1"/>
-    <col min="81" max="81" width="4.85546875" customWidth="1"/>
+    <col min="64" max="64" width="4.6640625" customWidth="1"/>
+    <col min="65" max="65" width="4.5546875" customWidth="1"/>
+    <col min="66" max="66" width="4.6640625" customWidth="1"/>
+    <col min="67" max="67" width="4.44140625" customWidth="1"/>
+    <col min="68" max="69" width="4.6640625" customWidth="1"/>
+    <col min="70" max="70" width="5.6640625" customWidth="1"/>
+    <col min="71" max="72" width="5.5546875" customWidth="1"/>
+    <col min="73" max="73" width="4.44140625" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="5.44140625" customWidth="1"/>
+    <col min="75" max="76" width="4.88671875" customWidth="1"/>
+    <col min="77" max="77" width="5.33203125" customWidth="1"/>
+    <col min="78" max="78" width="4.44140625" customWidth="1"/>
+    <col min="79" max="80" width="5.33203125" customWidth="1"/>
+    <col min="81" max="81" width="4.88671875" customWidth="1"/>
     <col min="82" max="82" width="5" customWidth="1"/>
-    <col min="83" max="83" width="5.42578125" customWidth="1"/>
-    <col min="84" max="84" width="4.85546875" customWidth="1"/>
-    <col min="85" max="85" width="5.140625" customWidth="1"/>
-    <col min="86" max="86" width="5.42578125" customWidth="1"/>
-    <col min="87" max="87" width="4.85546875" customWidth="1"/>
-    <col min="88" max="88" width="5.85546875" customWidth="1"/>
-    <col min="89" max="89" width="4.42578125" customWidth="1"/>
+    <col min="83" max="83" width="5.44140625" customWidth="1"/>
+    <col min="84" max="84" width="4.88671875" customWidth="1"/>
+    <col min="85" max="85" width="5.109375" customWidth="1"/>
+    <col min="86" max="86" width="5.44140625" customWidth="1"/>
+    <col min="87" max="87" width="4.88671875" customWidth="1"/>
+    <col min="88" max="88" width="5.88671875" customWidth="1"/>
+    <col min="89" max="89" width="4.44140625" customWidth="1"/>
     <col min="90" max="90" width="5" customWidth="1"/>
-    <col min="91" max="91" width="6.85546875" customWidth="1"/>
+    <col min="91" max="91" width="6.88671875" customWidth="1"/>
     <col min="92" max="92" width="6" customWidth="1"/>
-    <col min="93" max="94" width="5.7109375" customWidth="1"/>
-    <col min="95" max="95" width="5.85546875" customWidth="1"/>
-    <col min="96" max="96" width="6.7109375" customWidth="1"/>
-    <col min="97" max="97" width="5.140625" customWidth="1"/>
-    <col min="98" max="98" width="6.42578125" customWidth="1"/>
+    <col min="93" max="94" width="5.6640625" customWidth="1"/>
+    <col min="95" max="95" width="5.88671875" customWidth="1"/>
+    <col min="96" max="96" width="6.6640625" customWidth="1"/>
+    <col min="97" max="97" width="5.109375" customWidth="1"/>
+    <col min="98" max="98" width="6.44140625" customWidth="1"/>
     <col min="99" max="99" width="5" customWidth="1"/>
-    <col min="100" max="101" width="5.140625" customWidth="1"/>
-    <col min="102" max="102" width="5.28515625" customWidth="1"/>
-    <col min="103" max="103" width="5.5703125" customWidth="1"/>
-    <col min="104" max="104" width="5.28515625" customWidth="1"/>
-    <col min="105" max="105" width="7.5703125" customWidth="1"/>
+    <col min="100" max="101" width="5.109375" customWidth="1"/>
+    <col min="102" max="102" width="5.33203125" customWidth="1"/>
+    <col min="103" max="103" width="5.5546875" customWidth="1"/>
+    <col min="104" max="104" width="5.33203125" customWidth="1"/>
+    <col min="105" max="105" width="7.5546875" customWidth="1"/>
     <col min="106" max="107" width="6" customWidth="1"/>
-    <col min="108" max="108" width="5.5703125" customWidth="1"/>
-    <col min="109" max="109" width="5.7109375" customWidth="1"/>
-    <col min="110" max="112" width="5.85546875" customWidth="1"/>
-    <col min="113" max="113" width="6.42578125" customWidth="1"/>
-    <col min="114" max="114" width="5.85546875" customWidth="1"/>
+    <col min="108" max="108" width="5.5546875" customWidth="1"/>
+    <col min="109" max="109" width="5.6640625" customWidth="1"/>
+    <col min="110" max="112" width="5.88671875" customWidth="1"/>
+    <col min="113" max="113" width="6.44140625" customWidth="1"/>
+    <col min="114" max="114" width="5.88671875" customWidth="1"/>
     <col min="115" max="115" width="6" customWidth="1"/>
-    <col min="116" max="116" width="6.5703125" customWidth="1"/>
-    <col min="117" max="117" width="5.85546875" customWidth="1"/>
-    <col min="118" max="118" width="5.28515625" customWidth="1"/>
-    <col min="119" max="121" width="5.85546875" customWidth="1"/>
-    <col min="122" max="122" width="5.7109375" customWidth="1"/>
-    <col min="123" max="123" width="6.7109375" customWidth="1"/>
-    <col min="124" max="125" width="5.140625" customWidth="1"/>
-    <col min="126" max="126" width="5.7109375" customWidth="1"/>
-    <col min="127" max="127" width="4.85546875" customWidth="1"/>
-    <col min="128" max="128" width="5.85546875" customWidth="1"/>
-    <col min="129" max="129" width="5.5703125" customWidth="1"/>
-    <col min="130" max="130" width="5.140625" customWidth="1"/>
+    <col min="116" max="116" width="6.5546875" customWidth="1"/>
+    <col min="117" max="117" width="5.88671875" customWidth="1"/>
+    <col min="118" max="118" width="5.33203125" customWidth="1"/>
+    <col min="119" max="121" width="5.88671875" customWidth="1"/>
+    <col min="122" max="122" width="5.6640625" customWidth="1"/>
+    <col min="123" max="123" width="6.6640625" customWidth="1"/>
+    <col min="124" max="125" width="5.109375" customWidth="1"/>
+    <col min="126" max="126" width="5.6640625" customWidth="1"/>
+    <col min="127" max="127" width="4.88671875" customWidth="1"/>
+    <col min="128" max="128" width="5.88671875" customWidth="1"/>
+    <col min="129" max="129" width="5.5546875" customWidth="1"/>
+    <col min="130" max="130" width="5.109375" customWidth="1"/>
     <col min="131" max="131" width="6" customWidth="1"/>
-    <col min="132" max="132" width="5.7109375" customWidth="1"/>
+    <col min="132" max="132" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:132" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:132" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>68</v>
@@ -1600,13 +1597,13 @@
       <c r="C1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="50"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
@@ -1639,7 +1636,7 @@
       <c r="AN1" s="1"/>
       <c r="AO1" s="1"/>
     </row>
-    <row r="2" spans="1:132" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:132" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -1682,33 +1679,33 @@
       <c r="AN2" s="1"/>
       <c r="AO2" s="1"/>
     </row>
-    <row r="3" spans="1:132" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:132" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" s="56" t="s">
         <v>67</v>
       </c>
-      <c r="E3" s="53"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="55" t="s">
+      <c r="E3" s="57"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="57" t="s">
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="58"/>
-      <c r="M3" s="58"/>
-      <c r="N3" s="58"/>
-      <c r="O3" s="58"/>
-      <c r="P3" s="58"/>
-      <c r="Q3" s="58"/>
-      <c r="R3" s="59"/>
+      <c r="L3" s="62"/>
+      <c r="M3" s="62"/>
+      <c r="N3" s="62"/>
+      <c r="O3" s="62"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="63"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -1733,33 +1730,33 @@
       <c r="AN3" s="1"/>
       <c r="AO3" s="1"/>
     </row>
-    <row r="4" spans="1:132" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:132" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="52" t="s">
+      <c r="D4" s="56" t="s">
         <v>65</v>
       </c>
-      <c r="E4" s="53"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="55" t="s">
+      <c r="E4" s="57"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="57" t="s">
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="L4" s="58"/>
-      <c r="M4" s="58"/>
-      <c r="N4" s="58"/>
-      <c r="O4" s="58"/>
-      <c r="P4" s="58"/>
-      <c r="Q4" s="58"/>
-      <c r="R4" s="59"/>
+      <c r="L4" s="62"/>
+      <c r="M4" s="62"/>
+      <c r="N4" s="62"/>
+      <c r="O4" s="62"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="63"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
@@ -1784,7 +1781,7 @@
       <c r="AN4" s="1"/>
       <c r="AO4" s="1"/>
     </row>
-    <row r="5" spans="1:132" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:132" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -1827,21 +1824,21 @@
       <c r="AN5" s="1"/>
       <c r="AO5" s="1"/>
     </row>
-    <row r="6" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
-      <c r="B6" s="60" t="s">
+      <c r="B6" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="62" t="s">
+      <c r="C6" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="62" t="s">
+      <c r="E6" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="62" t="s">
+      <c r="F6" s="52" t="s">
         <v>8</v>
       </c>
       <c r="G6" s="47" t="s">
@@ -2007,13 +2004,13 @@
       <c r="EA6" s="48"/>
       <c r="EB6" s="49"/>
     </row>
-    <row r="7" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
-      <c r="B7" s="61"/>
-      <c r="C7" s="63"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="63"/>
-      <c r="F7" s="63"/>
+      <c r="B7" s="51"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
       <c r="G7" s="37" t="s">
         <v>69</v>
       </c>
@@ -2189,211 +2186,211 @@
         <v>126</v>
       </c>
       <c r="BM7" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="BN7" s="37" t="s">
         <v>133</v>
       </c>
-      <c r="BN7" s="37" t="s">
+      <c r="BO7" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="BO7" s="37" t="s">
+      <c r="BP7" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="BP7" s="37" t="s">
+      <c r="BQ7" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="BQ7" s="37" t="s">
+      <c r="BR7" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="BR7" s="37" t="s">
+      <c r="BS7" s="37" t="s">
         <v>138</v>
       </c>
-      <c r="BS7" s="37" t="s">
+      <c r="BT7" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="BT7" s="37" t="s">
+      <c r="BU7" s="37" t="s">
         <v>140</v>
       </c>
-      <c r="BU7" s="37" t="s">
+      <c r="BV7" s="37" t="s">
         <v>141</v>
       </c>
-      <c r="BV7" s="37" t="s">
+      <c r="BW7" s="37" t="s">
         <v>142</v>
       </c>
-      <c r="BW7" s="37" t="s">
+      <c r="BX7" s="37" t="s">
         <v>143</v>
       </c>
-      <c r="BX7" s="37" t="s">
+      <c r="BY7" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="BY7" s="37" t="s">
+      <c r="BZ7" s="37" t="s">
         <v>145</v>
       </c>
-      <c r="BZ7" s="37" t="s">
+      <c r="CA7" s="37" t="s">
         <v>146</v>
       </c>
-      <c r="CA7" s="37" t="s">
+      <c r="CB7" s="37" t="s">
         <v>147</v>
       </c>
-      <c r="CB7" s="37" t="s">
+      <c r="CC7" s="37" t="s">
         <v>148</v>
       </c>
-      <c r="CC7" s="37" t="s">
+      <c r="CD7" s="37" t="s">
         <v>149</v>
       </c>
-      <c r="CD7" s="37" t="s">
+      <c r="CE7" s="37" t="s">
         <v>150</v>
       </c>
-      <c r="CE7" s="37" t="s">
+      <c r="CF7" s="37" t="s">
         <v>151</v>
       </c>
-      <c r="CF7" s="37" t="s">
+      <c r="CG7" s="37" t="s">
         <v>152</v>
       </c>
-      <c r="CG7" s="37" t="s">
+      <c r="CH7" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="CH7" s="37" t="s">
+      <c r="CI7" s="37" t="s">
         <v>154</v>
       </c>
-      <c r="CI7" s="37" t="s">
+      <c r="CJ7" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="CJ7" s="37" t="s">
+      <c r="CK7" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="CK7" s="37" t="s">
+      <c r="CL7" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="CL7" s="37" t="s">
+      <c r="CM7" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="CM7" s="37" t="s">
+      <c r="CN7" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="CN7" s="37" t="s">
+      <c r="CO7" s="37" t="s">
         <v>160</v>
       </c>
-      <c r="CO7" s="37" t="s">
+      <c r="CP7" s="37" t="s">
         <v>161</v>
       </c>
-      <c r="CP7" s="37" t="s">
+      <c r="CQ7" s="37" t="s">
         <v>162</v>
       </c>
-      <c r="CQ7" s="37" t="s">
+      <c r="CR7" s="37" t="s">
         <v>163</v>
       </c>
-      <c r="CR7" s="37" t="s">
+      <c r="CS7" s="37" t="s">
         <v>164</v>
       </c>
-      <c r="CS7" s="37" t="s">
+      <c r="CT7" s="37" t="s">
         <v>165</v>
       </c>
-      <c r="CT7" s="37" t="s">
+      <c r="CU7" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="CU7" s="37" t="s">
+      <c r="CV7" s="37" t="s">
         <v>167</v>
       </c>
-      <c r="CV7" s="37" t="s">
+      <c r="CW7" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="CW7" s="37" t="s">
+      <c r="CX7" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="CX7" s="37" t="s">
+      <c r="CY7" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="CY7" s="37" t="s">
+      <c r="CZ7" s="37" t="s">
         <v>171</v>
       </c>
-      <c r="CZ7" s="37" t="s">
+      <c r="DA7" s="37" t="s">
         <v>172</v>
       </c>
-      <c r="DA7" s="37" t="s">
+      <c r="DB7" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="DB7" s="37" t="s">
+      <c r="DC7" s="37" t="s">
         <v>174</v>
       </c>
-      <c r="DC7" s="37" t="s">
+      <c r="DD7" s="37" t="s">
         <v>175</v>
       </c>
-      <c r="DD7" s="37" t="s">
+      <c r="DE7" s="37" t="s">
         <v>176</v>
       </c>
-      <c r="DE7" s="37" t="s">
+      <c r="DF7" s="37" t="s">
         <v>177</v>
       </c>
-      <c r="DF7" s="37" t="s">
+      <c r="DG7" s="37" t="s">
         <v>178</v>
       </c>
-      <c r="DG7" s="37" t="s">
+      <c r="DH7" s="37" t="s">
         <v>179</v>
       </c>
-      <c r="DH7" s="37" t="s">
+      <c r="DI7" s="37" t="s">
         <v>180</v>
       </c>
-      <c r="DI7" s="37" t="s">
+      <c r="DJ7" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="DJ7" s="37" t="s">
+      <c r="DK7" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="DK7" s="37" t="s">
+      <c r="DL7" s="37" t="s">
         <v>183</v>
       </c>
-      <c r="DL7" s="37" t="s">
+      <c r="DM7" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="DM7" s="37" t="s">
+      <c r="DN7" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="DN7" s="37" t="s">
+      <c r="DO7" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="DO7" s="37" t="s">
+      <c r="DP7" s="37" t="s">
         <v>187</v>
       </c>
-      <c r="DP7" s="37" t="s">
+      <c r="DQ7" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="DQ7" s="37" t="s">
+      <c r="DR7" s="37" t="s">
         <v>189</v>
       </c>
-      <c r="DR7" s="37" t="s">
+      <c r="DS7" s="37" t="s">
         <v>190</v>
       </c>
-      <c r="DS7" s="37" t="s">
+      <c r="DT7" s="37" t="s">
         <v>191</v>
       </c>
-      <c r="DT7" s="37" t="s">
+      <c r="DU7" s="37" t="s">
         <v>192</v>
       </c>
-      <c r="DU7" s="37" t="s">
+      <c r="DV7" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="DV7" s="37" t="s">
+      <c r="DW7" s="37" t="s">
         <v>194</v>
       </c>
-      <c r="DW7" s="37" t="s">
+      <c r="DX7" s="37" t="s">
         <v>195</v>
       </c>
-      <c r="DX7" s="37" t="s">
+      <c r="DY7" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="DY7" s="37" t="s">
+      <c r="DZ7" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="DZ7" s="37" t="s">
+      <c r="EA7" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="EA7" s="37" t="s">
+      <c r="EB7" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="EB7" s="37" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="8" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="6">
         <v>1</v>
@@ -2531,7 +2528,7 @@
       <c r="EA8" s="7"/>
       <c r="EB8" s="7"/>
     </row>
-    <row r="9" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="6">
         <v>1.1000000000000001</v>
@@ -2668,7 +2665,7 @@
       <c r="EA9" s="12"/>
       <c r="EB9" s="12"/>
     </row>
-    <row r="10" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="6">
         <v>1.2</v>
@@ -2805,7 +2802,7 @@
       <c r="EA10" s="12"/>
       <c r="EB10" s="12"/>
     </row>
-    <row r="11" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="6">
         <v>1.3</v>
@@ -2942,7 +2939,7 @@
       <c r="EA11" s="12"/>
       <c r="EB11" s="12"/>
     </row>
-    <row r="12" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="6">
         <v>1.4</v>
@@ -3079,7 +3076,7 @@
       <c r="EA12" s="12"/>
       <c r="EB12" s="12"/>
     </row>
-    <row r="13" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="6">
         <v>1.5</v>
@@ -3216,7 +3213,7 @@
       <c r="EA13" s="12"/>
       <c r="EB13" s="12"/>
     </row>
-    <row r="14" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="6">
         <v>2</v>
@@ -3354,7 +3351,7 @@
       <c r="EA14" s="7"/>
       <c r="EB14" s="7"/>
     </row>
-    <row r="15" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="6">
         <v>2.1</v>
@@ -3485,7 +3482,7 @@
       <c r="EA15" s="12"/>
       <c r="EB15" s="12"/>
     </row>
-    <row r="16" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="6">
         <v>2.2000000000000002</v>
@@ -3616,7 +3613,7 @@
       <c r="EA16" s="12"/>
       <c r="EB16" s="12"/>
     </row>
-    <row r="17" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="6">
         <v>2.2999999999999998</v>
@@ -3747,7 +3744,7 @@
       <c r="EA17" s="12"/>
       <c r="EB17" s="12"/>
     </row>
-    <row r="18" spans="1:132" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:132" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="6">
         <v>2.4</v>
@@ -3881,7 +3878,7 @@
       <c r="EA18" s="12"/>
       <c r="EB18" s="12"/>
     </row>
-    <row r="19" spans="1:132" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:132" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="6">
         <v>2.5</v>
@@ -4019,7 +4016,7 @@
       <c r="EA19" s="12"/>
       <c r="EB19" s="12"/>
     </row>
-    <row r="20" spans="1:132" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:132" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="6">
         <v>3</v>
@@ -4157,7 +4154,7 @@
       <c r="EA20" s="7"/>
       <c r="EB20" s="7"/>
     </row>
-    <row r="21" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="6">
         <v>3.1</v>
@@ -4292,7 +4289,7 @@
       <c r="EA21" s="12"/>
       <c r="EB21" s="12"/>
     </row>
-    <row r="22" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="6">
         <v>3.2</v>
@@ -4427,7 +4424,7 @@
       <c r="EA22" s="12"/>
       <c r="EB22" s="12"/>
     </row>
-    <row r="23" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="6">
         <v>3.3</v>
@@ -4438,8 +4435,8 @@
       <c r="D23" s="40">
         <v>46046</v>
       </c>
-      <c r="E23" s="40" t="s">
-        <v>132</v>
+      <c r="E23" s="40">
+        <v>46032</v>
       </c>
       <c r="F23" s="15" t="s">
         <v>127</v>
@@ -4561,7 +4558,7 @@
       <c r="EA23" s="19"/>
       <c r="EB23" s="12"/>
     </row>
-    <row r="24" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="6">
         <v>3.4</v>
@@ -4572,8 +4569,8 @@
       <c r="D24" s="40">
         <v>46046</v>
       </c>
-      <c r="E24" s="40" t="s">
-        <v>132</v>
+      <c r="E24" s="40">
+        <v>46032</v>
       </c>
       <c r="F24" s="15" t="s">
         <v>127</v>
@@ -4695,7 +4692,7 @@
       <c r="EA24" s="19"/>
       <c r="EB24" s="12"/>
     </row>
-    <row r="25" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="6">
         <v>3.5</v>
@@ -4706,8 +4703,8 @@
       <c r="D25" s="40">
         <v>46046</v>
       </c>
-      <c r="E25" s="40" t="s">
-        <v>132</v>
+      <c r="E25" s="40">
+        <v>46032</v>
       </c>
       <c r="F25" s="15" t="s">
         <v>127</v>
@@ -4829,7 +4826,7 @@
       <c r="EA25" s="19"/>
       <c r="EB25" s="12"/>
     </row>
-    <row r="26" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="6">
         <v>4</v>
@@ -4967,7 +4964,7 @@
       <c r="EA26" s="7"/>
       <c r="EB26" s="7"/>
     </row>
-    <row r="27" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="6">
         <v>4.0999999999999996</v>
@@ -5099,7 +5096,7 @@
       <c r="EA27" s="19"/>
       <c r="EB27" s="12"/>
     </row>
-    <row r="28" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="6">
         <v>4.2</v>
@@ -5231,7 +5228,7 @@
       <c r="EA28" s="19"/>
       <c r="EB28" s="12"/>
     </row>
-    <row r="29" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="6">
         <v>4.3</v>
@@ -5363,7 +5360,7 @@
       <c r="EA29" s="19"/>
       <c r="EB29" s="12"/>
     </row>
-    <row r="30" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="6">
         <v>4.4000000000000004</v>
@@ -5481,7 +5478,7 @@
       <c r="EA30" s="19"/>
       <c r="EB30" s="12"/>
     </row>
-    <row r="31" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="6">
         <v>4.5</v>
@@ -5599,7 +5596,7 @@
       <c r="EA31" s="19"/>
       <c r="EB31" s="12"/>
     </row>
-    <row r="32" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="6">
         <v>5</v>
@@ -5737,7 +5734,7 @@
       <c r="EA32" s="7"/>
       <c r="EB32" s="7"/>
     </row>
-    <row r="33" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="6">
         <v>5.0999999999999996</v>
@@ -5877,7 +5874,7 @@
       <c r="EA33" s="12"/>
       <c r="EB33" s="12"/>
     </row>
-    <row r="34" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="6">
         <v>5.2</v>
@@ -6017,7 +6014,7 @@
       <c r="EA34" s="12"/>
       <c r="EB34" s="12"/>
     </row>
-    <row r="35" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="6">
         <v>6</v>
@@ -6155,7 +6152,7 @@
       <c r="EA35" s="7"/>
       <c r="EB35" s="7"/>
     </row>
-    <row r="36" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="6">
         <v>6.1</v>
@@ -6282,7 +6279,7 @@
       <c r="EA36" s="12"/>
       <c r="EB36" s="12"/>
     </row>
-    <row r="37" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="6">
         <v>6.2</v>
@@ -6409,7 +6406,7 @@
       <c r="EA37" s="12"/>
       <c r="EB37" s="12"/>
     </row>
-    <row r="38" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="6">
         <v>6.3</v>
@@ -6536,7 +6533,7 @@
       <c r="EA38" s="12"/>
       <c r="EB38" s="12"/>
     </row>
-    <row r="39" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="6">
         <v>7</v>
@@ -6674,7 +6671,7 @@
       <c r="EA39" s="7"/>
       <c r="EB39" s="7"/>
     </row>
-    <row r="40" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="6">
         <v>7.1</v>
@@ -6683,7 +6680,7 @@
         <v>57</v>
       </c>
       <c r="D40" s="40" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E40" s="35">
         <v>46025</v>
@@ -6789,7 +6786,7 @@
       <c r="CX40" s="21"/>
       <c r="CY40" s="19"/>
     </row>
-    <row r="41" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="6">
         <v>7.2</v>
@@ -6798,11 +6795,13 @@
         <v>58</v>
       </c>
       <c r="D41" s="35">
-        <v>46025</v>
+        <v>46376</v>
       </c>
-      <c r="E41" s="35"/>
+      <c r="E41" s="40">
+        <v>46032</v>
+      </c>
       <c r="F41" s="15" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G41" s="13"/>
       <c r="H41" s="14"/>
@@ -6902,7 +6901,7 @@
       <c r="CX41" s="21"/>
       <c r="CY41" s="19"/>
     </row>
-    <row r="42" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="6">
         <v>7.3</v>
@@ -6910,10 +6909,12 @@
       <c r="C42" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="D42" s="35"/>
-      <c r="E42" s="35"/>
+      <c r="D42" s="40">
+        <v>46032</v>
+      </c>
+      <c r="E42" s="40"/>
       <c r="F42" s="15" t="s">
-        <v>14</v>
+        <v>131</v>
       </c>
       <c r="G42" s="46"/>
       <c r="H42" s="46"/>
@@ -7013,7 +7014,7 @@
       <c r="CX42" s="25"/>
       <c r="CY42" s="19"/>
     </row>
-    <row r="43" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="6">
         <v>7.4</v>
@@ -7124,7 +7125,7 @@
       <c r="CX43" s="27"/>
       <c r="CY43" s="19"/>
     </row>
-    <row r="44" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="6">
         <v>7.5</v>
@@ -7224,7 +7225,7 @@
       <c r="CM44" s="46"/>
       <c r="CN44" s="46"/>
     </row>
-    <row r="45" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="6">
         <v>7.6</v>
@@ -7324,7 +7325,7 @@
       <c r="CM45" s="46"/>
       <c r="CN45" s="46"/>
     </row>
-    <row r="46" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="6">
         <v>7.7</v>
@@ -7424,7 +7425,7 @@
       <c r="CM46" s="46"/>
       <c r="CN46" s="46"/>
     </row>
-    <row r="47" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -7467,7 +7468,7 @@
       <c r="AN47" s="1"/>
       <c r="AO47" s="1"/>
     </row>
-    <row r="48" spans="1:132" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:132" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -7510,7 +7511,7 @@
       <c r="AN48" s="1"/>
       <c r="AO48" s="1"/>
     </row>
-    <row r="49" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -7553,7 +7554,7 @@
       <c r="AN49" s="1"/>
       <c r="AO49" s="1"/>
     </row>
-    <row r="50" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -7596,7 +7597,7 @@
       <c r="AN50" s="1"/>
       <c r="AO50" s="1"/>
     </row>
-    <row r="51" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -7639,7 +7640,7 @@
       <c r="AN51" s="1"/>
       <c r="AO51" s="1"/>
     </row>
-    <row r="52" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -7682,7 +7683,7 @@
       <c r="AN52" s="1"/>
       <c r="AO52" s="1"/>
     </row>
-    <row r="53" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -7725,7 +7726,7 @@
       <c r="AN53" s="1"/>
       <c r="AO53" s="1"/>
     </row>
-    <row r="54" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -7768,7 +7769,7 @@
       <c r="AN54" s="1"/>
       <c r="AO54" s="1"/>
     </row>
-    <row r="55" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -7811,7 +7812,7 @@
       <c r="AN55" s="1"/>
       <c r="AO55" s="1"/>
     </row>
-    <row r="56" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -7854,7 +7855,7 @@
       <c r="AN56" s="1"/>
       <c r="AO56" s="1"/>
     </row>
-    <row r="57" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -7897,7 +7898,7 @@
       <c r="AN57" s="1"/>
       <c r="AO57" s="1"/>
     </row>
-    <row r="58" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -7940,7 +7941,7 @@
       <c r="AN58" s="1"/>
       <c r="AO58" s="1"/>
     </row>
-    <row r="59" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -7983,7 +7984,7 @@
       <c r="AN59" s="1"/>
       <c r="AO59" s="1"/>
     </row>
-    <row r="60" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -8026,7 +8027,7 @@
       <c r="AN60" s="1"/>
       <c r="AO60" s="1"/>
     </row>
-    <row r="61" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -8069,7 +8070,7 @@
       <c r="AN61" s="1"/>
       <c r="AO61" s="1"/>
     </row>
-    <row r="62" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -8112,7 +8113,7 @@
       <c r="AN62" s="1"/>
       <c r="AO62" s="1"/>
     </row>
-    <row r="63" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -8155,7 +8156,7 @@
       <c r="AN63" s="1"/>
       <c r="AO63" s="1"/>
     </row>
-    <row r="64" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -8198,7 +8199,7 @@
       <c r="AN64" s="1"/>
       <c r="AO64" s="1"/>
     </row>
-    <row r="65" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -8241,7 +8242,7 @@
       <c r="AN65" s="1"/>
       <c r="AO65" s="1"/>
     </row>
-    <row r="66" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -8284,7 +8285,7 @@
       <c r="AN66" s="1"/>
       <c r="AO66" s="1"/>
     </row>
-    <row r="67" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -8327,7 +8328,7 @@
       <c r="AN67" s="1"/>
       <c r="AO67" s="1"/>
     </row>
-    <row r="68" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -8370,7 +8371,7 @@
       <c r="AN68" s="1"/>
       <c r="AO68" s="1"/>
     </row>
-    <row r="69" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -8413,7 +8414,7 @@
       <c r="AN69" s="1"/>
       <c r="AO69" s="1"/>
     </row>
-    <row r="70" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -8456,7 +8457,7 @@
       <c r="AN70" s="1"/>
       <c r="AO70" s="1"/>
     </row>
-    <row r="71" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -8499,7 +8500,7 @@
       <c r="AN71" s="1"/>
       <c r="AO71" s="1"/>
     </row>
-    <row r="72" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -8542,7 +8543,7 @@
       <c r="AN72" s="1"/>
       <c r="AO72" s="1"/>
     </row>
-    <row r="73" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -8585,7 +8586,7 @@
       <c r="AN73" s="1"/>
       <c r="AO73" s="1"/>
     </row>
-    <row r="74" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -8628,7 +8629,7 @@
       <c r="AN74" s="1"/>
       <c r="AO74" s="1"/>
     </row>
-    <row r="75" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -8671,7 +8672,7 @@
       <c r="AN75" s="1"/>
       <c r="AO75" s="1"/>
     </row>
-    <row r="76" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -8714,7 +8715,7 @@
       <c r="AN76" s="1"/>
       <c r="AO76" s="1"/>
     </row>
-    <row r="77" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -8757,7 +8758,7 @@
       <c r="AN77" s="1"/>
       <c r="AO77" s="1"/>
     </row>
-    <row r="78" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -8800,7 +8801,7 @@
       <c r="AN78" s="1"/>
       <c r="AO78" s="1"/>
     </row>
-    <row r="79" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -8843,7 +8844,7 @@
       <c r="AN79" s="1"/>
       <c r="AO79" s="1"/>
     </row>
-    <row r="80" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -8886,7 +8887,7 @@
       <c r="AN80" s="1"/>
       <c r="AO80" s="1"/>
     </row>
-    <row r="81" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -8929,7 +8930,7 @@
       <c r="AN81" s="1"/>
       <c r="AO81" s="1"/>
     </row>
-    <row r="82" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -8972,7 +8973,7 @@
       <c r="AN82" s="1"/>
       <c r="AO82" s="1"/>
     </row>
-    <row r="83" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -9015,7 +9016,7 @@
       <c r="AN83" s="1"/>
       <c r="AO83" s="1"/>
     </row>
-    <row r="84" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -9058,7 +9059,7 @@
       <c r="AN84" s="1"/>
       <c r="AO84" s="1"/>
     </row>
-    <row r="85" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -9101,7 +9102,7 @@
       <c r="AN85" s="1"/>
       <c r="AO85" s="1"/>
     </row>
-    <row r="86" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -9144,7 +9145,7 @@
       <c r="AN86" s="1"/>
       <c r="AO86" s="1"/>
     </row>
-    <row r="87" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -9187,7 +9188,7 @@
       <c r="AN87" s="1"/>
       <c r="AO87" s="1"/>
     </row>
-    <row r="88" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -9230,7 +9231,7 @@
       <c r="AN88" s="1"/>
       <c r="AO88" s="1"/>
     </row>
-    <row r="89" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -9273,7 +9274,7 @@
       <c r="AN89" s="1"/>
       <c r="AO89" s="1"/>
     </row>
-    <row r="90" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -9316,7 +9317,7 @@
       <c r="AN90" s="1"/>
       <c r="AO90" s="1"/>
     </row>
-    <row r="91" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -9359,7 +9360,7 @@
       <c r="AN91" s="1"/>
       <c r="AO91" s="1"/>
     </row>
-    <row r="92" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -9402,7 +9403,7 @@
       <c r="AN92" s="1"/>
       <c r="AO92" s="1"/>
     </row>
-    <row r="93" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -9445,7 +9446,7 @@
       <c r="AN93" s="1"/>
       <c r="AO93" s="1"/>
     </row>
-    <row r="94" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -9488,7 +9489,7 @@
       <c r="AN94" s="1"/>
       <c r="AO94" s="1"/>
     </row>
-    <row r="95" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -9531,7 +9532,7 @@
       <c r="AN95" s="1"/>
       <c r="AO95" s="1"/>
     </row>
-    <row r="96" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -9574,7 +9575,7 @@
       <c r="AN96" s="1"/>
       <c r="AO96" s="1"/>
     </row>
-    <row r="97" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -9617,7 +9618,7 @@
       <c r="AN97" s="1"/>
       <c r="AO97" s="1"/>
     </row>
-    <row r="98" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -9660,7 +9661,7 @@
       <c r="AN98" s="1"/>
       <c r="AO98" s="1"/>
     </row>
-    <row r="99" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -9703,7 +9704,7 @@
       <c r="AN99" s="1"/>
       <c r="AO99" s="1"/>
     </row>
-    <row r="100" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -9746,7 +9747,7 @@
       <c r="AN100" s="1"/>
       <c r="AO100" s="1"/>
     </row>
-    <row r="101" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -9789,7 +9790,7 @@
       <c r="AN101" s="1"/>
       <c r="AO101" s="1"/>
     </row>
-    <row r="102" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -9832,7 +9833,7 @@
       <c r="AN102" s="1"/>
       <c r="AO102" s="1"/>
     </row>
-    <row r="103" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -9875,7 +9876,7 @@
       <c r="AN103" s="1"/>
       <c r="AO103" s="1"/>
     </row>
-    <row r="104" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -9918,7 +9919,7 @@
       <c r="AN104" s="1"/>
       <c r="AO104" s="1"/>
     </row>
-    <row r="105" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -9961,7 +9962,7 @@
       <c r="AN105" s="1"/>
       <c r="AO105" s="1"/>
     </row>
-    <row r="106" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -10004,7 +10005,7 @@
       <c r="AN106" s="1"/>
       <c r="AO106" s="1"/>
     </row>
-    <row r="107" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -10047,7 +10048,7 @@
       <c r="AN107" s="1"/>
       <c r="AO107" s="1"/>
     </row>
-    <row r="108" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -10090,7 +10091,7 @@
       <c r="AN108" s="1"/>
       <c r="AO108" s="1"/>
     </row>
-    <row r="109" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -10133,7 +10134,7 @@
       <c r="AN109" s="1"/>
       <c r="AO109" s="1"/>
     </row>
-    <row r="110" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -10176,7 +10177,7 @@
       <c r="AN110" s="1"/>
       <c r="AO110" s="1"/>
     </row>
-    <row r="111" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -10219,7 +10220,7 @@
       <c r="AN111" s="1"/>
       <c r="AO111" s="1"/>
     </row>
-    <row r="112" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -10262,7 +10263,7 @@
       <c r="AN112" s="1"/>
       <c r="AO112" s="1"/>
     </row>
-    <row r="113" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -10305,7 +10306,7 @@
       <c r="AN113" s="1"/>
       <c r="AO113" s="1"/>
     </row>
-    <row r="114" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -10348,7 +10349,7 @@
       <c r="AN114" s="1"/>
       <c r="AO114" s="1"/>
     </row>
-    <row r="115" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -10391,7 +10392,7 @@
       <c r="AN115" s="1"/>
       <c r="AO115" s="1"/>
     </row>
-    <row r="116" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -10434,7 +10435,7 @@
       <c r="AN116" s="1"/>
       <c r="AO116" s="1"/>
     </row>
-    <row r="117" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -10477,7 +10478,7 @@
       <c r="AN117" s="1"/>
       <c r="AO117" s="1"/>
     </row>
-    <row r="118" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -10520,7 +10521,7 @@
       <c r="AN118" s="1"/>
       <c r="AO118" s="1"/>
     </row>
-    <row r="119" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -10563,7 +10564,7 @@
       <c r="AN119" s="1"/>
       <c r="AO119" s="1"/>
     </row>
-    <row r="120" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -10606,7 +10607,7 @@
       <c r="AN120" s="1"/>
       <c r="AO120" s="1"/>
     </row>
-    <row r="121" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -10649,7 +10650,7 @@
       <c r="AN121" s="1"/>
       <c r="AO121" s="1"/>
     </row>
-    <row r="122" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -10692,7 +10693,7 @@
       <c r="AN122" s="1"/>
       <c r="AO122" s="1"/>
     </row>
-    <row r="123" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -10735,7 +10736,7 @@
       <c r="AN123" s="1"/>
       <c r="AO123" s="1"/>
     </row>
-    <row r="124" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -10778,7 +10779,7 @@
       <c r="AN124" s="1"/>
       <c r="AO124" s="1"/>
     </row>
-    <row r="125" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -10821,7 +10822,7 @@
       <c r="AN125" s="1"/>
       <c r="AO125" s="1"/>
     </row>
-    <row r="126" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -10864,7 +10865,7 @@
       <c r="AN126" s="1"/>
       <c r="AO126" s="1"/>
     </row>
-    <row r="127" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -10907,7 +10908,7 @@
       <c r="AN127" s="1"/>
       <c r="AO127" s="1"/>
     </row>
-    <row r="128" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -10950,7 +10951,7 @@
       <c r="AN128" s="1"/>
       <c r="AO128" s="1"/>
     </row>
-    <row r="129" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -10993,7 +10994,7 @@
       <c r="AN129" s="1"/>
       <c r="AO129" s="1"/>
     </row>
-    <row r="130" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -11036,7 +11037,7 @@
       <c r="AN130" s="1"/>
       <c r="AO130" s="1"/>
     </row>
-    <row r="131" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -11079,7 +11080,7 @@
       <c r="AN131" s="1"/>
       <c r="AO131" s="1"/>
     </row>
-    <row r="132" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -11122,7 +11123,7 @@
       <c r="AN132" s="1"/>
       <c r="AO132" s="1"/>
     </row>
-    <row r="133" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -11165,7 +11166,7 @@
       <c r="AN133" s="1"/>
       <c r="AO133" s="1"/>
     </row>
-    <row r="134" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -11208,7 +11209,7 @@
       <c r="AN134" s="1"/>
       <c r="AO134" s="1"/>
     </row>
-    <row r="135" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -11251,7 +11252,7 @@
       <c r="AN135" s="1"/>
       <c r="AO135" s="1"/>
     </row>
-    <row r="136" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -11294,7 +11295,7 @@
       <c r="AN136" s="1"/>
       <c r="AO136" s="1"/>
     </row>
-    <row r="137" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -11337,7 +11338,7 @@
       <c r="AN137" s="1"/>
       <c r="AO137" s="1"/>
     </row>
-    <row r="138" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -11380,7 +11381,7 @@
       <c r="AN138" s="1"/>
       <c r="AO138" s="1"/>
     </row>
-    <row r="139" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -11423,7 +11424,7 @@
       <c r="AN139" s="1"/>
       <c r="AO139" s="1"/>
     </row>
-    <row r="140" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -11466,7 +11467,7 @@
       <c r="AN140" s="1"/>
       <c r="AO140" s="1"/>
     </row>
-    <row r="141" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -11509,7 +11510,7 @@
       <c r="AN141" s="1"/>
       <c r="AO141" s="1"/>
     </row>
-    <row r="142" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -11552,7 +11553,7 @@
       <c r="AN142" s="1"/>
       <c r="AO142" s="1"/>
     </row>
-    <row r="143" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -11595,7 +11596,7 @@
       <c r="AN143" s="1"/>
       <c r="AO143" s="1"/>
     </row>
-    <row r="144" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -11638,7 +11639,7 @@
       <c r="AN144" s="1"/>
       <c r="AO144" s="1"/>
     </row>
-    <row r="145" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -11681,7 +11682,7 @@
       <c r="AN145" s="1"/>
       <c r="AO145" s="1"/>
     </row>
-    <row r="146" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -11724,7 +11725,7 @@
       <c r="AN146" s="1"/>
       <c r="AO146" s="1"/>
     </row>
-    <row r="147" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -11767,7 +11768,7 @@
       <c r="AN147" s="1"/>
       <c r="AO147" s="1"/>
     </row>
-    <row r="148" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -11810,7 +11811,7 @@
       <c r="AN148" s="1"/>
       <c r="AO148" s="1"/>
     </row>
-    <row r="149" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -11853,7 +11854,7 @@
       <c r="AN149" s="1"/>
       <c r="AO149" s="1"/>
     </row>
-    <row r="150" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -11896,7 +11897,7 @@
       <c r="AN150" s="1"/>
       <c r="AO150" s="1"/>
     </row>
-    <row r="151" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -11939,7 +11940,7 @@
       <c r="AN151" s="1"/>
       <c r="AO151" s="1"/>
     </row>
-    <row r="152" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -11982,7 +11983,7 @@
       <c r="AN152" s="1"/>
       <c r="AO152" s="1"/>
     </row>
-    <row r="153" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -12025,7 +12026,7 @@
       <c r="AN153" s="1"/>
       <c r="AO153" s="1"/>
     </row>
-    <row r="154" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -12068,7 +12069,7 @@
       <c r="AN154" s="1"/>
       <c r="AO154" s="1"/>
     </row>
-    <row r="155" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -12111,7 +12112,7 @@
       <c r="AN155" s="1"/>
       <c r="AO155" s="1"/>
     </row>
-    <row r="156" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -12154,7 +12155,7 @@
       <c r="AN156" s="1"/>
       <c r="AO156" s="1"/>
     </row>
-    <row r="157" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -12197,7 +12198,7 @@
       <c r="AN157" s="1"/>
       <c r="AO157" s="1"/>
     </row>
-    <row r="158" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -12240,7 +12241,7 @@
       <c r="AN158" s="1"/>
       <c r="AO158" s="1"/>
     </row>
-    <row r="159" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -12283,7 +12284,7 @@
       <c r="AN159" s="1"/>
       <c r="AO159" s="1"/>
     </row>
-    <row r="160" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -12326,7 +12327,7 @@
       <c r="AN160" s="1"/>
       <c r="AO160" s="1"/>
     </row>
-    <row r="161" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -12369,7 +12370,7 @@
       <c r="AN161" s="1"/>
       <c r="AO161" s="1"/>
     </row>
-    <row r="162" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -12412,7 +12413,7 @@
       <c r="AN162" s="1"/>
       <c r="AO162" s="1"/>
     </row>
-    <row r="163" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -12455,7 +12456,7 @@
       <c r="AN163" s="1"/>
       <c r="AO163" s="1"/>
     </row>
-    <row r="164" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -12498,7 +12499,7 @@
       <c r="AN164" s="1"/>
       <c r="AO164" s="1"/>
     </row>
-    <row r="165" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -12541,7 +12542,7 @@
       <c r="AN165" s="1"/>
       <c r="AO165" s="1"/>
     </row>
-    <row r="166" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -12584,7 +12585,7 @@
       <c r="AN166" s="1"/>
       <c r="AO166" s="1"/>
     </row>
-    <row r="167" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -12627,7 +12628,7 @@
       <c r="AN167" s="1"/>
       <c r="AO167" s="1"/>
     </row>
-    <row r="168" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -12670,7 +12671,7 @@
       <c r="AN168" s="1"/>
       <c r="AO168" s="1"/>
     </row>
-    <row r="169" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -12713,7 +12714,7 @@
       <c r="AN169" s="1"/>
       <c r="AO169" s="1"/>
     </row>
-    <row r="170" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -12756,7 +12757,7 @@
       <c r="AN170" s="1"/>
       <c r="AO170" s="1"/>
     </row>
-    <row r="171" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -12799,7 +12800,7 @@
       <c r="AN171" s="1"/>
       <c r="AO171" s="1"/>
     </row>
-    <row r="172" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -12842,7 +12843,7 @@
       <c r="AN172" s="1"/>
       <c r="AO172" s="1"/>
     </row>
-    <row r="173" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -12885,7 +12886,7 @@
       <c r="AN173" s="1"/>
       <c r="AO173" s="1"/>
     </row>
-    <row r="174" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -12928,7 +12929,7 @@
       <c r="AN174" s="1"/>
       <c r="AO174" s="1"/>
     </row>
-    <row r="175" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -12971,7 +12972,7 @@
       <c r="AN175" s="1"/>
       <c r="AO175" s="1"/>
     </row>
-    <row r="176" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -13014,7 +13015,7 @@
       <c r="AN176" s="1"/>
       <c r="AO176" s="1"/>
     </row>
-    <row r="177" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -13057,7 +13058,7 @@
       <c r="AN177" s="1"/>
       <c r="AO177" s="1"/>
     </row>
-    <row r="178" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -13100,7 +13101,7 @@
       <c r="AN178" s="1"/>
       <c r="AO178" s="1"/>
     </row>
-    <row r="179" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -13143,7 +13144,7 @@
       <c r="AN179" s="1"/>
       <c r="AO179" s="1"/>
     </row>
-    <row r="180" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -13186,7 +13187,7 @@
       <c r="AN180" s="1"/>
       <c r="AO180" s="1"/>
     </row>
-    <row r="181" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -13229,7 +13230,7 @@
       <c r="AN181" s="1"/>
       <c r="AO181" s="1"/>
     </row>
-    <row r="182" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -13272,7 +13273,7 @@
       <c r="AN182" s="1"/>
       <c r="AO182" s="1"/>
     </row>
-    <row r="183" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -13315,7 +13316,7 @@
       <c r="AN183" s="1"/>
       <c r="AO183" s="1"/>
     </row>
-    <row r="184" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -13358,7 +13359,7 @@
       <c r="AN184" s="1"/>
       <c r="AO184" s="1"/>
     </row>
-    <row r="185" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -13401,7 +13402,7 @@
       <c r="AN185" s="1"/>
       <c r="AO185" s="1"/>
     </row>
-    <row r="186" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -13444,7 +13445,7 @@
       <c r="AN186" s="1"/>
       <c r="AO186" s="1"/>
     </row>
-    <row r="187" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -13487,7 +13488,7 @@
       <c r="AN187" s="1"/>
       <c r="AO187" s="1"/>
     </row>
-    <row r="188" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -13530,7 +13531,7 @@
       <c r="AN188" s="1"/>
       <c r="AO188" s="1"/>
     </row>
-    <row r="189" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -13573,7 +13574,7 @@
       <c r="AN189" s="1"/>
       <c r="AO189" s="1"/>
     </row>
-    <row r="190" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -13616,7 +13617,7 @@
       <c r="AN190" s="1"/>
       <c r="AO190" s="1"/>
     </row>
-    <row r="191" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -13659,7 +13660,7 @@
       <c r="AN191" s="1"/>
       <c r="AO191" s="1"/>
     </row>
-    <row r="192" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -13702,7 +13703,7 @@
       <c r="AN192" s="1"/>
       <c r="AO192" s="1"/>
     </row>
-    <row r="193" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -13745,7 +13746,7 @@
       <c r="AN193" s="1"/>
       <c r="AO193" s="1"/>
     </row>
-    <row r="194" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -13788,7 +13789,7 @@
       <c r="AN194" s="1"/>
       <c r="AO194" s="1"/>
     </row>
-    <row r="195" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -13831,7 +13832,7 @@
       <c r="AN195" s="1"/>
       <c r="AO195" s="1"/>
     </row>
-    <row r="196" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -13874,7 +13875,7 @@
       <c r="AN196" s="1"/>
       <c r="AO196" s="1"/>
     </row>
-    <row r="197" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -13917,7 +13918,7 @@
       <c r="AN197" s="1"/>
       <c r="AO197" s="1"/>
     </row>
-    <row r="198" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -13960,7 +13961,7 @@
       <c r="AN198" s="1"/>
       <c r="AO198" s="1"/>
     </row>
-    <row r="199" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -14003,7 +14004,7 @@
       <c r="AN199" s="1"/>
       <c r="AO199" s="1"/>
     </row>
-    <row r="200" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -14046,7 +14047,7 @@
       <c r="AN200" s="1"/>
       <c r="AO200" s="1"/>
     </row>
-    <row r="201" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -14089,7 +14090,7 @@
       <c r="AN201" s="1"/>
       <c r="AO201" s="1"/>
     </row>
-    <row r="202" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -14132,7 +14133,7 @@
       <c r="AN202" s="1"/>
       <c r="AO202" s="1"/>
     </row>
-    <row r="203" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -14175,7 +14176,7 @@
       <c r="AN203" s="1"/>
       <c r="AO203" s="1"/>
     </row>
-    <row r="204" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -14218,7 +14219,7 @@
       <c r="AN204" s="1"/>
       <c r="AO204" s="1"/>
     </row>
-    <row r="205" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -14261,7 +14262,7 @@
       <c r="AN205" s="1"/>
       <c r="AO205" s="1"/>
     </row>
-    <row r="206" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -14304,7 +14305,7 @@
       <c r="AN206" s="1"/>
       <c r="AO206" s="1"/>
     </row>
-    <row r="207" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -14347,7 +14348,7 @@
       <c r="AN207" s="1"/>
       <c r="AO207" s="1"/>
     </row>
-    <row r="208" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -14390,7 +14391,7 @@
       <c r="AN208" s="1"/>
       <c r="AO208" s="1"/>
     </row>
-    <row r="209" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -14433,7 +14434,7 @@
       <c r="AN209" s="1"/>
       <c r="AO209" s="1"/>
     </row>
-    <row r="210" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -14476,7 +14477,7 @@
       <c r="AN210" s="1"/>
       <c r="AO210" s="1"/>
     </row>
-    <row r="211" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -14519,7 +14520,7 @@
       <c r="AN211" s="1"/>
       <c r="AO211" s="1"/>
     </row>
-    <row r="212" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -14562,7 +14563,7 @@
       <c r="AN212" s="1"/>
       <c r="AO212" s="1"/>
     </row>
-    <row r="213" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -14605,7 +14606,7 @@
       <c r="AN213" s="1"/>
       <c r="AO213" s="1"/>
     </row>
-    <row r="214" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -14648,7 +14649,7 @@
       <c r="AN214" s="1"/>
       <c r="AO214" s="1"/>
     </row>
-    <row r="215" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -14691,7 +14692,7 @@
       <c r="AN215" s="1"/>
       <c r="AO215" s="1"/>
     </row>
-    <row r="216" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -14734,7 +14735,7 @@
       <c r="AN216" s="1"/>
       <c r="AO216" s="1"/>
     </row>
-    <row r="217" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -14777,7 +14778,7 @@
       <c r="AN217" s="1"/>
       <c r="AO217" s="1"/>
     </row>
-    <row r="218" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -14820,7 +14821,7 @@
       <c r="AN218" s="1"/>
       <c r="AO218" s="1"/>
     </row>
-    <row r="219" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -14863,7 +14864,7 @@
       <c r="AN219" s="1"/>
       <c r="AO219" s="1"/>
     </row>
-    <row r="220" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -14906,7 +14907,7 @@
       <c r="AN220" s="1"/>
       <c r="AO220" s="1"/>
     </row>
-    <row r="221" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -14949,7 +14950,7 @@
       <c r="AN221" s="1"/>
       <c r="AO221" s="1"/>
     </row>
-    <row r="222" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -14992,7 +14993,7 @@
       <c r="AN222" s="1"/>
       <c r="AO222" s="1"/>
     </row>
-    <row r="223" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -15035,7 +15036,7 @@
       <c r="AN223" s="1"/>
       <c r="AO223" s="1"/>
     </row>
-    <row r="224" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -15078,7 +15079,7 @@
       <c r="AN224" s="1"/>
       <c r="AO224" s="1"/>
     </row>
-    <row r="225" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -15121,7 +15122,7 @@
       <c r="AN225" s="1"/>
       <c r="AO225" s="1"/>
     </row>
-    <row r="226" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -15164,7 +15165,7 @@
       <c r="AN226" s="1"/>
       <c r="AO226" s="1"/>
     </row>
-    <row r="227" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -15207,7 +15208,7 @@
       <c r="AN227" s="1"/>
       <c r="AO227" s="1"/>
     </row>
-    <row r="228" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -15250,7 +15251,7 @@
       <c r="AN228" s="1"/>
       <c r="AO228" s="1"/>
     </row>
-    <row r="229" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -15293,7 +15294,7 @@
       <c r="AN229" s="1"/>
       <c r="AO229" s="1"/>
     </row>
-    <row r="230" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -15336,7 +15337,7 @@
       <c r="AN230" s="1"/>
       <c r="AO230" s="1"/>
     </row>
-    <row r="231" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -15379,7 +15380,7 @@
       <c r="AN231" s="1"/>
       <c r="AO231" s="1"/>
     </row>
-    <row r="232" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -15422,7 +15423,7 @@
       <c r="AN232" s="1"/>
       <c r="AO232" s="1"/>
     </row>
-    <row r="233" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -15465,7 +15466,7 @@
       <c r="AN233" s="1"/>
       <c r="AO233" s="1"/>
     </row>
-    <row r="234" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -15508,7 +15509,7 @@
       <c r="AN234" s="1"/>
       <c r="AO234" s="1"/>
     </row>
-    <row r="235" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -15551,7 +15552,7 @@
       <c r="AN235" s="1"/>
       <c r="AO235" s="1"/>
     </row>
-    <row r="236" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -15594,7 +15595,7 @@
       <c r="AN236" s="1"/>
       <c r="AO236" s="1"/>
     </row>
-    <row r="237" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -15637,7 +15638,7 @@
       <c r="AN237" s="1"/>
       <c r="AO237" s="1"/>
     </row>
-    <row r="238" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -15680,7 +15681,7 @@
       <c r="AN238" s="1"/>
       <c r="AO238" s="1"/>
     </row>
-    <row r="239" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -15723,7 +15724,7 @@
       <c r="AN239" s="1"/>
       <c r="AO239" s="1"/>
     </row>
-    <row r="240" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -15766,7 +15767,7 @@
       <c r="AN240" s="1"/>
       <c r="AO240" s="1"/>
     </row>
-    <row r="241" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -15809,7 +15810,7 @@
       <c r="AN241" s="1"/>
       <c r="AO241" s="1"/>
     </row>
-    <row r="242" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -15852,7 +15853,7 @@
       <c r="AN242" s="1"/>
       <c r="AO242" s="1"/>
     </row>
-    <row r="243" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -15895,7 +15896,7 @@
       <c r="AN243" s="1"/>
       <c r="AO243" s="1"/>
     </row>
-    <row r="244" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -15938,7 +15939,7 @@
       <c r="AN244" s="1"/>
       <c r="AO244" s="1"/>
     </row>
-    <row r="245" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -15981,7 +15982,7 @@
       <c r="AN245" s="1"/>
       <c r="AO245" s="1"/>
     </row>
-    <row r="246" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -16024,7 +16025,7 @@
       <c r="AN246" s="1"/>
       <c r="AO246" s="1"/>
     </row>
-    <row r="247" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -16067,7 +16068,7 @@
       <c r="AN247" s="1"/>
       <c r="AO247" s="1"/>
     </row>
-    <row r="248" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -16110,7 +16111,7 @@
       <c r="AN248" s="1"/>
       <c r="AO248" s="1"/>
     </row>
-    <row r="249" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -16153,7 +16154,7 @@
       <c r="AN249" s="1"/>
       <c r="AO249" s="1"/>
     </row>
-    <row r="250" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -16196,7 +16197,7 @@
       <c r="AN250" s="1"/>
       <c r="AO250" s="1"/>
     </row>
-    <row r="251" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -16239,7 +16240,7 @@
       <c r="AN251" s="1"/>
       <c r="AO251" s="1"/>
     </row>
-    <row r="252" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -16282,7 +16283,7 @@
       <c r="AN252" s="1"/>
       <c r="AO252" s="1"/>
     </row>
-    <row r="253" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -16325,7 +16326,7 @@
       <c r="AN253" s="1"/>
       <c r="AO253" s="1"/>
     </row>
-    <row r="254" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -16368,7 +16369,7 @@
       <c r="AN254" s="1"/>
       <c r="AO254" s="1"/>
     </row>
-    <row r="255" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -16411,7 +16412,7 @@
       <c r="AN255" s="1"/>
       <c r="AO255" s="1"/>
     </row>
-    <row r="256" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -16454,7 +16455,7 @@
       <c r="AN256" s="1"/>
       <c r="AO256" s="1"/>
     </row>
-    <row r="257" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -16497,7 +16498,7 @@
       <c r="AN257" s="1"/>
       <c r="AO257" s="1"/>
     </row>
-    <row r="258" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -16540,7 +16541,7 @@
       <c r="AN258" s="1"/>
       <c r="AO258" s="1"/>
     </row>
-    <row r="259" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -16583,7 +16584,7 @@
       <c r="AN259" s="1"/>
       <c r="AO259" s="1"/>
     </row>
-    <row r="260" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -16626,7 +16627,7 @@
       <c r="AN260" s="1"/>
       <c r="AO260" s="1"/>
     </row>
-    <row r="261" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -16669,7 +16670,7 @@
       <c r="AN261" s="1"/>
       <c r="AO261" s="1"/>
     </row>
-    <row r="262" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -16712,7 +16713,7 @@
       <c r="AN262" s="1"/>
       <c r="AO262" s="1"/>
     </row>
-    <row r="263" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -16755,7 +16756,7 @@
       <c r="AN263" s="1"/>
       <c r="AO263" s="1"/>
     </row>
-    <row r="264" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -16798,7 +16799,7 @@
       <c r="AN264" s="1"/>
       <c r="AO264" s="1"/>
     </row>
-    <row r="265" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -16841,7 +16842,7 @@
       <c r="AN265" s="1"/>
       <c r="AO265" s="1"/>
     </row>
-    <row r="266" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -16884,7 +16885,7 @@
       <c r="AN266" s="1"/>
       <c r="AO266" s="1"/>
     </row>
-    <row r="267" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -16927,7 +16928,7 @@
       <c r="AN267" s="1"/>
       <c r="AO267" s="1"/>
     </row>
-    <row r="268" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -16970,7 +16971,7 @@
       <c r="AN268" s="1"/>
       <c r="AO268" s="1"/>
     </row>
-    <row r="269" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -17013,7 +17014,7 @@
       <c r="AN269" s="1"/>
       <c r="AO269" s="1"/>
     </row>
-    <row r="270" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -17056,7 +17057,7 @@
       <c r="AN270" s="1"/>
       <c r="AO270" s="1"/>
     </row>
-    <row r="271" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -17099,7 +17100,7 @@
       <c r="AN271" s="1"/>
       <c r="AO271" s="1"/>
     </row>
-    <row r="272" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -17142,7 +17143,7 @@
       <c r="AN272" s="1"/>
       <c r="AO272" s="1"/>
     </row>
-    <row r="273" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -17185,7 +17186,7 @@
       <c r="AN273" s="1"/>
       <c r="AO273" s="1"/>
     </row>
-    <row r="274" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -17228,7 +17229,7 @@
       <c r="AN274" s="1"/>
       <c r="AO274" s="1"/>
     </row>
-    <row r="275" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -17271,7 +17272,7 @@
       <c r="AN275" s="1"/>
       <c r="AO275" s="1"/>
     </row>
-    <row r="276" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -17314,7 +17315,7 @@
       <c r="AN276" s="1"/>
       <c r="AO276" s="1"/>
     </row>
-    <row r="277" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -17357,7 +17358,7 @@
       <c r="AN277" s="1"/>
       <c r="AO277" s="1"/>
     </row>
-    <row r="278" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -17400,7 +17401,7 @@
       <c r="AN278" s="1"/>
       <c r="AO278" s="1"/>
     </row>
-    <row r="279" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -17443,7 +17444,7 @@
       <c r="AN279" s="1"/>
       <c r="AO279" s="1"/>
     </row>
-    <row r="280" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -17486,7 +17487,7 @@
       <c r="AN280" s="1"/>
       <c r="AO280" s="1"/>
     </row>
-    <row r="281" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -17529,7 +17530,7 @@
       <c r="AN281" s="1"/>
       <c r="AO281" s="1"/>
     </row>
-    <row r="282" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -17572,7 +17573,7 @@
       <c r="AN282" s="1"/>
       <c r="AO282" s="1"/>
     </row>
-    <row r="283" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -17615,7 +17616,7 @@
       <c r="AN283" s="1"/>
       <c r="AO283" s="1"/>
     </row>
-    <row r="284" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -17658,7 +17659,7 @@
       <c r="AN284" s="1"/>
       <c r="AO284" s="1"/>
     </row>
-    <row r="285" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -17701,7 +17702,7 @@
       <c r="AN285" s="1"/>
       <c r="AO285" s="1"/>
     </row>
-    <row r="286" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -17744,7 +17745,7 @@
       <c r="AN286" s="1"/>
       <c r="AO286" s="1"/>
     </row>
-    <row r="287" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -17787,7 +17788,7 @@
       <c r="AN287" s="1"/>
       <c r="AO287" s="1"/>
     </row>
-    <row r="288" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -17830,7 +17831,7 @@
       <c r="AN288" s="1"/>
       <c r="AO288" s="1"/>
     </row>
-    <row r="289" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -17873,7 +17874,7 @@
       <c r="AN289" s="1"/>
       <c r="AO289" s="1"/>
     </row>
-    <row r="290" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -17916,7 +17917,7 @@
       <c r="AN290" s="1"/>
       <c r="AO290" s="1"/>
     </row>
-    <row r="291" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -17959,7 +17960,7 @@
       <c r="AN291" s="1"/>
       <c r="AO291" s="1"/>
     </row>
-    <row r="292" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -18002,7 +18003,7 @@
       <c r="AN292" s="1"/>
       <c r="AO292" s="1"/>
     </row>
-    <row r="293" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -18045,7 +18046,7 @@
       <c r="AN293" s="1"/>
       <c r="AO293" s="1"/>
     </row>
-    <row r="294" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -18088,7 +18089,7 @@
       <c r="AN294" s="1"/>
       <c r="AO294" s="1"/>
     </row>
-    <row r="295" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -18131,7 +18132,7 @@
       <c r="AN295" s="1"/>
       <c r="AO295" s="1"/>
     </row>
-    <row r="296" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -18174,7 +18175,7 @@
       <c r="AN296" s="1"/>
       <c r="AO296" s="1"/>
     </row>
-    <row r="297" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -18217,7 +18218,7 @@
       <c r="AN297" s="1"/>
       <c r="AO297" s="1"/>
     </row>
-    <row r="298" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -18260,7 +18261,7 @@
       <c r="AN298" s="1"/>
       <c r="AO298" s="1"/>
     </row>
-    <row r="299" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -18303,7 +18304,7 @@
       <c r="AN299" s="1"/>
       <c r="AO299" s="1"/>
     </row>
-    <row r="300" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -18346,7 +18347,7 @@
       <c r="AN300" s="1"/>
       <c r="AO300" s="1"/>
     </row>
-    <row r="301" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -18389,7 +18390,7 @@
       <c r="AN301" s="1"/>
       <c r="AO301" s="1"/>
     </row>
-    <row r="302" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -18432,7 +18433,7 @@
       <c r="AN302" s="1"/>
       <c r="AO302" s="1"/>
     </row>
-    <row r="303" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -18475,7 +18476,7 @@
       <c r="AN303" s="1"/>
       <c r="AO303" s="1"/>
     </row>
-    <row r="304" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -18518,7 +18519,7 @@
       <c r="AN304" s="1"/>
       <c r="AO304" s="1"/>
     </row>
-    <row r="305" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -18561,7 +18562,7 @@
       <c r="AN305" s="1"/>
       <c r="AO305" s="1"/>
     </row>
-    <row r="306" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -18604,7 +18605,7 @@
       <c r="AN306" s="1"/>
       <c r="AO306" s="1"/>
     </row>
-    <row r="307" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -18647,7 +18648,7 @@
       <c r="AN307" s="1"/>
       <c r="AO307" s="1"/>
     </row>
-    <row r="308" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -18690,7 +18691,7 @@
       <c r="AN308" s="1"/>
       <c r="AO308" s="1"/>
     </row>
-    <row r="309" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -18733,7 +18734,7 @@
       <c r="AN309" s="1"/>
       <c r="AO309" s="1"/>
     </row>
-    <row r="310" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -18776,7 +18777,7 @@
       <c r="AN310" s="1"/>
       <c r="AO310" s="1"/>
     </row>
-    <row r="311" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -18819,7 +18820,7 @@
       <c r="AN311" s="1"/>
       <c r="AO311" s="1"/>
     </row>
-    <row r="312" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -18862,7 +18863,7 @@
       <c r="AN312" s="1"/>
       <c r="AO312" s="1"/>
     </row>
-    <row r="313" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -18905,7 +18906,7 @@
       <c r="AN313" s="1"/>
       <c r="AO313" s="1"/>
     </row>
-    <row r="314" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -18948,7 +18949,7 @@
       <c r="AN314" s="1"/>
       <c r="AO314" s="1"/>
     </row>
-    <row r="315" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -18991,7 +18992,7 @@
       <c r="AN315" s="1"/>
       <c r="AO315" s="1"/>
     </row>
-    <row r="316" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -19034,7 +19035,7 @@
       <c r="AN316" s="1"/>
       <c r="AO316" s="1"/>
     </row>
-    <row r="317" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -19077,7 +19078,7 @@
       <c r="AN317" s="1"/>
       <c r="AO317" s="1"/>
     </row>
-    <row r="318" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -19120,7 +19121,7 @@
       <c r="AN318" s="1"/>
       <c r="AO318" s="1"/>
     </row>
-    <row r="319" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -19163,7 +19164,7 @@
       <c r="AN319" s="1"/>
       <c r="AO319" s="1"/>
     </row>
-    <row r="320" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -19206,7 +19207,7 @@
       <c r="AN320" s="1"/>
       <c r="AO320" s="1"/>
     </row>
-    <row r="321" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -19249,7 +19250,7 @@
       <c r="AN321" s="1"/>
       <c r="AO321" s="1"/>
     </row>
-    <row r="322" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -19292,7 +19293,7 @@
       <c r="AN322" s="1"/>
       <c r="AO322" s="1"/>
     </row>
-    <row r="323" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -19335,7 +19336,7 @@
       <c r="AN323" s="1"/>
       <c r="AO323" s="1"/>
     </row>
-    <row r="324" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -19378,7 +19379,7 @@
       <c r="AN324" s="1"/>
       <c r="AO324" s="1"/>
     </row>
-    <row r="325" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -19421,7 +19422,7 @@
       <c r="AN325" s="1"/>
       <c r="AO325" s="1"/>
     </row>
-    <row r="326" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -19464,7 +19465,7 @@
       <c r="AN326" s="1"/>
       <c r="AO326" s="1"/>
     </row>
-    <row r="327" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -19507,7 +19508,7 @@
       <c r="AN327" s="1"/>
       <c r="AO327" s="1"/>
     </row>
-    <row r="328" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -19550,7 +19551,7 @@
       <c r="AN328" s="1"/>
       <c r="AO328" s="1"/>
     </row>
-    <row r="329" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -19593,7 +19594,7 @@
       <c r="AN329" s="1"/>
       <c r="AO329" s="1"/>
     </row>
-    <row r="330" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -19636,7 +19637,7 @@
       <c r="AN330" s="1"/>
       <c r="AO330" s="1"/>
     </row>
-    <row r="331" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -19679,7 +19680,7 @@
       <c r="AN331" s="1"/>
       <c r="AO331" s="1"/>
     </row>
-    <row r="332" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -19722,7 +19723,7 @@
       <c r="AN332" s="1"/>
       <c r="AO332" s="1"/>
     </row>
-    <row r="333" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -19765,7 +19766,7 @@
       <c r="AN333" s="1"/>
       <c r="AO333" s="1"/>
     </row>
-    <row r="334" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -19808,7 +19809,7 @@
       <c r="AN334" s="1"/>
       <c r="AO334" s="1"/>
     </row>
-    <row r="335" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -19851,7 +19852,7 @@
       <c r="AN335" s="1"/>
       <c r="AO335" s="1"/>
     </row>
-    <row r="336" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -19894,7 +19895,7 @@
       <c r="AN336" s="1"/>
       <c r="AO336" s="1"/>
     </row>
-    <row r="337" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -19937,7 +19938,7 @@
       <c r="AN337" s="1"/>
       <c r="AO337" s="1"/>
     </row>
-    <row r="338" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -19980,7 +19981,7 @@
       <c r="AN338" s="1"/>
       <c r="AO338" s="1"/>
     </row>
-    <row r="339" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -20023,7 +20024,7 @@
       <c r="AN339" s="1"/>
       <c r="AO339" s="1"/>
     </row>
-    <row r="340" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -20066,7 +20067,7 @@
       <c r="AN340" s="1"/>
       <c r="AO340" s="1"/>
     </row>
-    <row r="341" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -20109,7 +20110,7 @@
       <c r="AN341" s="1"/>
       <c r="AO341" s="1"/>
     </row>
-    <row r="342" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -20152,7 +20153,7 @@
       <c r="AN342" s="1"/>
       <c r="AO342" s="1"/>
     </row>
-    <row r="343" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -20195,7 +20196,7 @@
       <c r="AN343" s="1"/>
       <c r="AO343" s="1"/>
     </row>
-    <row r="344" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -20238,7 +20239,7 @@
       <c r="AN344" s="1"/>
       <c r="AO344" s="1"/>
     </row>
-    <row r="345" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -20281,7 +20282,7 @@
       <c r="AN345" s="1"/>
       <c r="AO345" s="1"/>
     </row>
-    <row r="346" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -20324,7 +20325,7 @@
       <c r="AN346" s="1"/>
       <c r="AO346" s="1"/>
     </row>
-    <row r="347" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -20367,7 +20368,7 @@
       <c r="AN347" s="1"/>
       <c r="AO347" s="1"/>
     </row>
-    <row r="348" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -20410,7 +20411,7 @@
       <c r="AN348" s="1"/>
       <c r="AO348" s="1"/>
     </row>
-    <row r="349" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -20453,7 +20454,7 @@
       <c r="AN349" s="1"/>
       <c r="AO349" s="1"/>
     </row>
-    <row r="350" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -20496,7 +20497,7 @@
       <c r="AN350" s="1"/>
       <c r="AO350" s="1"/>
     </row>
-    <row r="351" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -20539,7 +20540,7 @@
       <c r="AN351" s="1"/>
       <c r="AO351" s="1"/>
     </row>
-    <row r="352" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -20582,7 +20583,7 @@
       <c r="AN352" s="1"/>
       <c r="AO352" s="1"/>
     </row>
-    <row r="353" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -20625,7 +20626,7 @@
       <c r="AN353" s="1"/>
       <c r="AO353" s="1"/>
     </row>
-    <row r="354" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -20668,7 +20669,7 @@
       <c r="AN354" s="1"/>
       <c r="AO354" s="1"/>
     </row>
-    <row r="355" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -20711,7 +20712,7 @@
       <c r="AN355" s="1"/>
       <c r="AO355" s="1"/>
     </row>
-    <row r="356" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -20754,7 +20755,7 @@
       <c r="AN356" s="1"/>
       <c r="AO356" s="1"/>
     </row>
-    <row r="357" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -20797,7 +20798,7 @@
       <c r="AN357" s="1"/>
       <c r="AO357" s="1"/>
     </row>
-    <row r="358" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -20840,7 +20841,7 @@
       <c r="AN358" s="1"/>
       <c r="AO358" s="1"/>
     </row>
-    <row r="359" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -20883,7 +20884,7 @@
       <c r="AN359" s="1"/>
       <c r="AO359" s="1"/>
     </row>
-    <row r="360" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -20926,7 +20927,7 @@
       <c r="AN360" s="1"/>
       <c r="AO360" s="1"/>
     </row>
-    <row r="361" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -20969,7 +20970,7 @@
       <c r="AN361" s="1"/>
       <c r="AO361" s="1"/>
     </row>
-    <row r="362" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -21012,7 +21013,7 @@
       <c r="AN362" s="1"/>
       <c r="AO362" s="1"/>
     </row>
-    <row r="363" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -21055,7 +21056,7 @@
       <c r="AN363" s="1"/>
       <c r="AO363" s="1"/>
     </row>
-    <row r="364" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -21098,7 +21099,7 @@
       <c r="AN364" s="1"/>
       <c r="AO364" s="1"/>
     </row>
-    <row r="365" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -21141,7 +21142,7 @@
       <c r="AN365" s="1"/>
       <c r="AO365" s="1"/>
     </row>
-    <row r="366" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -21184,7 +21185,7 @@
       <c r="AN366" s="1"/>
       <c r="AO366" s="1"/>
     </row>
-    <row r="367" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -21227,7 +21228,7 @@
       <c r="AN367" s="1"/>
       <c r="AO367" s="1"/>
     </row>
-    <row r="368" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -21270,7 +21271,7 @@
       <c r="AN368" s="1"/>
       <c r="AO368" s="1"/>
     </row>
-    <row r="369" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -21313,7 +21314,7 @@
       <c r="AN369" s="1"/>
       <c r="AO369" s="1"/>
     </row>
-    <row r="370" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -21356,7 +21357,7 @@
       <c r="AN370" s="1"/>
       <c r="AO370" s="1"/>
     </row>
-    <row r="371" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -21399,7 +21400,7 @@
       <c r="AN371" s="1"/>
       <c r="AO371" s="1"/>
     </row>
-    <row r="372" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -21442,7 +21443,7 @@
       <c r="AN372" s="1"/>
       <c r="AO372" s="1"/>
     </row>
-    <row r="373" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -21485,7 +21486,7 @@
       <c r="AN373" s="1"/>
       <c r="AO373" s="1"/>
     </row>
-    <row r="374" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -21528,7 +21529,7 @@
       <c r="AN374" s="1"/>
       <c r="AO374" s="1"/>
     </row>
-    <row r="375" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -21571,7 +21572,7 @@
       <c r="AN375" s="1"/>
       <c r="AO375" s="1"/>
     </row>
-    <row r="376" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -21614,7 +21615,7 @@
       <c r="AN376" s="1"/>
       <c r="AO376" s="1"/>
     </row>
-    <row r="377" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -21657,7 +21658,7 @@
       <c r="AN377" s="1"/>
       <c r="AO377" s="1"/>
     </row>
-    <row r="378" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -21700,7 +21701,7 @@
       <c r="AN378" s="1"/>
       <c r="AO378" s="1"/>
     </row>
-    <row r="379" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -21743,7 +21744,7 @@
       <c r="AN379" s="1"/>
       <c r="AO379" s="1"/>
     </row>
-    <row r="380" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -21786,7 +21787,7 @@
       <c r="AN380" s="1"/>
       <c r="AO380" s="1"/>
     </row>
-    <row r="381" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -21829,7 +21830,7 @@
       <c r="AN381" s="1"/>
       <c r="AO381" s="1"/>
     </row>
-    <row r="382" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -21872,7 +21873,7 @@
       <c r="AN382" s="1"/>
       <c r="AO382" s="1"/>
     </row>
-    <row r="383" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -21915,7 +21916,7 @@
       <c r="AN383" s="1"/>
       <c r="AO383" s="1"/>
     </row>
-    <row r="384" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -21958,7 +21959,7 @@
       <c r="AN384" s="1"/>
       <c r="AO384" s="1"/>
     </row>
-    <row r="385" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -22001,7 +22002,7 @@
       <c r="AN385" s="1"/>
       <c r="AO385" s="1"/>
     </row>
-    <row r="386" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -22044,7 +22045,7 @@
       <c r="AN386" s="1"/>
       <c r="AO386" s="1"/>
     </row>
-    <row r="387" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -22087,7 +22088,7 @@
       <c r="AN387" s="1"/>
       <c r="AO387" s="1"/>
     </row>
-    <row r="388" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -22130,7 +22131,7 @@
       <c r="AN388" s="1"/>
       <c r="AO388" s="1"/>
     </row>
-    <row r="389" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -22173,7 +22174,7 @@
       <c r="AN389" s="1"/>
       <c r="AO389" s="1"/>
     </row>
-    <row r="390" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -22216,7 +22217,7 @@
       <c r="AN390" s="1"/>
       <c r="AO390" s="1"/>
     </row>
-    <row r="391" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -22259,7 +22260,7 @@
       <c r="AN391" s="1"/>
       <c r="AO391" s="1"/>
     </row>
-    <row r="392" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -22302,7 +22303,7 @@
       <c r="AN392" s="1"/>
       <c r="AO392" s="1"/>
     </row>
-    <row r="393" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -22345,7 +22346,7 @@
       <c r="AN393" s="1"/>
       <c r="AO393" s="1"/>
     </row>
-    <row r="394" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -22388,7 +22389,7 @@
       <c r="AN394" s="1"/>
       <c r="AO394" s="1"/>
     </row>
-    <row r="395" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -22431,7 +22432,7 @@
       <c r="AN395" s="1"/>
       <c r="AO395" s="1"/>
     </row>
-    <row r="396" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -22474,7 +22475,7 @@
       <c r="AN396" s="1"/>
       <c r="AO396" s="1"/>
     </row>
-    <row r="397" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -22517,7 +22518,7 @@
       <c r="AN397" s="1"/>
       <c r="AO397" s="1"/>
     </row>
-    <row r="398" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -22560,7 +22561,7 @@
       <c r="AN398" s="1"/>
       <c r="AO398" s="1"/>
     </row>
-    <row r="399" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -22603,7 +22604,7 @@
       <c r="AN399" s="1"/>
       <c r="AO399" s="1"/>
     </row>
-    <row r="400" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -22646,7 +22647,7 @@
       <c r="AN400" s="1"/>
       <c r="AO400" s="1"/>
     </row>
-    <row r="401" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -22689,7 +22690,7 @@
       <c r="AN401" s="1"/>
       <c r="AO401" s="1"/>
     </row>
-    <row r="402" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -22732,7 +22733,7 @@
       <c r="AN402" s="1"/>
       <c r="AO402" s="1"/>
     </row>
-    <row r="403" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -22775,7 +22776,7 @@
       <c r="AN403" s="1"/>
       <c r="AO403" s="1"/>
     </row>
-    <row r="404" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -22818,7 +22819,7 @@
       <c r="AN404" s="1"/>
       <c r="AO404" s="1"/>
     </row>
-    <row r="405" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -22861,7 +22862,7 @@
       <c r="AN405" s="1"/>
       <c r="AO405" s="1"/>
     </row>
-    <row r="406" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -22904,7 +22905,7 @@
       <c r="AN406" s="1"/>
       <c r="AO406" s="1"/>
     </row>
-    <row r="407" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -22947,7 +22948,7 @@
       <c r="AN407" s="1"/>
       <c r="AO407" s="1"/>
     </row>
-    <row r="408" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -22990,7 +22991,7 @@
       <c r="AN408" s="1"/>
       <c r="AO408" s="1"/>
     </row>
-    <row r="409" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -23033,7 +23034,7 @@
       <c r="AN409" s="1"/>
       <c r="AO409" s="1"/>
     </row>
-    <row r="410" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -23076,7 +23077,7 @@
       <c r="AN410" s="1"/>
       <c r="AO410" s="1"/>
     </row>
-    <row r="411" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -23119,7 +23120,7 @@
       <c r="AN411" s="1"/>
       <c r="AO411" s="1"/>
     </row>
-    <row r="412" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -23162,7 +23163,7 @@
       <c r="AN412" s="1"/>
       <c r="AO412" s="1"/>
     </row>
-    <row r="413" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -23205,7 +23206,7 @@
       <c r="AN413" s="1"/>
       <c r="AO413" s="1"/>
     </row>
-    <row r="414" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -23248,7 +23249,7 @@
       <c r="AN414" s="1"/>
       <c r="AO414" s="1"/>
     </row>
-    <row r="415" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -23291,7 +23292,7 @@
       <c r="AN415" s="1"/>
       <c r="AO415" s="1"/>
     </row>
-    <row r="416" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -23334,7 +23335,7 @@
       <c r="AN416" s="1"/>
       <c r="AO416" s="1"/>
     </row>
-    <row r="417" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -23377,7 +23378,7 @@
       <c r="AN417" s="1"/>
       <c r="AO417" s="1"/>
     </row>
-    <row r="418" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -23420,7 +23421,7 @@
       <c r="AN418" s="1"/>
       <c r="AO418" s="1"/>
     </row>
-    <row r="419" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -23463,7 +23464,7 @@
       <c r="AN419" s="1"/>
       <c r="AO419" s="1"/>
     </row>
-    <row r="420" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -23506,7 +23507,7 @@
       <c r="AN420" s="1"/>
       <c r="AO420" s="1"/>
     </row>
-    <row r="421" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -23549,7 +23550,7 @@
       <c r="AN421" s="1"/>
       <c r="AO421" s="1"/>
     </row>
-    <row r="422" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -23592,7 +23593,7 @@
       <c r="AN422" s="1"/>
       <c r="AO422" s="1"/>
     </row>
-    <row r="423" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -23635,7 +23636,7 @@
       <c r="AN423" s="1"/>
       <c r="AO423" s="1"/>
     </row>
-    <row r="424" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -23678,7 +23679,7 @@
       <c r="AN424" s="1"/>
       <c r="AO424" s="1"/>
     </row>
-    <row r="425" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -23721,7 +23722,7 @@
       <c r="AN425" s="1"/>
       <c r="AO425" s="1"/>
     </row>
-    <row r="426" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -23764,7 +23765,7 @@
       <c r="AN426" s="1"/>
       <c r="AO426" s="1"/>
     </row>
-    <row r="427" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -23807,7 +23808,7 @@
       <c r="AN427" s="1"/>
       <c r="AO427" s="1"/>
     </row>
-    <row r="428" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -23850,7 +23851,7 @@
       <c r="AN428" s="1"/>
       <c r="AO428" s="1"/>
     </row>
-    <row r="429" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -23893,7 +23894,7 @@
       <c r="AN429" s="1"/>
       <c r="AO429" s="1"/>
     </row>
-    <row r="430" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -23936,7 +23937,7 @@
       <c r="AN430" s="1"/>
       <c r="AO430" s="1"/>
     </row>
-    <row r="431" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -23979,7 +23980,7 @@
       <c r="AN431" s="1"/>
       <c r="AO431" s="1"/>
     </row>
-    <row r="432" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -24022,7 +24023,7 @@
       <c r="AN432" s="1"/>
       <c r="AO432" s="1"/>
     </row>
-    <row r="433" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -24065,7 +24066,7 @@
       <c r="AN433" s="1"/>
       <c r="AO433" s="1"/>
     </row>
-    <row r="434" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -24108,7 +24109,7 @@
       <c r="AN434" s="1"/>
       <c r="AO434" s="1"/>
     </row>
-    <row r="435" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -24151,7 +24152,7 @@
       <c r="AN435" s="1"/>
       <c r="AO435" s="1"/>
     </row>
-    <row r="436" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -24194,7 +24195,7 @@
       <c r="AN436" s="1"/>
       <c r="AO436" s="1"/>
     </row>
-    <row r="437" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -24237,7 +24238,7 @@
       <c r="AN437" s="1"/>
       <c r="AO437" s="1"/>
     </row>
-    <row r="438" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -24280,7 +24281,7 @@
       <c r="AN438" s="1"/>
       <c r="AO438" s="1"/>
     </row>
-    <row r="439" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -24323,7 +24324,7 @@
       <c r="AN439" s="1"/>
       <c r="AO439" s="1"/>
     </row>
-    <row r="440" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -24366,7 +24367,7 @@
       <c r="AN440" s="1"/>
       <c r="AO440" s="1"/>
     </row>
-    <row r="441" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -24409,7 +24410,7 @@
       <c r="AN441" s="1"/>
       <c r="AO441" s="1"/>
     </row>
-    <row r="442" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -24452,7 +24453,7 @@
       <c r="AN442" s="1"/>
       <c r="AO442" s="1"/>
     </row>
-    <row r="443" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -24495,7 +24496,7 @@
       <c r="AN443" s="1"/>
       <c r="AO443" s="1"/>
     </row>
-    <row r="444" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -24538,7 +24539,7 @@
       <c r="AN444" s="1"/>
       <c r="AO444" s="1"/>
     </row>
-    <row r="445" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -24581,7 +24582,7 @@
       <c r="AN445" s="1"/>
       <c r="AO445" s="1"/>
     </row>
-    <row r="446" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -24624,7 +24625,7 @@
       <c r="AN446" s="1"/>
       <c r="AO446" s="1"/>
     </row>
-    <row r="447" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -24667,7 +24668,7 @@
       <c r="AN447" s="1"/>
       <c r="AO447" s="1"/>
     </row>
-    <row r="448" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -24710,7 +24711,7 @@
       <c r="AN448" s="1"/>
       <c r="AO448" s="1"/>
     </row>
-    <row r="449" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -24753,7 +24754,7 @@
       <c r="AN449" s="1"/>
       <c r="AO449" s="1"/>
     </row>
-    <row r="450" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -24796,7 +24797,7 @@
       <c r="AN450" s="1"/>
       <c r="AO450" s="1"/>
     </row>
-    <row r="451" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -24839,7 +24840,7 @@
       <c r="AN451" s="1"/>
       <c r="AO451" s="1"/>
     </row>
-    <row r="452" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -24882,7 +24883,7 @@
       <c r="AN452" s="1"/>
       <c r="AO452" s="1"/>
     </row>
-    <row r="453" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -24925,7 +24926,7 @@
       <c r="AN453" s="1"/>
       <c r="AO453" s="1"/>
     </row>
-    <row r="454" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -24968,7 +24969,7 @@
       <c r="AN454" s="1"/>
       <c r="AO454" s="1"/>
     </row>
-    <row r="455" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -25011,7 +25012,7 @@
       <c r="AN455" s="1"/>
       <c r="AO455" s="1"/>
     </row>
-    <row r="456" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -25054,7 +25055,7 @@
       <c r="AN456" s="1"/>
       <c r="AO456" s="1"/>
     </row>
-    <row r="457" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -25097,7 +25098,7 @@
       <c r="AN457" s="1"/>
       <c r="AO457" s="1"/>
     </row>
-    <row r="458" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -25140,7 +25141,7 @@
       <c r="AN458" s="1"/>
       <c r="AO458" s="1"/>
     </row>
-    <row r="459" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -25183,7 +25184,7 @@
       <c r="AN459" s="1"/>
       <c r="AO459" s="1"/>
     </row>
-    <row r="460" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -25226,7 +25227,7 @@
       <c r="AN460" s="1"/>
       <c r="AO460" s="1"/>
     </row>
-    <row r="461" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -25269,7 +25270,7 @@
       <c r="AN461" s="1"/>
       <c r="AO461" s="1"/>
     </row>
-    <row r="462" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -25312,7 +25313,7 @@
       <c r="AN462" s="1"/>
       <c r="AO462" s="1"/>
     </row>
-    <row r="463" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -25355,7 +25356,7 @@
       <c r="AN463" s="1"/>
       <c r="AO463" s="1"/>
     </row>
-    <row r="464" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -25398,7 +25399,7 @@
       <c r="AN464" s="1"/>
       <c r="AO464" s="1"/>
     </row>
-    <row r="465" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -25441,7 +25442,7 @@
       <c r="AN465" s="1"/>
       <c r="AO465" s="1"/>
     </row>
-    <row r="466" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -25484,7 +25485,7 @@
       <c r="AN466" s="1"/>
       <c r="AO466" s="1"/>
     </row>
-    <row r="467" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -25527,7 +25528,7 @@
       <c r="AN467" s="1"/>
       <c r="AO467" s="1"/>
     </row>
-    <row r="468" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -25570,7 +25571,7 @@
       <c r="AN468" s="1"/>
       <c r="AO468" s="1"/>
     </row>
-    <row r="469" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -25613,7 +25614,7 @@
       <c r="AN469" s="1"/>
       <c r="AO469" s="1"/>
     </row>
-    <row r="470" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -25656,7 +25657,7 @@
       <c r="AN470" s="1"/>
       <c r="AO470" s="1"/>
     </row>
-    <row r="471" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -25699,7 +25700,7 @@
       <c r="AN471" s="1"/>
       <c r="AO471" s="1"/>
     </row>
-    <row r="472" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -25742,7 +25743,7 @@
       <c r="AN472" s="1"/>
       <c r="AO472" s="1"/>
     </row>
-    <row r="473" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -25785,7 +25786,7 @@
       <c r="AN473" s="1"/>
       <c r="AO473" s="1"/>
     </row>
-    <row r="474" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -25828,7 +25829,7 @@
       <c r="AN474" s="1"/>
       <c r="AO474" s="1"/>
     </row>
-    <row r="475" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -25871,7 +25872,7 @@
       <c r="AN475" s="1"/>
       <c r="AO475" s="1"/>
     </row>
-    <row r="476" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -25914,7 +25915,7 @@
       <c r="AN476" s="1"/>
       <c r="AO476" s="1"/>
     </row>
-    <row r="477" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -25957,7 +25958,7 @@
       <c r="AN477" s="1"/>
       <c r="AO477" s="1"/>
     </row>
-    <row r="478" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -26000,7 +26001,7 @@
       <c r="AN478" s="1"/>
       <c r="AO478" s="1"/>
     </row>
-    <row r="479" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -26043,7 +26044,7 @@
       <c r="AN479" s="1"/>
       <c r="AO479" s="1"/>
     </row>
-    <row r="480" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -26086,7 +26087,7 @@
       <c r="AN480" s="1"/>
       <c r="AO480" s="1"/>
     </row>
-    <row r="481" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -26129,7 +26130,7 @@
       <c r="AN481" s="1"/>
       <c r="AO481" s="1"/>
     </row>
-    <row r="482" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -26172,7 +26173,7 @@
       <c r="AN482" s="1"/>
       <c r="AO482" s="1"/>
     </row>
-    <row r="483" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -26215,7 +26216,7 @@
       <c r="AN483" s="1"/>
       <c r="AO483" s="1"/>
     </row>
-    <row r="484" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -26258,7 +26259,7 @@
       <c r="AN484" s="1"/>
       <c r="AO484" s="1"/>
     </row>
-    <row r="485" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -26301,7 +26302,7 @@
       <c r="AN485" s="1"/>
       <c r="AO485" s="1"/>
     </row>
-    <row r="486" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -26344,7 +26345,7 @@
       <c r="AN486" s="1"/>
       <c r="AO486" s="1"/>
     </row>
-    <row r="487" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -26387,7 +26388,7 @@
       <c r="AN487" s="1"/>
       <c r="AO487" s="1"/>
     </row>
-    <row r="488" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -26430,7 +26431,7 @@
       <c r="AN488" s="1"/>
       <c r="AO488" s="1"/>
     </row>
-    <row r="489" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -26473,7 +26474,7 @@
       <c r="AN489" s="1"/>
       <c r="AO489" s="1"/>
     </row>
-    <row r="490" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -26516,7 +26517,7 @@
       <c r="AN490" s="1"/>
       <c r="AO490" s="1"/>
     </row>
-    <row r="491" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -26559,7 +26560,7 @@
       <c r="AN491" s="1"/>
       <c r="AO491" s="1"/>
     </row>
-    <row r="492" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -26602,7 +26603,7 @@
       <c r="AN492" s="1"/>
       <c r="AO492" s="1"/>
     </row>
-    <row r="493" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -26645,7 +26646,7 @@
       <c r="AN493" s="1"/>
       <c r="AO493" s="1"/>
     </row>
-    <row r="494" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -26688,7 +26689,7 @@
       <c r="AN494" s="1"/>
       <c r="AO494" s="1"/>
     </row>
-    <row r="495" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -26731,7 +26732,7 @@
       <c r="AN495" s="1"/>
       <c r="AO495" s="1"/>
     </row>
-    <row r="496" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -26774,7 +26775,7 @@
       <c r="AN496" s="1"/>
       <c r="AO496" s="1"/>
     </row>
-    <row r="497" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -26817,7 +26818,7 @@
       <c r="AN497" s="1"/>
       <c r="AO497" s="1"/>
     </row>
-    <row r="498" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -26860,7 +26861,7 @@
       <c r="AN498" s="1"/>
       <c r="AO498" s="1"/>
     </row>
-    <row r="499" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -26903,7 +26904,7 @@
       <c r="AN499" s="1"/>
       <c r="AO499" s="1"/>
     </row>
-    <row r="500" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
@@ -26946,7 +26947,7 @@
       <c r="AN500" s="1"/>
       <c r="AO500" s="1"/>
     </row>
-    <row r="501" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A501" s="1"/>
       <c r="B501" s="1"/>
       <c r="C501" s="1"/>
@@ -26989,7 +26990,7 @@
       <c r="AN501" s="1"/>
       <c r="AO501" s="1"/>
     </row>
-    <row r="502" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="1"/>
@@ -27032,7 +27033,7 @@
       <c r="AN502" s="1"/>
       <c r="AO502" s="1"/>
     </row>
-    <row r="503" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A503" s="1"/>
       <c r="B503" s="1"/>
       <c r="C503" s="1"/>
@@ -27075,7 +27076,7 @@
       <c r="AN503" s="1"/>
       <c r="AO503" s="1"/>
     </row>
-    <row r="504" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A504" s="1"/>
       <c r="B504" s="1"/>
       <c r="C504" s="1"/>
@@ -27118,7 +27119,7 @@
       <c r="AN504" s="1"/>
       <c r="AO504" s="1"/>
     </row>
-    <row r="505" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A505" s="1"/>
       <c r="B505" s="1"/>
       <c r="C505" s="1"/>
@@ -27161,7 +27162,7 @@
       <c r="AN505" s="1"/>
       <c r="AO505" s="1"/>
     </row>
-    <row r="506" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A506" s="1"/>
       <c r="B506" s="1"/>
       <c r="C506" s="1"/>
@@ -27204,7 +27205,7 @@
       <c r="AN506" s="1"/>
       <c r="AO506" s="1"/>
     </row>
-    <row r="507" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A507" s="1"/>
       <c r="B507" s="1"/>
       <c r="C507" s="1"/>
@@ -27247,7 +27248,7 @@
       <c r="AN507" s="1"/>
       <c r="AO507" s="1"/>
     </row>
-    <row r="508" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A508" s="1"/>
       <c r="B508" s="1"/>
       <c r="C508" s="1"/>
@@ -27290,7 +27291,7 @@
       <c r="AN508" s="1"/>
       <c r="AO508" s="1"/>
     </row>
-    <row r="509" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A509" s="1"/>
       <c r="B509" s="1"/>
       <c r="C509" s="1"/>
@@ -27333,7 +27334,7 @@
       <c r="AN509" s="1"/>
       <c r="AO509" s="1"/>
     </row>
-    <row r="510" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A510" s="1"/>
       <c r="B510" s="1"/>
       <c r="C510" s="1"/>
@@ -27376,7 +27377,7 @@
       <c r="AN510" s="1"/>
       <c r="AO510" s="1"/>
     </row>
-    <row r="511" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A511" s="1"/>
       <c r="B511" s="1"/>
       <c r="C511" s="1"/>
@@ -27419,7 +27420,7 @@
       <c r="AN511" s="1"/>
       <c r="AO511" s="1"/>
     </row>
-    <row r="512" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A512" s="1"/>
       <c r="B512" s="1"/>
       <c r="C512" s="1"/>
@@ -27462,7 +27463,7 @@
       <c r="AN512" s="1"/>
       <c r="AO512" s="1"/>
     </row>
-    <row r="513" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A513" s="1"/>
       <c r="B513" s="1"/>
       <c r="C513" s="1"/>
@@ -27505,7 +27506,7 @@
       <c r="AN513" s="1"/>
       <c r="AO513" s="1"/>
     </row>
-    <row r="514" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A514" s="1"/>
       <c r="B514" s="1"/>
       <c r="C514" s="1"/>
@@ -27548,7 +27549,7 @@
       <c r="AN514" s="1"/>
       <c r="AO514" s="1"/>
     </row>
-    <row r="515" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A515" s="1"/>
       <c r="B515" s="1"/>
       <c r="C515" s="1"/>
@@ -27591,7 +27592,7 @@
       <c r="AN515" s="1"/>
       <c r="AO515" s="1"/>
     </row>
-    <row r="516" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A516" s="1"/>
       <c r="B516" s="1"/>
       <c r="C516" s="1"/>
@@ -27634,7 +27635,7 @@
       <c r="AN516" s="1"/>
       <c r="AO516" s="1"/>
     </row>
-    <row r="517" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A517" s="1"/>
       <c r="B517" s="1"/>
       <c r="C517" s="1"/>
@@ -27677,7 +27678,7 @@
       <c r="AN517" s="1"/>
       <c r="AO517" s="1"/>
     </row>
-    <row r="518" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A518" s="1"/>
       <c r="B518" s="1"/>
       <c r="C518" s="1"/>
@@ -27720,7 +27721,7 @@
       <c r="AN518" s="1"/>
       <c r="AO518" s="1"/>
     </row>
-    <row r="519" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A519" s="1"/>
       <c r="B519" s="1"/>
       <c r="C519" s="1"/>
@@ -27763,7 +27764,7 @@
       <c r="AN519" s="1"/>
       <c r="AO519" s="1"/>
     </row>
-    <row r="520" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A520" s="1"/>
       <c r="B520" s="1"/>
       <c r="C520" s="1"/>
@@ -27806,7 +27807,7 @@
       <c r="AN520" s="1"/>
       <c r="AO520" s="1"/>
     </row>
-    <row r="521" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A521" s="1"/>
       <c r="B521" s="1"/>
       <c r="C521" s="1"/>
@@ -27849,7 +27850,7 @@
       <c r="AN521" s="1"/>
       <c r="AO521" s="1"/>
     </row>
-    <row r="522" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
       <c r="C522" s="1"/>
@@ -27892,7 +27893,7 @@
       <c r="AN522" s="1"/>
       <c r="AO522" s="1"/>
     </row>
-    <row r="523" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="1"/>
@@ -27935,7 +27936,7 @@
       <c r="AN523" s="1"/>
       <c r="AO523" s="1"/>
     </row>
-    <row r="524" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
       <c r="C524" s="1"/>
@@ -27978,7 +27979,7 @@
       <c r="AN524" s="1"/>
       <c r="AO524" s="1"/>
     </row>
-    <row r="525" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A525" s="1"/>
       <c r="B525" s="1"/>
       <c r="C525" s="1"/>
@@ -28021,7 +28022,7 @@
       <c r="AN525" s="1"/>
       <c r="AO525" s="1"/>
     </row>
-    <row r="526" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A526" s="1"/>
       <c r="B526" s="1"/>
       <c r="C526" s="1"/>
@@ -28064,7 +28065,7 @@
       <c r="AN526" s="1"/>
       <c r="AO526" s="1"/>
     </row>
-    <row r="527" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A527" s="1"/>
       <c r="B527" s="1"/>
       <c r="C527" s="1"/>
@@ -28107,7 +28108,7 @@
       <c r="AN527" s="1"/>
       <c r="AO527" s="1"/>
     </row>
-    <row r="528" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
@@ -28150,7 +28151,7 @@
       <c r="AN528" s="1"/>
       <c r="AO528" s="1"/>
     </row>
-    <row r="529" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
@@ -28193,7 +28194,7 @@
       <c r="AN529" s="1"/>
       <c r="AO529" s="1"/>
     </row>
-    <row r="530" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
@@ -28236,7 +28237,7 @@
       <c r="AN530" s="1"/>
       <c r="AO530" s="1"/>
     </row>
-    <row r="531" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
@@ -28279,7 +28280,7 @@
       <c r="AN531" s="1"/>
       <c r="AO531" s="1"/>
     </row>
-    <row r="532" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A532" s="1"/>
       <c r="B532" s="1"/>
       <c r="C532" s="1"/>
@@ -28322,7 +28323,7 @@
       <c r="AN532" s="1"/>
       <c r="AO532" s="1"/>
     </row>
-    <row r="533" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
       <c r="C533" s="1"/>
@@ -28365,7 +28366,7 @@
       <c r="AN533" s="1"/>
       <c r="AO533" s="1"/>
     </row>
-    <row r="534" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
@@ -28408,7 +28409,7 @@
       <c r="AN534" s="1"/>
       <c r="AO534" s="1"/>
     </row>
-    <row r="535" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
@@ -28451,7 +28452,7 @@
       <c r="AN535" s="1"/>
       <c r="AO535" s="1"/>
     </row>
-    <row r="536" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
@@ -28494,7 +28495,7 @@
       <c r="AN536" s="1"/>
       <c r="AO536" s="1"/>
     </row>
-    <row r="537" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
@@ -28537,7 +28538,7 @@
       <c r="AN537" s="1"/>
       <c r="AO537" s="1"/>
     </row>
-    <row r="538" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
       <c r="C538" s="1"/>
@@ -28580,7 +28581,7 @@
       <c r="AN538" s="1"/>
       <c r="AO538" s="1"/>
     </row>
-    <row r="539" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
       <c r="C539" s="1"/>
@@ -28623,7 +28624,7 @@
       <c r="AN539" s="1"/>
       <c r="AO539" s="1"/>
     </row>
-    <row r="540" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
@@ -28666,7 +28667,7 @@
       <c r="AN540" s="1"/>
       <c r="AO540" s="1"/>
     </row>
-    <row r="541" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
       <c r="C541" s="1"/>
@@ -28709,7 +28710,7 @@
       <c r="AN541" s="1"/>
       <c r="AO541" s="1"/>
     </row>
-    <row r="542" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
@@ -28752,7 +28753,7 @@
       <c r="AN542" s="1"/>
       <c r="AO542" s="1"/>
     </row>
-    <row r="543" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A543" s="1"/>
       <c r="B543" s="1"/>
       <c r="C543" s="1"/>
@@ -28795,7 +28796,7 @@
       <c r="AN543" s="1"/>
       <c r="AO543" s="1"/>
     </row>
-    <row r="544" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
       <c r="C544" s="1"/>
@@ -28838,7 +28839,7 @@
       <c r="AN544" s="1"/>
       <c r="AO544" s="1"/>
     </row>
-    <row r="545" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A545" s="1"/>
       <c r="B545" s="1"/>
       <c r="C545" s="1"/>
@@ -28881,7 +28882,7 @@
       <c r="AN545" s="1"/>
       <c r="AO545" s="1"/>
     </row>
-    <row r="546" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A546" s="1"/>
       <c r="B546" s="1"/>
       <c r="C546" s="1"/>
@@ -28924,7 +28925,7 @@
       <c r="AN546" s="1"/>
       <c r="AO546" s="1"/>
     </row>
-    <row r="547" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
@@ -28967,7 +28968,7 @@
       <c r="AN547" s="1"/>
       <c r="AO547" s="1"/>
     </row>
-    <row r="548" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
@@ -29010,7 +29011,7 @@
       <c r="AN548" s="1"/>
       <c r="AO548" s="1"/>
     </row>
-    <row r="549" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
@@ -29053,7 +29054,7 @@
       <c r="AN549" s="1"/>
       <c r="AO549" s="1"/>
     </row>
-    <row r="550" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
@@ -29096,7 +29097,7 @@
       <c r="AN550" s="1"/>
       <c r="AO550" s="1"/>
     </row>
-    <row r="551" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
       <c r="C551" s="1"/>
@@ -29139,7 +29140,7 @@
       <c r="AN551" s="1"/>
       <c r="AO551" s="1"/>
     </row>
-    <row r="552" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
@@ -29182,7 +29183,7 @@
       <c r="AN552" s="1"/>
       <c r="AO552" s="1"/>
     </row>
-    <row r="553" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
@@ -29225,7 +29226,7 @@
       <c r="AN553" s="1"/>
       <c r="AO553" s="1"/>
     </row>
-    <row r="554" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
@@ -29268,7 +29269,7 @@
       <c r="AN554" s="1"/>
       <c r="AO554" s="1"/>
     </row>
-    <row r="555" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A555" s="1"/>
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
@@ -29311,7 +29312,7 @@
       <c r="AN555" s="1"/>
       <c r="AO555" s="1"/>
     </row>
-    <row r="556" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A556" s="1"/>
       <c r="B556" s="1"/>
       <c r="C556" s="1"/>
@@ -29354,7 +29355,7 @@
       <c r="AN556" s="1"/>
       <c r="AO556" s="1"/>
     </row>
-    <row r="557" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
@@ -29397,7 +29398,7 @@
       <c r="AN557" s="1"/>
       <c r="AO557" s="1"/>
     </row>
-    <row r="558" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
@@ -29440,7 +29441,7 @@
       <c r="AN558" s="1"/>
       <c r="AO558" s="1"/>
     </row>
-    <row r="559" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
@@ -29483,7 +29484,7 @@
       <c r="AN559" s="1"/>
       <c r="AO559" s="1"/>
     </row>
-    <row r="560" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
@@ -29526,7 +29527,7 @@
       <c r="AN560" s="1"/>
       <c r="AO560" s="1"/>
     </row>
-    <row r="561" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A561" s="1"/>
       <c r="B561" s="1"/>
       <c r="C561" s="1"/>
@@ -29569,7 +29570,7 @@
       <c r="AN561" s="1"/>
       <c r="AO561" s="1"/>
     </row>
-    <row r="562" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A562" s="1"/>
       <c r="B562" s="1"/>
       <c r="C562" s="1"/>
@@ -29612,7 +29613,7 @@
       <c r="AN562" s="1"/>
       <c r="AO562" s="1"/>
     </row>
-    <row r="563" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
@@ -29655,7 +29656,7 @@
       <c r="AN563" s="1"/>
       <c r="AO563" s="1"/>
     </row>
-    <row r="564" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
@@ -29698,7 +29699,7 @@
       <c r="AN564" s="1"/>
       <c r="AO564" s="1"/>
     </row>
-    <row r="565" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
@@ -29741,7 +29742,7 @@
       <c r="AN565" s="1"/>
       <c r="AO565" s="1"/>
     </row>
-    <row r="566" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
@@ -29784,7 +29785,7 @@
       <c r="AN566" s="1"/>
       <c r="AO566" s="1"/>
     </row>
-    <row r="567" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
@@ -29827,7 +29828,7 @@
       <c r="AN567" s="1"/>
       <c r="AO567" s="1"/>
     </row>
-    <row r="568" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
@@ -29870,7 +29871,7 @@
       <c r="AN568" s="1"/>
       <c r="AO568" s="1"/>
     </row>
-    <row r="569" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
@@ -29913,7 +29914,7 @@
       <c r="AN569" s="1"/>
       <c r="AO569" s="1"/>
     </row>
-    <row r="570" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
@@ -29956,7 +29957,7 @@
       <c r="AN570" s="1"/>
       <c r="AO570" s="1"/>
     </row>
-    <row r="571" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
@@ -29999,7 +30000,7 @@
       <c r="AN571" s="1"/>
       <c r="AO571" s="1"/>
     </row>
-    <row r="572" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
@@ -30042,7 +30043,7 @@
       <c r="AN572" s="1"/>
       <c r="AO572" s="1"/>
     </row>
-    <row r="573" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
@@ -30085,7 +30086,7 @@
       <c r="AN573" s="1"/>
       <c r="AO573" s="1"/>
     </row>
-    <row r="574" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
@@ -30128,7 +30129,7 @@
       <c r="AN574" s="1"/>
       <c r="AO574" s="1"/>
     </row>
-    <row r="575" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
@@ -30171,7 +30172,7 @@
       <c r="AN575" s="1"/>
       <c r="AO575" s="1"/>
     </row>
-    <row r="576" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
@@ -30214,7 +30215,7 @@
       <c r="AN576" s="1"/>
       <c r="AO576" s="1"/>
     </row>
-    <row r="577" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
@@ -30257,7 +30258,7 @@
       <c r="AN577" s="1"/>
       <c r="AO577" s="1"/>
     </row>
-    <row r="578" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
@@ -30300,7 +30301,7 @@
       <c r="AN578" s="1"/>
       <c r="AO578" s="1"/>
     </row>
-    <row r="579" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
@@ -30343,7 +30344,7 @@
       <c r="AN579" s="1"/>
       <c r="AO579" s="1"/>
     </row>
-    <row r="580" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
@@ -30386,7 +30387,7 @@
       <c r="AN580" s="1"/>
       <c r="AO580" s="1"/>
     </row>
-    <row r="581" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
@@ -30429,7 +30430,7 @@
       <c r="AN581" s="1"/>
       <c r="AO581" s="1"/>
     </row>
-    <row r="582" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
@@ -30472,7 +30473,7 @@
       <c r="AN582" s="1"/>
       <c r="AO582" s="1"/>
     </row>
-    <row r="583" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
@@ -30515,7 +30516,7 @@
       <c r="AN583" s="1"/>
       <c r="AO583" s="1"/>
     </row>
-    <row r="584" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
@@ -30558,7 +30559,7 @@
       <c r="AN584" s="1"/>
       <c r="AO584" s="1"/>
     </row>
-    <row r="585" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
@@ -30601,7 +30602,7 @@
       <c r="AN585" s="1"/>
       <c r="AO585" s="1"/>
     </row>
-    <row r="586" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
@@ -30644,7 +30645,7 @@
       <c r="AN586" s="1"/>
       <c r="AO586" s="1"/>
     </row>
-    <row r="587" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
@@ -30687,7 +30688,7 @@
       <c r="AN587" s="1"/>
       <c r="AO587" s="1"/>
     </row>
-    <row r="588" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
@@ -30730,7 +30731,7 @@
       <c r="AN588" s="1"/>
       <c r="AO588" s="1"/>
     </row>
-    <row r="589" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
@@ -30773,7 +30774,7 @@
       <c r="AN589" s="1"/>
       <c r="AO589" s="1"/>
     </row>
-    <row r="590" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
       <c r="C590" s="1"/>
@@ -30816,7 +30817,7 @@
       <c r="AN590" s="1"/>
       <c r="AO590" s="1"/>
     </row>
-    <row r="591" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
@@ -30859,7 +30860,7 @@
       <c r="AN591" s="1"/>
       <c r="AO591" s="1"/>
     </row>
-    <row r="592" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -30902,7 +30903,7 @@
       <c r="AN592" s="1"/>
       <c r="AO592" s="1"/>
     </row>
-    <row r="593" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -30945,7 +30946,7 @@
       <c r="AN593" s="1"/>
       <c r="AO593" s="1"/>
     </row>
-    <row r="594" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -30988,7 +30989,7 @@
       <c r="AN594" s="1"/>
       <c r="AO594" s="1"/>
     </row>
-    <row r="595" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
@@ -31031,7 +31032,7 @@
       <c r="AN595" s="1"/>
       <c r="AO595" s="1"/>
     </row>
-    <row r="596" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
@@ -31074,7 +31075,7 @@
       <c r="AN596" s="1"/>
       <c r="AO596" s="1"/>
     </row>
-    <row r="597" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A597" s="1"/>
       <c r="B597" s="1"/>
       <c r="C597" s="1"/>
@@ -31117,7 +31118,7 @@
       <c r="AN597" s="1"/>
       <c r="AO597" s="1"/>
     </row>
-    <row r="598" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A598" s="1"/>
       <c r="B598" s="1"/>
       <c r="C598" s="1"/>
@@ -31160,7 +31161,7 @@
       <c r="AN598" s="1"/>
       <c r="AO598" s="1"/>
     </row>
-    <row r="599" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A599" s="1"/>
       <c r="B599" s="1"/>
       <c r="C599" s="1"/>
@@ -31203,7 +31204,7 @@
       <c r="AN599" s="1"/>
       <c r="AO599" s="1"/>
     </row>
-    <row r="600" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A600" s="1"/>
       <c r="B600" s="1"/>
       <c r="C600" s="1"/>
@@ -31246,7 +31247,7 @@
       <c r="AN600" s="1"/>
       <c r="AO600" s="1"/>
     </row>
-    <row r="601" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A601" s="1"/>
       <c r="B601" s="1"/>
       <c r="C601" s="1"/>
@@ -31289,7 +31290,7 @@
       <c r="AN601" s="1"/>
       <c r="AO601" s="1"/>
     </row>
-    <row r="602" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
       <c r="C602" s="1"/>
@@ -31332,7 +31333,7 @@
       <c r="AN602" s="1"/>
       <c r="AO602" s="1"/>
     </row>
-    <row r="603" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A603" s="1"/>
       <c r="B603" s="1"/>
       <c r="C603" s="1"/>
@@ -31375,7 +31376,7 @@
       <c r="AN603" s="1"/>
       <c r="AO603" s="1"/>
     </row>
-    <row r="604" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
       <c r="C604" s="1"/>
@@ -31418,7 +31419,7 @@
       <c r="AN604" s="1"/>
       <c r="AO604" s="1"/>
     </row>
-    <row r="605" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
       <c r="C605" s="1"/>
@@ -31461,7 +31462,7 @@
       <c r="AN605" s="1"/>
       <c r="AO605" s="1"/>
     </row>
-    <row r="606" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
@@ -31504,7 +31505,7 @@
       <c r="AN606" s="1"/>
       <c r="AO606" s="1"/>
     </row>
-    <row r="607" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A607" s="1"/>
       <c r="B607" s="1"/>
       <c r="C607" s="1"/>
@@ -31547,7 +31548,7 @@
       <c r="AN607" s="1"/>
       <c r="AO607" s="1"/>
     </row>
-    <row r="608" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A608" s="1"/>
       <c r="B608" s="1"/>
       <c r="C608" s="1"/>
@@ -31590,7 +31591,7 @@
       <c r="AN608" s="1"/>
       <c r="AO608" s="1"/>
     </row>
-    <row r="609" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
@@ -31633,7 +31634,7 @@
       <c r="AN609" s="1"/>
       <c r="AO609" s="1"/>
     </row>
-    <row r="610" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
@@ -31676,7 +31677,7 @@
       <c r="AN610" s="1"/>
       <c r="AO610" s="1"/>
     </row>
-    <row r="611" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
@@ -31719,7 +31720,7 @@
       <c r="AN611" s="1"/>
       <c r="AO611" s="1"/>
     </row>
-    <row r="612" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A612" s="1"/>
       <c r="B612" s="1"/>
       <c r="C612" s="1"/>
@@ -31762,7 +31763,7 @@
       <c r="AN612" s="1"/>
       <c r="AO612" s="1"/>
     </row>
-    <row r="613" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A613" s="1"/>
       <c r="B613" s="1"/>
       <c r="C613" s="1"/>
@@ -31805,7 +31806,7 @@
       <c r="AN613" s="1"/>
       <c r="AO613" s="1"/>
     </row>
-    <row r="614" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A614" s="1"/>
       <c r="B614" s="1"/>
       <c r="C614" s="1"/>
@@ -31848,7 +31849,7 @@
       <c r="AN614" s="1"/>
       <c r="AO614" s="1"/>
     </row>
-    <row r="615" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A615" s="1"/>
       <c r="B615" s="1"/>
       <c r="C615" s="1"/>
@@ -31891,7 +31892,7 @@
       <c r="AN615" s="1"/>
       <c r="AO615" s="1"/>
     </row>
-    <row r="616" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A616" s="1"/>
       <c r="B616" s="1"/>
       <c r="C616" s="1"/>
@@ -31934,7 +31935,7 @@
       <c r="AN616" s="1"/>
       <c r="AO616" s="1"/>
     </row>
-    <row r="617" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A617" s="1"/>
       <c r="B617" s="1"/>
       <c r="C617" s="1"/>
@@ -31977,7 +31978,7 @@
       <c r="AN617" s="1"/>
       <c r="AO617" s="1"/>
     </row>
-    <row r="618" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
       <c r="C618" s="1"/>
@@ -32020,7 +32021,7 @@
       <c r="AN618" s="1"/>
       <c r="AO618" s="1"/>
     </row>
-    <row r="619" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
       <c r="C619" s="1"/>
@@ -32063,7 +32064,7 @@
       <c r="AN619" s="1"/>
       <c r="AO619" s="1"/>
     </row>
-    <row r="620" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A620" s="1"/>
       <c r="B620" s="1"/>
       <c r="C620" s="1"/>
@@ -32106,7 +32107,7 @@
       <c r="AN620" s="1"/>
       <c r="AO620" s="1"/>
     </row>
-    <row r="621" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A621" s="1"/>
       <c r="B621" s="1"/>
       <c r="C621" s="1"/>
@@ -32149,7 +32150,7 @@
       <c r="AN621" s="1"/>
       <c r="AO621" s="1"/>
     </row>
-    <row r="622" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A622" s="1"/>
       <c r="B622" s="1"/>
       <c r="C622" s="1"/>
@@ -32192,7 +32193,7 @@
       <c r="AN622" s="1"/>
       <c r="AO622" s="1"/>
     </row>
-    <row r="623" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A623" s="1"/>
       <c r="B623" s="1"/>
       <c r="C623" s="1"/>
@@ -32235,7 +32236,7 @@
       <c r="AN623" s="1"/>
       <c r="AO623" s="1"/>
     </row>
-    <row r="624" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A624" s="1"/>
       <c r="B624" s="1"/>
       <c r="C624" s="1"/>
@@ -32278,7 +32279,7 @@
       <c r="AN624" s="1"/>
       <c r="AO624" s="1"/>
     </row>
-    <row r="625" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A625" s="1"/>
       <c r="B625" s="1"/>
       <c r="C625" s="1"/>
@@ -32321,7 +32322,7 @@
       <c r="AN625" s="1"/>
       <c r="AO625" s="1"/>
     </row>
-    <row r="626" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A626" s="1"/>
       <c r="B626" s="1"/>
       <c r="C626" s="1"/>
@@ -32364,7 +32365,7 @@
       <c r="AN626" s="1"/>
       <c r="AO626" s="1"/>
     </row>
-    <row r="627" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A627" s="1"/>
       <c r="B627" s="1"/>
       <c r="C627" s="1"/>
@@ -32407,7 +32408,7 @@
       <c r="AN627" s="1"/>
       <c r="AO627" s="1"/>
     </row>
-    <row r="628" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A628" s="1"/>
       <c r="B628" s="1"/>
       <c r="C628" s="1"/>
@@ -32450,7 +32451,7 @@
       <c r="AN628" s="1"/>
       <c r="AO628" s="1"/>
     </row>
-    <row r="629" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A629" s="1"/>
       <c r="B629" s="1"/>
       <c r="C629" s="1"/>
@@ -32493,7 +32494,7 @@
       <c r="AN629" s="1"/>
       <c r="AO629" s="1"/>
     </row>
-    <row r="630" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A630" s="1"/>
       <c r="B630" s="1"/>
       <c r="C630" s="1"/>
@@ -32536,7 +32537,7 @@
       <c r="AN630" s="1"/>
       <c r="AO630" s="1"/>
     </row>
-    <row r="631" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A631" s="1"/>
       <c r="B631" s="1"/>
       <c r="C631" s="1"/>
@@ -32579,7 +32580,7 @@
       <c r="AN631" s="1"/>
       <c r="AO631" s="1"/>
     </row>
-    <row r="632" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="1"/>
@@ -32622,7 +32623,7 @@
       <c r="AN632" s="1"/>
       <c r="AO632" s="1"/>
     </row>
-    <row r="633" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A633" s="1"/>
       <c r="B633" s="1"/>
       <c r="C633" s="1"/>
@@ -32665,7 +32666,7 @@
       <c r="AN633" s="1"/>
       <c r="AO633" s="1"/>
     </row>
-    <row r="634" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A634" s="1"/>
       <c r="B634" s="1"/>
       <c r="C634" s="1"/>
@@ -32708,7 +32709,7 @@
       <c r="AN634" s="1"/>
       <c r="AO634" s="1"/>
     </row>
-    <row r="635" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A635" s="1"/>
       <c r="B635" s="1"/>
       <c r="C635" s="1"/>
@@ -32751,7 +32752,7 @@
       <c r="AN635" s="1"/>
       <c r="AO635" s="1"/>
     </row>
-    <row r="636" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A636" s="1"/>
       <c r="B636" s="1"/>
       <c r="C636" s="1"/>
@@ -32794,7 +32795,7 @@
       <c r="AN636" s="1"/>
       <c r="AO636" s="1"/>
     </row>
-    <row r="637" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A637" s="1"/>
       <c r="B637" s="1"/>
       <c r="C637" s="1"/>
@@ -32837,7 +32838,7 @@
       <c r="AN637" s="1"/>
       <c r="AO637" s="1"/>
     </row>
-    <row r="638" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A638" s="1"/>
       <c r="B638" s="1"/>
       <c r="C638" s="1"/>
@@ -32880,7 +32881,7 @@
       <c r="AN638" s="1"/>
       <c r="AO638" s="1"/>
     </row>
-    <row r="639" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A639" s="1"/>
       <c r="B639" s="1"/>
       <c r="C639" s="1"/>
@@ -32923,7 +32924,7 @@
       <c r="AN639" s="1"/>
       <c r="AO639" s="1"/>
     </row>
-    <row r="640" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A640" s="1"/>
       <c r="B640" s="1"/>
       <c r="C640" s="1"/>
@@ -32966,7 +32967,7 @@
       <c r="AN640" s="1"/>
       <c r="AO640" s="1"/>
     </row>
-    <row r="641" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A641" s="1"/>
       <c r="B641" s="1"/>
       <c r="C641" s="1"/>
@@ -33009,7 +33010,7 @@
       <c r="AN641" s="1"/>
       <c r="AO641" s="1"/>
     </row>
-    <row r="642" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A642" s="1"/>
       <c r="B642" s="1"/>
       <c r="C642" s="1"/>
@@ -33052,7 +33053,7 @@
       <c r="AN642" s="1"/>
       <c r="AO642" s="1"/>
     </row>
-    <row r="643" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A643" s="1"/>
       <c r="B643" s="1"/>
       <c r="C643" s="1"/>
@@ -33095,7 +33096,7 @@
       <c r="AN643" s="1"/>
       <c r="AO643" s="1"/>
     </row>
-    <row r="644" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A644" s="1"/>
       <c r="B644" s="1"/>
       <c r="C644" s="1"/>
@@ -33138,7 +33139,7 @@
       <c r="AN644" s="1"/>
       <c r="AO644" s="1"/>
     </row>
-    <row r="645" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A645" s="1"/>
       <c r="B645" s="1"/>
       <c r="C645" s="1"/>
@@ -33181,7 +33182,7 @@
       <c r="AN645" s="1"/>
       <c r="AO645" s="1"/>
     </row>
-    <row r="646" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A646" s="1"/>
       <c r="B646" s="1"/>
       <c r="C646" s="1"/>
@@ -33224,7 +33225,7 @@
       <c r="AN646" s="1"/>
       <c r="AO646" s="1"/>
     </row>
-    <row r="647" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A647" s="1"/>
       <c r="B647" s="1"/>
       <c r="C647" s="1"/>
@@ -33267,7 +33268,7 @@
       <c r="AN647" s="1"/>
       <c r="AO647" s="1"/>
     </row>
-    <row r="648" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A648" s="1"/>
       <c r="B648" s="1"/>
       <c r="C648" s="1"/>
@@ -33310,7 +33311,7 @@
       <c r="AN648" s="1"/>
       <c r="AO648" s="1"/>
     </row>
-    <row r="649" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A649" s="1"/>
       <c r="B649" s="1"/>
       <c r="C649" s="1"/>
@@ -33353,7 +33354,7 @@
       <c r="AN649" s="1"/>
       <c r="AO649" s="1"/>
     </row>
-    <row r="650" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A650" s="1"/>
       <c r="B650" s="1"/>
       <c r="C650" s="1"/>
@@ -33396,7 +33397,7 @@
       <c r="AN650" s="1"/>
       <c r="AO650" s="1"/>
     </row>
-    <row r="651" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A651" s="1"/>
       <c r="B651" s="1"/>
       <c r="C651" s="1"/>
@@ -33439,7 +33440,7 @@
       <c r="AN651" s="1"/>
       <c r="AO651" s="1"/>
     </row>
-    <row r="652" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A652" s="1"/>
       <c r="B652" s="1"/>
       <c r="C652" s="1"/>
@@ -33482,7 +33483,7 @@
       <c r="AN652" s="1"/>
       <c r="AO652" s="1"/>
     </row>
-    <row r="653" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A653" s="1"/>
       <c r="B653" s="1"/>
       <c r="C653" s="1"/>
@@ -33525,7 +33526,7 @@
       <c r="AN653" s="1"/>
       <c r="AO653" s="1"/>
     </row>
-    <row r="654" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A654" s="1"/>
       <c r="B654" s="1"/>
       <c r="C654" s="1"/>
@@ -33568,7 +33569,7 @@
       <c r="AN654" s="1"/>
       <c r="AO654" s="1"/>
     </row>
-    <row r="655" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A655" s="1"/>
       <c r="B655" s="1"/>
       <c r="C655" s="1"/>
@@ -33611,7 +33612,7 @@
       <c r="AN655" s="1"/>
       <c r="AO655" s="1"/>
     </row>
-    <row r="656" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A656" s="1"/>
       <c r="B656" s="1"/>
       <c r="C656" s="1"/>
@@ -33654,7 +33655,7 @@
       <c r="AN656" s="1"/>
       <c r="AO656" s="1"/>
     </row>
-    <row r="657" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A657" s="1"/>
       <c r="B657" s="1"/>
       <c r="C657" s="1"/>
@@ -33697,7 +33698,7 @@
       <c r="AN657" s="1"/>
       <c r="AO657" s="1"/>
     </row>
-    <row r="658" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="1"/>
@@ -33740,7 +33741,7 @@
       <c r="AN658" s="1"/>
       <c r="AO658" s="1"/>
     </row>
-    <row r="659" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A659" s="1"/>
       <c r="B659" s="1"/>
       <c r="C659" s="1"/>
@@ -33783,7 +33784,7 @@
       <c r="AN659" s="1"/>
       <c r="AO659" s="1"/>
     </row>
-    <row r="660" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A660" s="1"/>
       <c r="B660" s="1"/>
       <c r="C660" s="1"/>
@@ -33826,7 +33827,7 @@
       <c r="AN660" s="1"/>
       <c r="AO660" s="1"/>
     </row>
-    <row r="661" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A661" s="1"/>
       <c r="B661" s="1"/>
       <c r="C661" s="1"/>
@@ -33869,7 +33870,7 @@
       <c r="AN661" s="1"/>
       <c r="AO661" s="1"/>
     </row>
-    <row r="662" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A662" s="1"/>
       <c r="B662" s="1"/>
       <c r="C662" s="1"/>
@@ -33912,7 +33913,7 @@
       <c r="AN662" s="1"/>
       <c r="AO662" s="1"/>
     </row>
-    <row r="663" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A663" s="1"/>
       <c r="B663" s="1"/>
       <c r="C663" s="1"/>
@@ -33955,7 +33956,7 @@
       <c r="AN663" s="1"/>
       <c r="AO663" s="1"/>
     </row>
-    <row r="664" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A664" s="1"/>
       <c r="B664" s="1"/>
       <c r="C664" s="1"/>
@@ -33998,7 +33999,7 @@
       <c r="AN664" s="1"/>
       <c r="AO664" s="1"/>
     </row>
-    <row r="665" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A665" s="1"/>
       <c r="B665" s="1"/>
       <c r="C665" s="1"/>
@@ -34041,7 +34042,7 @@
       <c r="AN665" s="1"/>
       <c r="AO665" s="1"/>
     </row>
-    <row r="666" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A666" s="1"/>
       <c r="B666" s="1"/>
       <c r="C666" s="1"/>
@@ -34084,7 +34085,7 @@
       <c r="AN666" s="1"/>
       <c r="AO666" s="1"/>
     </row>
-    <row r="667" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A667" s="1"/>
       <c r="B667" s="1"/>
       <c r="C667" s="1"/>
@@ -34127,7 +34128,7 @@
       <c r="AN667" s="1"/>
       <c r="AO667" s="1"/>
     </row>
-    <row r="668" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A668" s="1"/>
       <c r="B668" s="1"/>
       <c r="C668" s="1"/>
@@ -34170,7 +34171,7 @@
       <c r="AN668" s="1"/>
       <c r="AO668" s="1"/>
     </row>
-    <row r="669" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A669" s="1"/>
       <c r="B669" s="1"/>
       <c r="C669" s="1"/>
@@ -34213,7 +34214,7 @@
       <c r="AN669" s="1"/>
       <c r="AO669" s="1"/>
     </row>
-    <row r="670" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A670" s="1"/>
       <c r="B670" s="1"/>
       <c r="C670" s="1"/>
@@ -34256,7 +34257,7 @@
       <c r="AN670" s="1"/>
       <c r="AO670" s="1"/>
     </row>
-    <row r="671" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A671" s="1"/>
       <c r="B671" s="1"/>
       <c r="C671" s="1"/>
@@ -34299,7 +34300,7 @@
       <c r="AN671" s="1"/>
       <c r="AO671" s="1"/>
     </row>
-    <row r="672" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A672" s="1"/>
       <c r="B672" s="1"/>
       <c r="C672" s="1"/>
@@ -34342,7 +34343,7 @@
       <c r="AN672" s="1"/>
       <c r="AO672" s="1"/>
     </row>
-    <row r="673" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A673" s="1"/>
       <c r="B673" s="1"/>
       <c r="C673" s="1"/>
@@ -34385,7 +34386,7 @@
       <c r="AN673" s="1"/>
       <c r="AO673" s="1"/>
     </row>
-    <row r="674" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A674" s="1"/>
       <c r="B674" s="1"/>
       <c r="C674" s="1"/>
@@ -34428,7 +34429,7 @@
       <c r="AN674" s="1"/>
       <c r="AO674" s="1"/>
     </row>
-    <row r="675" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A675" s="1"/>
       <c r="B675" s="1"/>
       <c r="C675" s="1"/>
@@ -34471,7 +34472,7 @@
       <c r="AN675" s="1"/>
       <c r="AO675" s="1"/>
     </row>
-    <row r="676" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A676" s="1"/>
       <c r="B676" s="1"/>
       <c r="C676" s="1"/>
@@ -34514,7 +34515,7 @@
       <c r="AN676" s="1"/>
       <c r="AO676" s="1"/>
     </row>
-    <row r="677" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A677" s="1"/>
       <c r="B677" s="1"/>
       <c r="C677" s="1"/>
@@ -34557,7 +34558,7 @@
       <c r="AN677" s="1"/>
       <c r="AO677" s="1"/>
     </row>
-    <row r="678" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A678" s="1"/>
       <c r="B678" s="1"/>
       <c r="C678" s="1"/>
@@ -34600,7 +34601,7 @@
       <c r="AN678" s="1"/>
       <c r="AO678" s="1"/>
     </row>
-    <row r="679" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A679" s="1"/>
       <c r="B679" s="1"/>
       <c r="C679" s="1"/>
@@ -34643,7 +34644,7 @@
       <c r="AN679" s="1"/>
       <c r="AO679" s="1"/>
     </row>
-    <row r="680" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A680" s="1"/>
       <c r="B680" s="1"/>
       <c r="C680" s="1"/>
@@ -34686,7 +34687,7 @@
       <c r="AN680" s="1"/>
       <c r="AO680" s="1"/>
     </row>
-    <row r="681" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A681" s="1"/>
       <c r="B681" s="1"/>
       <c r="C681" s="1"/>
@@ -34729,7 +34730,7 @@
       <c r="AN681" s="1"/>
       <c r="AO681" s="1"/>
     </row>
-    <row r="682" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A682" s="1"/>
       <c r="B682" s="1"/>
       <c r="C682" s="1"/>
@@ -34772,7 +34773,7 @@
       <c r="AN682" s="1"/>
       <c r="AO682" s="1"/>
     </row>
-    <row r="683" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A683" s="1"/>
       <c r="B683" s="1"/>
       <c r="C683" s="1"/>
@@ -34815,7 +34816,7 @@
       <c r="AN683" s="1"/>
       <c r="AO683" s="1"/>
     </row>
-    <row r="684" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="1"/>
@@ -34858,7 +34859,7 @@
       <c r="AN684" s="1"/>
       <c r="AO684" s="1"/>
     </row>
-    <row r="685" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A685" s="1"/>
       <c r="B685" s="1"/>
       <c r="C685" s="1"/>
@@ -34901,7 +34902,7 @@
       <c r="AN685" s="1"/>
       <c r="AO685" s="1"/>
     </row>
-    <row r="686" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A686" s="1"/>
       <c r="B686" s="1"/>
       <c r="C686" s="1"/>
@@ -34944,7 +34945,7 @@
       <c r="AN686" s="1"/>
       <c r="AO686" s="1"/>
     </row>
-    <row r="687" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A687" s="1"/>
       <c r="B687" s="1"/>
       <c r="C687" s="1"/>
@@ -34987,7 +34988,7 @@
       <c r="AN687" s="1"/>
       <c r="AO687" s="1"/>
     </row>
-    <row r="688" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A688" s="1"/>
       <c r="B688" s="1"/>
       <c r="C688" s="1"/>
@@ -35030,7 +35031,7 @@
       <c r="AN688" s="1"/>
       <c r="AO688" s="1"/>
     </row>
-    <row r="689" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A689" s="1"/>
       <c r="B689" s="1"/>
       <c r="C689" s="1"/>
@@ -35073,7 +35074,7 @@
       <c r="AN689" s="1"/>
       <c r="AO689" s="1"/>
     </row>
-    <row r="690" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A690" s="1"/>
       <c r="B690" s="1"/>
       <c r="C690" s="1"/>
@@ -35116,7 +35117,7 @@
       <c r="AN690" s="1"/>
       <c r="AO690" s="1"/>
     </row>
-    <row r="691" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A691" s="1"/>
       <c r="B691" s="1"/>
       <c r="C691" s="1"/>
@@ -35159,7 +35160,7 @@
       <c r="AN691" s="1"/>
       <c r="AO691" s="1"/>
     </row>
-    <row r="692" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A692" s="1"/>
       <c r="B692" s="1"/>
       <c r="C692" s="1"/>
@@ -35202,7 +35203,7 @@
       <c r="AN692" s="1"/>
       <c r="AO692" s="1"/>
     </row>
-    <row r="693" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A693" s="1"/>
       <c r="B693" s="1"/>
       <c r="C693" s="1"/>
@@ -35245,7 +35246,7 @@
       <c r="AN693" s="1"/>
       <c r="AO693" s="1"/>
     </row>
-    <row r="694" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A694" s="1"/>
       <c r="B694" s="1"/>
       <c r="C694" s="1"/>
@@ -35288,7 +35289,7 @@
       <c r="AN694" s="1"/>
       <c r="AO694" s="1"/>
     </row>
-    <row r="695" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A695" s="1"/>
       <c r="B695" s="1"/>
       <c r="C695" s="1"/>
@@ -35331,7 +35332,7 @@
       <c r="AN695" s="1"/>
       <c r="AO695" s="1"/>
     </row>
-    <row r="696" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A696" s="1"/>
       <c r="B696" s="1"/>
       <c r="C696" s="1"/>
@@ -35374,7 +35375,7 @@
       <c r="AN696" s="1"/>
       <c r="AO696" s="1"/>
     </row>
-    <row r="697" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A697" s="1"/>
       <c r="B697" s="1"/>
       <c r="C697" s="1"/>
@@ -35417,7 +35418,7 @@
       <c r="AN697" s="1"/>
       <c r="AO697" s="1"/>
     </row>
-    <row r="698" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A698" s="1"/>
       <c r="B698" s="1"/>
       <c r="C698" s="1"/>
@@ -35460,7 +35461,7 @@
       <c r="AN698" s="1"/>
       <c r="AO698" s="1"/>
     </row>
-    <row r="699" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A699" s="1"/>
       <c r="B699" s="1"/>
       <c r="C699" s="1"/>
@@ -35503,7 +35504,7 @@
       <c r="AN699" s="1"/>
       <c r="AO699" s="1"/>
     </row>
-    <row r="700" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A700" s="1"/>
       <c r="B700" s="1"/>
       <c r="C700" s="1"/>
@@ -35546,7 +35547,7 @@
       <c r="AN700" s="1"/>
       <c r="AO700" s="1"/>
     </row>
-    <row r="701" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A701" s="1"/>
       <c r="B701" s="1"/>
       <c r="C701" s="1"/>
@@ -35589,7 +35590,7 @@
       <c r="AN701" s="1"/>
       <c r="AO701" s="1"/>
     </row>
-    <row r="702" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A702" s="1"/>
       <c r="B702" s="1"/>
       <c r="C702" s="1"/>
@@ -35632,7 +35633,7 @@
       <c r="AN702" s="1"/>
       <c r="AO702" s="1"/>
     </row>
-    <row r="703" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A703" s="1"/>
       <c r="B703" s="1"/>
       <c r="C703" s="1"/>
@@ -35675,7 +35676,7 @@
       <c r="AN703" s="1"/>
       <c r="AO703" s="1"/>
     </row>
-    <row r="704" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A704" s="1"/>
       <c r="B704" s="1"/>
       <c r="C704" s="1"/>
@@ -35718,7 +35719,7 @@
       <c r="AN704" s="1"/>
       <c r="AO704" s="1"/>
     </row>
-    <row r="705" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A705" s="1"/>
       <c r="B705" s="1"/>
       <c r="C705" s="1"/>
@@ -35761,7 +35762,7 @@
       <c r="AN705" s="1"/>
       <c r="AO705" s="1"/>
     </row>
-    <row r="706" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A706" s="1"/>
       <c r="B706" s="1"/>
       <c r="C706" s="1"/>
@@ -35804,7 +35805,7 @@
       <c r="AN706" s="1"/>
       <c r="AO706" s="1"/>
     </row>
-    <row r="707" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A707" s="1"/>
       <c r="B707" s="1"/>
       <c r="C707" s="1"/>
@@ -35847,7 +35848,7 @@
       <c r="AN707" s="1"/>
       <c r="AO707" s="1"/>
     </row>
-    <row r="708" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A708" s="1"/>
       <c r="B708" s="1"/>
       <c r="C708" s="1"/>
@@ -35890,7 +35891,7 @@
       <c r="AN708" s="1"/>
       <c r="AO708" s="1"/>
     </row>
-    <row r="709" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A709" s="1"/>
       <c r="B709" s="1"/>
       <c r="C709" s="1"/>
@@ -35933,7 +35934,7 @@
       <c r="AN709" s="1"/>
       <c r="AO709" s="1"/>
     </row>
-    <row r="710" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A710" s="1"/>
       <c r="B710" s="1"/>
       <c r="C710" s="1"/>
@@ -35976,7 +35977,7 @@
       <c r="AN710" s="1"/>
       <c r="AO710" s="1"/>
     </row>
-    <row r="711" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A711" s="1"/>
       <c r="B711" s="1"/>
       <c r="C711" s="1"/>
@@ -36019,7 +36020,7 @@
       <c r="AN711" s="1"/>
       <c r="AO711" s="1"/>
     </row>
-    <row r="712" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A712" s="1"/>
       <c r="B712" s="1"/>
       <c r="C712" s="1"/>
@@ -36062,7 +36063,7 @@
       <c r="AN712" s="1"/>
       <c r="AO712" s="1"/>
     </row>
-    <row r="713" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A713" s="1"/>
       <c r="B713" s="1"/>
       <c r="C713" s="1"/>
@@ -36105,7 +36106,7 @@
       <c r="AN713" s="1"/>
       <c r="AO713" s="1"/>
     </row>
-    <row r="714" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A714" s="1"/>
       <c r="B714" s="1"/>
       <c r="C714" s="1"/>
@@ -36148,7 +36149,7 @@
       <c r="AN714" s="1"/>
       <c r="AO714" s="1"/>
     </row>
-    <row r="715" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A715" s="1"/>
       <c r="B715" s="1"/>
       <c r="C715" s="1"/>
@@ -36191,7 +36192,7 @@
       <c r="AN715" s="1"/>
       <c r="AO715" s="1"/>
     </row>
-    <row r="716" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A716" s="1"/>
       <c r="B716" s="1"/>
       <c r="C716" s="1"/>
@@ -36234,7 +36235,7 @@
       <c r="AN716" s="1"/>
       <c r="AO716" s="1"/>
     </row>
-    <row r="717" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A717" s="1"/>
       <c r="B717" s="1"/>
       <c r="C717" s="1"/>
@@ -36277,7 +36278,7 @@
       <c r="AN717" s="1"/>
       <c r="AO717" s="1"/>
     </row>
-    <row r="718" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A718" s="1"/>
       <c r="B718" s="1"/>
       <c r="C718" s="1"/>
@@ -36320,7 +36321,7 @@
       <c r="AN718" s="1"/>
       <c r="AO718" s="1"/>
     </row>
-    <row r="719" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A719" s="1"/>
       <c r="B719" s="1"/>
       <c r="C719" s="1"/>
@@ -36363,7 +36364,7 @@
       <c r="AN719" s="1"/>
       <c r="AO719" s="1"/>
     </row>
-    <row r="720" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A720" s="1"/>
       <c r="B720" s="1"/>
       <c r="C720" s="1"/>
@@ -36406,7 +36407,7 @@
       <c r="AN720" s="1"/>
       <c r="AO720" s="1"/>
     </row>
-    <row r="721" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A721" s="1"/>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
@@ -36449,7 +36450,7 @@
       <c r="AN721" s="1"/>
       <c r="AO721" s="1"/>
     </row>
-    <row r="722" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A722" s="1"/>
       <c r="B722" s="1"/>
       <c r="C722" s="1"/>
@@ -36492,7 +36493,7 @@
       <c r="AN722" s="1"/>
       <c r="AO722" s="1"/>
     </row>
-    <row r="723" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A723" s="1"/>
       <c r="B723" s="1"/>
       <c r="C723" s="1"/>
@@ -36535,7 +36536,7 @@
       <c r="AN723" s="1"/>
       <c r="AO723" s="1"/>
     </row>
-    <row r="724" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A724" s="1"/>
       <c r="B724" s="1"/>
       <c r="C724" s="1"/>
@@ -36578,7 +36579,7 @@
       <c r="AN724" s="1"/>
       <c r="AO724" s="1"/>
     </row>
-    <row r="725" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A725" s="1"/>
       <c r="B725" s="1"/>
       <c r="C725" s="1"/>
@@ -36621,7 +36622,7 @@
       <c r="AN725" s="1"/>
       <c r="AO725" s="1"/>
     </row>
-    <row r="726" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A726" s="1"/>
       <c r="B726" s="1"/>
       <c r="C726" s="1"/>
@@ -36664,7 +36665,7 @@
       <c r="AN726" s="1"/>
       <c r="AO726" s="1"/>
     </row>
-    <row r="727" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A727" s="1"/>
       <c r="B727" s="1"/>
       <c r="C727" s="1"/>
@@ -36707,7 +36708,7 @@
       <c r="AN727" s="1"/>
       <c r="AO727" s="1"/>
     </row>
-    <row r="728" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A728" s="1"/>
       <c r="B728" s="1"/>
       <c r="C728" s="1"/>
@@ -36750,7 +36751,7 @@
       <c r="AN728" s="1"/>
       <c r="AO728" s="1"/>
     </row>
-    <row r="729" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A729" s="1"/>
       <c r="B729" s="1"/>
       <c r="C729" s="1"/>
@@ -36793,7 +36794,7 @@
       <c r="AN729" s="1"/>
       <c r="AO729" s="1"/>
     </row>
-    <row r="730" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A730" s="1"/>
       <c r="B730" s="1"/>
       <c r="C730" s="1"/>
@@ -36836,7 +36837,7 @@
       <c r="AN730" s="1"/>
       <c r="AO730" s="1"/>
     </row>
-    <row r="731" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A731" s="1"/>
       <c r="B731" s="1"/>
       <c r="C731" s="1"/>
@@ -36879,7 +36880,7 @@
       <c r="AN731" s="1"/>
       <c r="AO731" s="1"/>
     </row>
-    <row r="732" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A732" s="1"/>
       <c r="B732" s="1"/>
       <c r="C732" s="1"/>
@@ -36922,7 +36923,7 @@
       <c r="AN732" s="1"/>
       <c r="AO732" s="1"/>
     </row>
-    <row r="733" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A733" s="1"/>
       <c r="B733" s="1"/>
       <c r="C733" s="1"/>
@@ -36965,7 +36966,7 @@
       <c r="AN733" s="1"/>
       <c r="AO733" s="1"/>
     </row>
-    <row r="734" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A734" s="1"/>
       <c r="B734" s="1"/>
       <c r="C734" s="1"/>
@@ -37008,7 +37009,7 @@
       <c r="AN734" s="1"/>
       <c r="AO734" s="1"/>
     </row>
-    <row r="735" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A735" s="1"/>
       <c r="B735" s="1"/>
       <c r="C735" s="1"/>
@@ -37051,7 +37052,7 @@
       <c r="AN735" s="1"/>
       <c r="AO735" s="1"/>
     </row>
-    <row r="736" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A736" s="1"/>
       <c r="B736" s="1"/>
       <c r="C736" s="1"/>
@@ -37094,7 +37095,7 @@
       <c r="AN736" s="1"/>
       <c r="AO736" s="1"/>
     </row>
-    <row r="737" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A737" s="1"/>
       <c r="B737" s="1"/>
       <c r="C737" s="1"/>
@@ -37137,7 +37138,7 @@
       <c r="AN737" s="1"/>
       <c r="AO737" s="1"/>
     </row>
-    <row r="738" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A738" s="1"/>
       <c r="B738" s="1"/>
       <c r="C738" s="1"/>
@@ -37180,7 +37181,7 @@
       <c r="AN738" s="1"/>
       <c r="AO738" s="1"/>
     </row>
-    <row r="739" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A739" s="1"/>
       <c r="B739" s="1"/>
       <c r="C739" s="1"/>
@@ -37223,7 +37224,7 @@
       <c r="AN739" s="1"/>
       <c r="AO739" s="1"/>
     </row>
-    <row r="740" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A740" s="1"/>
       <c r="B740" s="1"/>
       <c r="C740" s="1"/>
@@ -37266,7 +37267,7 @@
       <c r="AN740" s="1"/>
       <c r="AO740" s="1"/>
     </row>
-    <row r="741" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A741" s="1"/>
       <c r="B741" s="1"/>
       <c r="C741" s="1"/>
@@ -37309,7 +37310,7 @@
       <c r="AN741" s="1"/>
       <c r="AO741" s="1"/>
     </row>
-    <row r="742" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A742" s="1"/>
       <c r="B742" s="1"/>
       <c r="C742" s="1"/>
@@ -37352,7 +37353,7 @@
       <c r="AN742" s="1"/>
       <c r="AO742" s="1"/>
     </row>
-    <row r="743" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A743" s="1"/>
       <c r="B743" s="1"/>
       <c r="C743" s="1"/>
@@ -37395,7 +37396,7 @@
       <c r="AN743" s="1"/>
       <c r="AO743" s="1"/>
     </row>
-    <row r="744" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A744" s="1"/>
       <c r="B744" s="1"/>
       <c r="C744" s="1"/>
@@ -37438,7 +37439,7 @@
       <c r="AN744" s="1"/>
       <c r="AO744" s="1"/>
     </row>
-    <row r="745" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A745" s="1"/>
       <c r="B745" s="1"/>
       <c r="C745" s="1"/>
@@ -37481,7 +37482,7 @@
       <c r="AN745" s="1"/>
       <c r="AO745" s="1"/>
     </row>
-    <row r="746" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A746" s="1"/>
       <c r="B746" s="1"/>
       <c r="C746" s="1"/>
@@ -37524,7 +37525,7 @@
       <c r="AN746" s="1"/>
       <c r="AO746" s="1"/>
     </row>
-    <row r="747" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A747" s="1"/>
       <c r="B747" s="1"/>
       <c r="C747" s="1"/>
@@ -37567,7 +37568,7 @@
       <c r="AN747" s="1"/>
       <c r="AO747" s="1"/>
     </row>
-    <row r="748" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A748" s="1"/>
       <c r="B748" s="1"/>
       <c r="C748" s="1"/>
@@ -37610,7 +37611,7 @@
       <c r="AN748" s="1"/>
       <c r="AO748" s="1"/>
     </row>
-    <row r="749" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A749" s="1"/>
       <c r="B749" s="1"/>
       <c r="C749" s="1"/>
@@ -37653,7 +37654,7 @@
       <c r="AN749" s="1"/>
       <c r="AO749" s="1"/>
     </row>
-    <row r="750" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A750" s="1"/>
       <c r="B750" s="1"/>
       <c r="C750" s="1"/>
@@ -37696,7 +37697,7 @@
       <c r="AN750" s="1"/>
       <c r="AO750" s="1"/>
     </row>
-    <row r="751" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A751" s="1"/>
       <c r="B751" s="1"/>
       <c r="C751" s="1"/>
@@ -37739,7 +37740,7 @@
       <c r="AN751" s="1"/>
       <c r="AO751" s="1"/>
     </row>
-    <row r="752" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A752" s="1"/>
       <c r="B752" s="1"/>
       <c r="C752" s="1"/>
@@ -37782,7 +37783,7 @@
       <c r="AN752" s="1"/>
       <c r="AO752" s="1"/>
     </row>
-    <row r="753" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A753" s="1"/>
       <c r="B753" s="1"/>
       <c r="C753" s="1"/>
@@ -37825,7 +37826,7 @@
       <c r="AN753" s="1"/>
       <c r="AO753" s="1"/>
     </row>
-    <row r="754" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A754" s="1"/>
       <c r="B754" s="1"/>
       <c r="C754" s="1"/>
@@ -37868,7 +37869,7 @@
       <c r="AN754" s="1"/>
       <c r="AO754" s="1"/>
     </row>
-    <row r="755" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A755" s="1"/>
       <c r="B755" s="1"/>
       <c r="C755" s="1"/>
@@ -37911,7 +37912,7 @@
       <c r="AN755" s="1"/>
       <c r="AO755" s="1"/>
     </row>
-    <row r="756" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A756" s="1"/>
       <c r="B756" s="1"/>
       <c r="C756" s="1"/>
@@ -37954,7 +37955,7 @@
       <c r="AN756" s="1"/>
       <c r="AO756" s="1"/>
     </row>
-    <row r="757" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A757" s="1"/>
       <c r="B757" s="1"/>
       <c r="C757" s="1"/>
@@ -37997,7 +37998,7 @@
       <c r="AN757" s="1"/>
       <c r="AO757" s="1"/>
     </row>
-    <row r="758" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A758" s="1"/>
       <c r="B758" s="1"/>
       <c r="C758" s="1"/>
@@ -38040,7 +38041,7 @@
       <c r="AN758" s="1"/>
       <c r="AO758" s="1"/>
     </row>
-    <row r="759" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A759" s="1"/>
       <c r="B759" s="1"/>
       <c r="C759" s="1"/>
@@ -38083,7 +38084,7 @@
       <c r="AN759" s="1"/>
       <c r="AO759" s="1"/>
     </row>
-    <row r="760" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A760" s="1"/>
       <c r="B760" s="1"/>
       <c r="C760" s="1"/>
@@ -38126,7 +38127,7 @@
       <c r="AN760" s="1"/>
       <c r="AO760" s="1"/>
     </row>
-    <row r="761" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A761" s="1"/>
       <c r="B761" s="1"/>
       <c r="C761" s="1"/>
@@ -38169,7 +38170,7 @@
       <c r="AN761" s="1"/>
       <c r="AO761" s="1"/>
     </row>
-    <row r="762" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A762" s="1"/>
       <c r="B762" s="1"/>
       <c r="C762" s="1"/>
@@ -38212,7 +38213,7 @@
       <c r="AN762" s="1"/>
       <c r="AO762" s="1"/>
     </row>
-    <row r="763" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A763" s="1"/>
       <c r="B763" s="1"/>
       <c r="C763" s="1"/>
@@ -38255,7 +38256,7 @@
       <c r="AN763" s="1"/>
       <c r="AO763" s="1"/>
     </row>
-    <row r="764" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A764" s="1"/>
       <c r="B764" s="1"/>
       <c r="C764" s="1"/>
@@ -38298,7 +38299,7 @@
       <c r="AN764" s="1"/>
       <c r="AO764" s="1"/>
     </row>
-    <row r="765" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A765" s="1"/>
       <c r="B765" s="1"/>
       <c r="C765" s="1"/>
@@ -38341,7 +38342,7 @@
       <c r="AN765" s="1"/>
       <c r="AO765" s="1"/>
     </row>
-    <row r="766" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A766" s="1"/>
       <c r="B766" s="1"/>
       <c r="C766" s="1"/>
@@ -38384,7 +38385,7 @@
       <c r="AN766" s="1"/>
       <c r="AO766" s="1"/>
     </row>
-    <row r="767" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A767" s="1"/>
       <c r="B767" s="1"/>
       <c r="C767" s="1"/>
@@ -38427,7 +38428,7 @@
       <c r="AN767" s="1"/>
       <c r="AO767" s="1"/>
     </row>
-    <row r="768" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A768" s="1"/>
       <c r="B768" s="1"/>
       <c r="C768" s="1"/>
@@ -38470,7 +38471,7 @@
       <c r="AN768" s="1"/>
       <c r="AO768" s="1"/>
     </row>
-    <row r="769" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A769" s="1"/>
       <c r="B769" s="1"/>
       <c r="C769" s="1"/>
@@ -38513,7 +38514,7 @@
       <c r="AN769" s="1"/>
       <c r="AO769" s="1"/>
     </row>
-    <row r="770" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A770" s="1"/>
       <c r="B770" s="1"/>
       <c r="C770" s="1"/>
@@ -38556,7 +38557,7 @@
       <c r="AN770" s="1"/>
       <c r="AO770" s="1"/>
     </row>
-    <row r="771" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A771" s="1"/>
       <c r="B771" s="1"/>
       <c r="C771" s="1"/>
@@ -38599,7 +38600,7 @@
       <c r="AN771" s="1"/>
       <c r="AO771" s="1"/>
     </row>
-    <row r="772" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A772" s="1"/>
       <c r="B772" s="1"/>
       <c r="C772" s="1"/>
@@ -38642,7 +38643,7 @@
       <c r="AN772" s="1"/>
       <c r="AO772" s="1"/>
     </row>
-    <row r="773" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A773" s="1"/>
       <c r="B773" s="1"/>
       <c r="C773" s="1"/>
@@ -38685,7 +38686,7 @@
       <c r="AN773" s="1"/>
       <c r="AO773" s="1"/>
     </row>
-    <row r="774" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A774" s="1"/>
       <c r="B774" s="1"/>
       <c r="C774" s="1"/>
@@ -38728,7 +38729,7 @@
       <c r="AN774" s="1"/>
       <c r="AO774" s="1"/>
     </row>
-    <row r="775" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A775" s="1"/>
       <c r="B775" s="1"/>
       <c r="C775" s="1"/>
@@ -38771,7 +38772,7 @@
       <c r="AN775" s="1"/>
       <c r="AO775" s="1"/>
     </row>
-    <row r="776" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A776" s="1"/>
       <c r="B776" s="1"/>
       <c r="C776" s="1"/>
@@ -38814,7 +38815,7 @@
       <c r="AN776" s="1"/>
       <c r="AO776" s="1"/>
     </row>
-    <row r="777" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A777" s="1"/>
       <c r="B777" s="1"/>
       <c r="C777" s="1"/>
@@ -38857,7 +38858,7 @@
       <c r="AN777" s="1"/>
       <c r="AO777" s="1"/>
     </row>
-    <row r="778" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A778" s="1"/>
       <c r="B778" s="1"/>
       <c r="C778" s="1"/>
@@ -38900,7 +38901,7 @@
       <c r="AN778" s="1"/>
       <c r="AO778" s="1"/>
     </row>
-    <row r="779" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A779" s="1"/>
       <c r="B779" s="1"/>
       <c r="C779" s="1"/>
@@ -38943,7 +38944,7 @@
       <c r="AN779" s="1"/>
       <c r="AO779" s="1"/>
     </row>
-    <row r="780" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A780" s="1"/>
       <c r="B780" s="1"/>
       <c r="C780" s="1"/>
@@ -38986,7 +38987,7 @@
       <c r="AN780" s="1"/>
       <c r="AO780" s="1"/>
     </row>
-    <row r="781" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A781" s="1"/>
       <c r="B781" s="1"/>
       <c r="C781" s="1"/>
@@ -39029,7 +39030,7 @@
       <c r="AN781" s="1"/>
       <c r="AO781" s="1"/>
     </row>
-    <row r="782" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A782" s="1"/>
       <c r="B782" s="1"/>
       <c r="C782" s="1"/>
@@ -39072,7 +39073,7 @@
       <c r="AN782" s="1"/>
       <c r="AO782" s="1"/>
     </row>
-    <row r="783" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A783" s="1"/>
       <c r="B783" s="1"/>
       <c r="C783" s="1"/>
@@ -39115,7 +39116,7 @@
       <c r="AN783" s="1"/>
       <c r="AO783" s="1"/>
     </row>
-    <row r="784" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A784" s="1"/>
       <c r="B784" s="1"/>
       <c r="C784" s="1"/>
@@ -39158,7 +39159,7 @@
       <c r="AN784" s="1"/>
       <c r="AO784" s="1"/>
     </row>
-    <row r="785" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A785" s="1"/>
       <c r="B785" s="1"/>
       <c r="C785" s="1"/>
@@ -39201,7 +39202,7 @@
       <c r="AN785" s="1"/>
       <c r="AO785" s="1"/>
     </row>
-    <row r="786" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A786" s="1"/>
       <c r="B786" s="1"/>
       <c r="C786" s="1"/>
@@ -39244,7 +39245,7 @@
       <c r="AN786" s="1"/>
       <c r="AO786" s="1"/>
     </row>
-    <row r="787" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A787" s="1"/>
       <c r="B787" s="1"/>
       <c r="C787" s="1"/>
@@ -39287,7 +39288,7 @@
       <c r="AN787" s="1"/>
       <c r="AO787" s="1"/>
     </row>
-    <row r="788" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A788" s="1"/>
       <c r="B788" s="1"/>
       <c r="C788" s="1"/>
@@ -39330,7 +39331,7 @@
       <c r="AN788" s="1"/>
       <c r="AO788" s="1"/>
     </row>
-    <row r="789" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A789" s="1"/>
       <c r="B789" s="1"/>
       <c r="C789" s="1"/>
@@ -39373,7 +39374,7 @@
       <c r="AN789" s="1"/>
       <c r="AO789" s="1"/>
     </row>
-    <row r="790" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A790" s="1"/>
       <c r="B790" s="1"/>
       <c r="C790" s="1"/>
@@ -39416,7 +39417,7 @@
       <c r="AN790" s="1"/>
       <c r="AO790" s="1"/>
     </row>
-    <row r="791" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A791" s="1"/>
       <c r="B791" s="1"/>
       <c r="C791" s="1"/>
@@ -39459,7 +39460,7 @@
       <c r="AN791" s="1"/>
       <c r="AO791" s="1"/>
     </row>
-    <row r="792" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A792" s="1"/>
       <c r="B792" s="1"/>
       <c r="C792" s="1"/>
@@ -39502,7 +39503,7 @@
       <c r="AN792" s="1"/>
       <c r="AO792" s="1"/>
     </row>
-    <row r="793" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A793" s="1"/>
       <c r="B793" s="1"/>
       <c r="C793" s="1"/>
@@ -39545,7 +39546,7 @@
       <c r="AN793" s="1"/>
       <c r="AO793" s="1"/>
     </row>
-    <row r="794" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A794" s="1"/>
       <c r="B794" s="1"/>
       <c r="C794" s="1"/>
@@ -39588,7 +39589,7 @@
       <c r="AN794" s="1"/>
       <c r="AO794" s="1"/>
     </row>
-    <row r="795" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A795" s="1"/>
       <c r="B795" s="1"/>
       <c r="C795" s="1"/>
@@ -39631,7 +39632,7 @@
       <c r="AN795" s="1"/>
       <c r="AO795" s="1"/>
     </row>
-    <row r="796" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A796" s="1"/>
       <c r="B796" s="1"/>
       <c r="C796" s="1"/>
@@ -39674,7 +39675,7 @@
       <c r="AN796" s="1"/>
       <c r="AO796" s="1"/>
     </row>
-    <row r="797" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A797" s="1"/>
       <c r="B797" s="1"/>
       <c r="C797" s="1"/>
@@ -39717,7 +39718,7 @@
       <c r="AN797" s="1"/>
       <c r="AO797" s="1"/>
     </row>
-    <row r="798" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A798" s="1"/>
       <c r="B798" s="1"/>
       <c r="C798" s="1"/>
@@ -39760,7 +39761,7 @@
       <c r="AN798" s="1"/>
       <c r="AO798" s="1"/>
     </row>
-    <row r="799" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A799" s="1"/>
       <c r="B799" s="1"/>
       <c r="C799" s="1"/>
@@ -39803,7 +39804,7 @@
       <c r="AN799" s="1"/>
       <c r="AO799" s="1"/>
     </row>
-    <row r="800" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A800" s="1"/>
       <c r="B800" s="1"/>
       <c r="C800" s="1"/>
@@ -39846,7 +39847,7 @@
       <c r="AN800" s="1"/>
       <c r="AO800" s="1"/>
     </row>
-    <row r="801" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A801" s="1"/>
       <c r="B801" s="1"/>
       <c r="C801" s="1"/>
@@ -39889,7 +39890,7 @@
       <c r="AN801" s="1"/>
       <c r="AO801" s="1"/>
     </row>
-    <row r="802" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A802" s="1"/>
       <c r="B802" s="1"/>
       <c r="C802" s="1"/>
@@ -39932,7 +39933,7 @@
       <c r="AN802" s="1"/>
       <c r="AO802" s="1"/>
     </row>
-    <row r="803" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A803" s="1"/>
       <c r="B803" s="1"/>
       <c r="C803" s="1"/>
@@ -39975,7 +39976,7 @@
       <c r="AN803" s="1"/>
       <c r="AO803" s="1"/>
     </row>
-    <row r="804" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A804" s="1"/>
       <c r="B804" s="1"/>
       <c r="C804" s="1"/>
@@ -40018,7 +40019,7 @@
       <c r="AN804" s="1"/>
       <c r="AO804" s="1"/>
     </row>
-    <row r="805" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A805" s="1"/>
       <c r="B805" s="1"/>
       <c r="C805" s="1"/>
@@ -40061,7 +40062,7 @@
       <c r="AN805" s="1"/>
       <c r="AO805" s="1"/>
     </row>
-    <row r="806" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A806" s="1"/>
       <c r="B806" s="1"/>
       <c r="C806" s="1"/>
@@ -40104,7 +40105,7 @@
       <c r="AN806" s="1"/>
       <c r="AO806" s="1"/>
     </row>
-    <row r="807" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A807" s="1"/>
       <c r="B807" s="1"/>
       <c r="C807" s="1"/>
@@ -40147,7 +40148,7 @@
       <c r="AN807" s="1"/>
       <c r="AO807" s="1"/>
     </row>
-    <row r="808" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A808" s="1"/>
       <c r="B808" s="1"/>
       <c r="C808" s="1"/>
@@ -40190,7 +40191,7 @@
       <c r="AN808" s="1"/>
       <c r="AO808" s="1"/>
     </row>
-    <row r="809" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A809" s="1"/>
       <c r="B809" s="1"/>
       <c r="C809" s="1"/>
@@ -40233,7 +40234,7 @@
       <c r="AN809" s="1"/>
       <c r="AO809" s="1"/>
     </row>
-    <row r="810" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A810" s="1"/>
       <c r="B810" s="1"/>
       <c r="C810" s="1"/>
@@ -40276,7 +40277,7 @@
       <c r="AN810" s="1"/>
       <c r="AO810" s="1"/>
     </row>
-    <row r="811" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A811" s="1"/>
       <c r="B811" s="1"/>
       <c r="C811" s="1"/>
@@ -40319,7 +40320,7 @@
       <c r="AN811" s="1"/>
       <c r="AO811" s="1"/>
     </row>
-    <row r="812" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A812" s="1"/>
       <c r="B812" s="1"/>
       <c r="C812" s="1"/>
@@ -40362,7 +40363,7 @@
       <c r="AN812" s="1"/>
       <c r="AO812" s="1"/>
     </row>
-    <row r="813" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A813" s="1"/>
       <c r="B813" s="1"/>
       <c r="C813" s="1"/>
@@ -40405,7 +40406,7 @@
       <c r="AN813" s="1"/>
       <c r="AO813" s="1"/>
     </row>
-    <row r="814" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A814" s="1"/>
       <c r="B814" s="1"/>
       <c r="C814" s="1"/>
@@ -40448,7 +40449,7 @@
       <c r="AN814" s="1"/>
       <c r="AO814" s="1"/>
     </row>
-    <row r="815" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A815" s="1"/>
       <c r="B815" s="1"/>
       <c r="C815" s="1"/>
@@ -40491,7 +40492,7 @@
       <c r="AN815" s="1"/>
       <c r="AO815" s="1"/>
     </row>
-    <row r="816" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A816" s="1"/>
       <c r="B816" s="1"/>
       <c r="C816" s="1"/>
@@ -40534,7 +40535,7 @@
       <c r="AN816" s="1"/>
       <c r="AO816" s="1"/>
     </row>
-    <row r="817" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A817" s="1"/>
       <c r="B817" s="1"/>
       <c r="C817" s="1"/>
@@ -40577,7 +40578,7 @@
       <c r="AN817" s="1"/>
       <c r="AO817" s="1"/>
     </row>
-    <row r="818" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A818" s="1"/>
       <c r="B818" s="1"/>
       <c r="C818" s="1"/>
@@ -40620,7 +40621,7 @@
       <c r="AN818" s="1"/>
       <c r="AO818" s="1"/>
     </row>
-    <row r="819" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A819" s="1"/>
       <c r="B819" s="1"/>
       <c r="C819" s="1"/>
@@ -40663,7 +40664,7 @@
       <c r="AN819" s="1"/>
       <c r="AO819" s="1"/>
     </row>
-    <row r="820" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A820" s="1"/>
       <c r="B820" s="1"/>
       <c r="C820" s="1"/>
@@ -40706,7 +40707,7 @@
       <c r="AN820" s="1"/>
       <c r="AO820" s="1"/>
     </row>
-    <row r="821" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A821" s="1"/>
       <c r="B821" s="1"/>
       <c r="C821" s="1"/>
@@ -40749,7 +40750,7 @@
       <c r="AN821" s="1"/>
       <c r="AO821" s="1"/>
     </row>
-    <row r="822" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A822" s="1"/>
       <c r="B822" s="1"/>
       <c r="C822" s="1"/>
@@ -40792,7 +40793,7 @@
       <c r="AN822" s="1"/>
       <c r="AO822" s="1"/>
     </row>
-    <row r="823" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A823" s="1"/>
       <c r="B823" s="1"/>
       <c r="C823" s="1"/>
@@ -40835,7 +40836,7 @@
       <c r="AN823" s="1"/>
       <c r="AO823" s="1"/>
     </row>
-    <row r="824" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A824" s="1"/>
       <c r="B824" s="1"/>
       <c r="C824" s="1"/>
@@ -40878,7 +40879,7 @@
       <c r="AN824" s="1"/>
       <c r="AO824" s="1"/>
     </row>
-    <row r="825" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A825" s="1"/>
       <c r="B825" s="1"/>
       <c r="C825" s="1"/>
@@ -40921,7 +40922,7 @@
       <c r="AN825" s="1"/>
       <c r="AO825" s="1"/>
     </row>
-    <row r="826" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A826" s="1"/>
       <c r="B826" s="1"/>
       <c r="C826" s="1"/>
@@ -40964,7 +40965,7 @@
       <c r="AN826" s="1"/>
       <c r="AO826" s="1"/>
     </row>
-    <row r="827" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A827" s="1"/>
       <c r="B827" s="1"/>
       <c r="C827" s="1"/>
@@ -41007,7 +41008,7 @@
       <c r="AN827" s="1"/>
       <c r="AO827" s="1"/>
     </row>
-    <row r="828" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A828" s="1"/>
       <c r="B828" s="1"/>
       <c r="C828" s="1"/>
@@ -41050,7 +41051,7 @@
       <c r="AN828" s="1"/>
       <c r="AO828" s="1"/>
     </row>
-    <row r="829" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A829" s="1"/>
       <c r="B829" s="1"/>
       <c r="C829" s="1"/>
@@ -41093,7 +41094,7 @@
       <c r="AN829" s="1"/>
       <c r="AO829" s="1"/>
     </row>
-    <row r="830" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A830" s="1"/>
       <c r="B830" s="1"/>
       <c r="C830" s="1"/>
@@ -41136,7 +41137,7 @@
       <c r="AN830" s="1"/>
       <c r="AO830" s="1"/>
     </row>
-    <row r="831" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A831" s="1"/>
       <c r="B831" s="1"/>
       <c r="C831" s="1"/>
@@ -41179,7 +41180,7 @@
       <c r="AN831" s="1"/>
       <c r="AO831" s="1"/>
     </row>
-    <row r="832" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A832" s="1"/>
       <c r="B832" s="1"/>
       <c r="C832" s="1"/>
@@ -41222,7 +41223,7 @@
       <c r="AN832" s="1"/>
       <c r="AO832" s="1"/>
     </row>
-    <row r="833" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A833" s="1"/>
       <c r="B833" s="1"/>
       <c r="C833" s="1"/>
@@ -41265,7 +41266,7 @@
       <c r="AN833" s="1"/>
       <c r="AO833" s="1"/>
     </row>
-    <row r="834" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A834" s="1"/>
       <c r="B834" s="1"/>
       <c r="C834" s="1"/>
@@ -41308,7 +41309,7 @@
       <c r="AN834" s="1"/>
       <c r="AO834" s="1"/>
     </row>
-    <row r="835" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A835" s="1"/>
       <c r="B835" s="1"/>
       <c r="C835" s="1"/>
@@ -41351,7 +41352,7 @@
       <c r="AN835" s="1"/>
       <c r="AO835" s="1"/>
     </row>
-    <row r="836" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A836" s="1"/>
       <c r="B836" s="1"/>
       <c r="C836" s="1"/>
@@ -41394,7 +41395,7 @@
       <c r="AN836" s="1"/>
       <c r="AO836" s="1"/>
     </row>
-    <row r="837" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A837" s="1"/>
       <c r="B837" s="1"/>
       <c r="C837" s="1"/>
@@ -41437,7 +41438,7 @@
       <c r="AN837" s="1"/>
       <c r="AO837" s="1"/>
     </row>
-    <row r="838" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A838" s="1"/>
       <c r="B838" s="1"/>
       <c r="C838" s="1"/>
@@ -41480,7 +41481,7 @@
       <c r="AN838" s="1"/>
       <c r="AO838" s="1"/>
     </row>
-    <row r="839" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A839" s="1"/>
       <c r="B839" s="1"/>
       <c r="C839" s="1"/>
@@ -41523,7 +41524,7 @@
       <c r="AN839" s="1"/>
       <c r="AO839" s="1"/>
     </row>
-    <row r="840" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A840" s="1"/>
       <c r="B840" s="1"/>
       <c r="C840" s="1"/>
@@ -41566,7 +41567,7 @@
       <c r="AN840" s="1"/>
       <c r="AO840" s="1"/>
     </row>
-    <row r="841" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A841" s="1"/>
       <c r="B841" s="1"/>
       <c r="C841" s="1"/>
@@ -41609,7 +41610,7 @@
       <c r="AN841" s="1"/>
       <c r="AO841" s="1"/>
     </row>
-    <row r="842" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A842" s="1"/>
       <c r="B842" s="1"/>
       <c r="C842" s="1"/>
@@ -41652,7 +41653,7 @@
       <c r="AN842" s="1"/>
       <c r="AO842" s="1"/>
     </row>
-    <row r="843" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A843" s="1"/>
       <c r="B843" s="1"/>
       <c r="C843" s="1"/>
@@ -41695,7 +41696,7 @@
       <c r="AN843" s="1"/>
       <c r="AO843" s="1"/>
     </row>
-    <row r="844" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A844" s="1"/>
       <c r="B844" s="1"/>
       <c r="C844" s="1"/>
@@ -41738,7 +41739,7 @@
       <c r="AN844" s="1"/>
       <c r="AO844" s="1"/>
     </row>
-    <row r="845" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A845" s="1"/>
       <c r="B845" s="1"/>
       <c r="C845" s="1"/>
@@ -41781,7 +41782,7 @@
       <c r="AN845" s="1"/>
       <c r="AO845" s="1"/>
     </row>
-    <row r="846" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A846" s="1"/>
       <c r="B846" s="1"/>
       <c r="C846" s="1"/>
@@ -41824,7 +41825,7 @@
       <c r="AN846" s="1"/>
       <c r="AO846" s="1"/>
     </row>
-    <row r="847" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A847" s="1"/>
       <c r="B847" s="1"/>
       <c r="C847" s="1"/>
@@ -41867,7 +41868,7 @@
       <c r="AN847" s="1"/>
       <c r="AO847" s="1"/>
     </row>
-    <row r="848" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A848" s="1"/>
       <c r="B848" s="1"/>
       <c r="C848" s="1"/>
@@ -41910,7 +41911,7 @@
       <c r="AN848" s="1"/>
       <c r="AO848" s="1"/>
     </row>
-    <row r="849" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A849" s="1"/>
       <c r="B849" s="1"/>
       <c r="C849" s="1"/>
@@ -41953,7 +41954,7 @@
       <c r="AN849" s="1"/>
       <c r="AO849" s="1"/>
     </row>
-    <row r="850" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A850" s="1"/>
       <c r="B850" s="1"/>
       <c r="C850" s="1"/>
@@ -41996,7 +41997,7 @@
       <c r="AN850" s="1"/>
       <c r="AO850" s="1"/>
     </row>
-    <row r="851" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A851" s="1"/>
       <c r="B851" s="1"/>
       <c r="C851" s="1"/>
@@ -42039,7 +42040,7 @@
       <c r="AN851" s="1"/>
       <c r="AO851" s="1"/>
     </row>
-    <row r="852" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A852" s="1"/>
       <c r="B852" s="1"/>
       <c r="C852" s="1"/>
@@ -42082,7 +42083,7 @@
       <c r="AN852" s="1"/>
       <c r="AO852" s="1"/>
     </row>
-    <row r="853" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A853" s="1"/>
       <c r="B853" s="1"/>
       <c r="C853" s="1"/>
@@ -42125,7 +42126,7 @@
       <c r="AN853" s="1"/>
       <c r="AO853" s="1"/>
     </row>
-    <row r="854" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A854" s="1"/>
       <c r="B854" s="1"/>
       <c r="C854" s="1"/>
@@ -42168,7 +42169,7 @@
       <c r="AN854" s="1"/>
       <c r="AO854" s="1"/>
     </row>
-    <row r="855" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A855" s="1"/>
       <c r="B855" s="1"/>
       <c r="C855" s="1"/>
@@ -42211,7 +42212,7 @@
       <c r="AN855" s="1"/>
       <c r="AO855" s="1"/>
     </row>
-    <row r="856" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A856" s="1"/>
       <c r="B856" s="1"/>
       <c r="C856" s="1"/>
@@ -42254,7 +42255,7 @@
       <c r="AN856" s="1"/>
       <c r="AO856" s="1"/>
     </row>
-    <row r="857" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A857" s="1"/>
       <c r="B857" s="1"/>
       <c r="C857" s="1"/>
@@ -42297,7 +42298,7 @@
       <c r="AN857" s="1"/>
       <c r="AO857" s="1"/>
     </row>
-    <row r="858" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A858" s="1"/>
       <c r="B858" s="1"/>
       <c r="C858" s="1"/>
@@ -42340,7 +42341,7 @@
       <c r="AN858" s="1"/>
       <c r="AO858" s="1"/>
     </row>
-    <row r="859" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A859" s="1"/>
       <c r="B859" s="1"/>
       <c r="C859" s="1"/>
@@ -42383,7 +42384,7 @@
       <c r="AN859" s="1"/>
       <c r="AO859" s="1"/>
     </row>
-    <row r="860" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A860" s="1"/>
       <c r="B860" s="1"/>
       <c r="C860" s="1"/>
@@ -42426,7 +42427,7 @@
       <c r="AN860" s="1"/>
       <c r="AO860" s="1"/>
     </row>
-    <row r="861" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A861" s="1"/>
       <c r="B861" s="1"/>
       <c r="C861" s="1"/>
@@ -42469,7 +42470,7 @@
       <c r="AN861" s="1"/>
       <c r="AO861" s="1"/>
     </row>
-    <row r="862" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A862" s="1"/>
       <c r="B862" s="1"/>
       <c r="C862" s="1"/>
@@ -42512,7 +42513,7 @@
       <c r="AN862" s="1"/>
       <c r="AO862" s="1"/>
     </row>
-    <row r="863" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A863" s="1"/>
       <c r="B863" s="1"/>
       <c r="C863" s="1"/>
@@ -42555,7 +42556,7 @@
       <c r="AN863" s="1"/>
       <c r="AO863" s="1"/>
     </row>
-    <row r="864" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A864" s="1"/>
       <c r="B864" s="1"/>
       <c r="C864" s="1"/>
@@ -42598,7 +42599,7 @@
       <c r="AN864" s="1"/>
       <c r="AO864" s="1"/>
     </row>
-    <row r="865" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A865" s="1"/>
       <c r="B865" s="1"/>
       <c r="C865" s="1"/>
@@ -42641,7 +42642,7 @@
       <c r="AN865" s="1"/>
       <c r="AO865" s="1"/>
     </row>
-    <row r="866" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A866" s="1"/>
       <c r="B866" s="1"/>
       <c r="C866" s="1"/>
@@ -42684,7 +42685,7 @@
       <c r="AN866" s="1"/>
       <c r="AO866" s="1"/>
     </row>
-    <row r="867" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A867" s="1"/>
       <c r="B867" s="1"/>
       <c r="C867" s="1"/>
@@ -42727,7 +42728,7 @@
       <c r="AN867" s="1"/>
       <c r="AO867" s="1"/>
     </row>
-    <row r="868" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A868" s="1"/>
       <c r="B868" s="1"/>
       <c r="C868" s="1"/>
@@ -42770,7 +42771,7 @@
       <c r="AN868" s="1"/>
       <c r="AO868" s="1"/>
     </row>
-    <row r="869" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A869" s="1"/>
       <c r="B869" s="1"/>
       <c r="C869" s="1"/>
@@ -42813,7 +42814,7 @@
       <c r="AN869" s="1"/>
       <c r="AO869" s="1"/>
     </row>
-    <row r="870" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A870" s="1"/>
       <c r="B870" s="1"/>
       <c r="C870" s="1"/>
@@ -42856,7 +42857,7 @@
       <c r="AN870" s="1"/>
       <c r="AO870" s="1"/>
     </row>
-    <row r="871" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A871" s="1"/>
       <c r="B871" s="1"/>
       <c r="C871" s="1"/>
@@ -42899,7 +42900,7 @@
       <c r="AN871" s="1"/>
       <c r="AO871" s="1"/>
     </row>
-    <row r="872" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A872" s="1"/>
       <c r="B872" s="1"/>
       <c r="C872" s="1"/>
@@ -42942,7 +42943,7 @@
       <c r="AN872" s="1"/>
       <c r="AO872" s="1"/>
     </row>
-    <row r="873" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A873" s="1"/>
       <c r="B873" s="1"/>
       <c r="C873" s="1"/>
@@ -42985,7 +42986,7 @@
       <c r="AN873" s="1"/>
       <c r="AO873" s="1"/>
     </row>
-    <row r="874" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A874" s="1"/>
       <c r="B874" s="1"/>
       <c r="C874" s="1"/>
@@ -43028,7 +43029,7 @@
       <c r="AN874" s="1"/>
       <c r="AO874" s="1"/>
     </row>
-    <row r="875" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A875" s="1"/>
       <c r="B875" s="1"/>
       <c r="C875" s="1"/>
@@ -43071,7 +43072,7 @@
       <c r="AN875" s="1"/>
       <c r="AO875" s="1"/>
     </row>
-    <row r="876" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A876" s="1"/>
       <c r="B876" s="1"/>
       <c r="C876" s="1"/>
@@ -43114,7 +43115,7 @@
       <c r="AN876" s="1"/>
       <c r="AO876" s="1"/>
     </row>
-    <row r="877" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A877" s="1"/>
       <c r="B877" s="1"/>
       <c r="C877" s="1"/>
@@ -43157,7 +43158,7 @@
       <c r="AN877" s="1"/>
       <c r="AO877" s="1"/>
     </row>
-    <row r="878" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A878" s="1"/>
       <c r="B878" s="1"/>
       <c r="C878" s="1"/>
@@ -43200,7 +43201,7 @@
       <c r="AN878" s="1"/>
       <c r="AO878" s="1"/>
     </row>
-    <row r="879" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A879" s="1"/>
       <c r="B879" s="1"/>
       <c r="C879" s="1"/>
@@ -43243,7 +43244,7 @@
       <c r="AN879" s="1"/>
       <c r="AO879" s="1"/>
     </row>
-    <row r="880" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A880" s="1"/>
       <c r="B880" s="1"/>
       <c r="C880" s="1"/>
@@ -43286,7 +43287,7 @@
       <c r="AN880" s="1"/>
       <c r="AO880" s="1"/>
     </row>
-    <row r="881" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A881" s="1"/>
       <c r="B881" s="1"/>
       <c r="C881" s="1"/>
@@ -43329,7 +43330,7 @@
       <c r="AN881" s="1"/>
       <c r="AO881" s="1"/>
     </row>
-    <row r="882" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A882" s="1"/>
       <c r="B882" s="1"/>
       <c r="C882" s="1"/>
@@ -43372,7 +43373,7 @@
       <c r="AN882" s="1"/>
       <c r="AO882" s="1"/>
     </row>
-    <row r="883" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A883" s="1"/>
       <c r="B883" s="1"/>
       <c r="C883" s="1"/>
@@ -43415,7 +43416,7 @@
       <c r="AN883" s="1"/>
       <c r="AO883" s="1"/>
     </row>
-    <row r="884" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A884" s="1"/>
       <c r="B884" s="1"/>
       <c r="C884" s="1"/>
@@ -43458,7 +43459,7 @@
       <c r="AN884" s="1"/>
       <c r="AO884" s="1"/>
     </row>
-    <row r="885" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A885" s="1"/>
       <c r="B885" s="1"/>
       <c r="C885" s="1"/>
@@ -43501,7 +43502,7 @@
       <c r="AN885" s="1"/>
       <c r="AO885" s="1"/>
     </row>
-    <row r="886" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A886" s="1"/>
       <c r="B886" s="1"/>
       <c r="C886" s="1"/>
@@ -43544,7 +43545,7 @@
       <c r="AN886" s="1"/>
       <c r="AO886" s="1"/>
     </row>
-    <row r="887" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A887" s="1"/>
       <c r="B887" s="1"/>
       <c r="C887" s="1"/>
@@ -43587,7 +43588,7 @@
       <c r="AN887" s="1"/>
       <c r="AO887" s="1"/>
     </row>
-    <row r="888" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A888" s="1"/>
       <c r="B888" s="1"/>
       <c r="C888" s="1"/>
@@ -43630,7 +43631,7 @@
       <c r="AN888" s="1"/>
       <c r="AO888" s="1"/>
     </row>
-    <row r="889" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A889" s="1"/>
       <c r="B889" s="1"/>
       <c r="C889" s="1"/>
@@ -43673,7 +43674,7 @@
       <c r="AN889" s="1"/>
       <c r="AO889" s="1"/>
     </row>
-    <row r="890" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A890" s="1"/>
       <c r="B890" s="1"/>
       <c r="C890" s="1"/>
@@ -43716,7 +43717,7 @@
       <c r="AN890" s="1"/>
       <c r="AO890" s="1"/>
     </row>
-    <row r="891" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A891" s="1"/>
       <c r="B891" s="1"/>
       <c r="C891" s="1"/>
@@ -43759,7 +43760,7 @@
       <c r="AN891" s="1"/>
       <c r="AO891" s="1"/>
     </row>
-    <row r="892" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A892" s="1"/>
       <c r="B892" s="1"/>
       <c r="C892" s="1"/>
@@ -43802,7 +43803,7 @@
       <c r="AN892" s="1"/>
       <c r="AO892" s="1"/>
     </row>
-    <row r="893" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A893" s="1"/>
       <c r="B893" s="1"/>
       <c r="C893" s="1"/>
@@ -43845,7 +43846,7 @@
       <c r="AN893" s="1"/>
       <c r="AO893" s="1"/>
     </row>
-    <row r="894" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A894" s="1"/>
       <c r="B894" s="1"/>
       <c r="C894" s="1"/>
@@ -43888,7 +43889,7 @@
       <c r="AN894" s="1"/>
       <c r="AO894" s="1"/>
     </row>
-    <row r="895" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A895" s="1"/>
       <c r="B895" s="1"/>
       <c r="C895" s="1"/>
@@ -43931,7 +43932,7 @@
       <c r="AN895" s="1"/>
       <c r="AO895" s="1"/>
     </row>
-    <row r="896" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A896" s="1"/>
       <c r="B896" s="1"/>
       <c r="C896" s="1"/>
@@ -43974,7 +43975,7 @@
       <c r="AN896" s="1"/>
       <c r="AO896" s="1"/>
     </row>
-    <row r="897" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A897" s="1"/>
       <c r="B897" s="1"/>
       <c r="C897" s="1"/>
@@ -44017,7 +44018,7 @@
       <c r="AN897" s="1"/>
       <c r="AO897" s="1"/>
     </row>
-    <row r="898" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A898" s="1"/>
       <c r="B898" s="1"/>
       <c r="C898" s="1"/>
@@ -44060,7 +44061,7 @@
       <c r="AN898" s="1"/>
       <c r="AO898" s="1"/>
     </row>
-    <row r="899" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A899" s="1"/>
       <c r="B899" s="1"/>
       <c r="C899" s="1"/>
@@ -44103,7 +44104,7 @@
       <c r="AN899" s="1"/>
       <c r="AO899" s="1"/>
     </row>
-    <row r="900" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A900" s="1"/>
       <c r="B900" s="1"/>
       <c r="C900" s="1"/>
@@ -44146,7 +44147,7 @@
       <c r="AN900" s="1"/>
       <c r="AO900" s="1"/>
     </row>
-    <row r="901" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A901" s="1"/>
       <c r="B901" s="1"/>
       <c r="C901" s="1"/>
@@ -44189,7 +44190,7 @@
       <c r="AN901" s="1"/>
       <c r="AO901" s="1"/>
     </row>
-    <row r="902" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A902" s="1"/>
       <c r="B902" s="1"/>
       <c r="C902" s="1"/>
@@ -44232,7 +44233,7 @@
       <c r="AN902" s="1"/>
       <c r="AO902" s="1"/>
     </row>
-    <row r="903" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A903" s="1"/>
       <c r="B903" s="1"/>
       <c r="C903" s="1"/>
@@ -44275,7 +44276,7 @@
       <c r="AN903" s="1"/>
       <c r="AO903" s="1"/>
     </row>
-    <row r="904" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A904" s="1"/>
       <c r="B904" s="1"/>
       <c r="C904" s="1"/>
@@ -44318,7 +44319,7 @@
       <c r="AN904" s="1"/>
       <c r="AO904" s="1"/>
     </row>
-    <row r="905" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A905" s="1"/>
       <c r="B905" s="1"/>
       <c r="C905" s="1"/>
@@ -44361,7 +44362,7 @@
       <c r="AN905" s="1"/>
       <c r="AO905" s="1"/>
     </row>
-    <row r="906" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A906" s="1"/>
       <c r="B906" s="1"/>
       <c r="C906" s="1"/>
@@ -44404,7 +44405,7 @@
       <c r="AN906" s="1"/>
       <c r="AO906" s="1"/>
     </row>
-    <row r="907" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A907" s="1"/>
       <c r="B907" s="1"/>
       <c r="C907" s="1"/>
@@ -44447,7 +44448,7 @@
       <c r="AN907" s="1"/>
       <c r="AO907" s="1"/>
     </row>
-    <row r="908" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A908" s="1"/>
       <c r="B908" s="1"/>
       <c r="C908" s="1"/>
@@ -44490,7 +44491,7 @@
       <c r="AN908" s="1"/>
       <c r="AO908" s="1"/>
     </row>
-    <row r="909" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A909" s="1"/>
       <c r="B909" s="1"/>
       <c r="C909" s="1"/>
@@ -44533,7 +44534,7 @@
       <c r="AN909" s="1"/>
       <c r="AO909" s="1"/>
     </row>
-    <row r="910" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A910" s="1"/>
       <c r="B910" s="1"/>
       <c r="C910" s="1"/>
@@ -44576,7 +44577,7 @@
       <c r="AN910" s="1"/>
       <c r="AO910" s="1"/>
     </row>
-    <row r="911" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A911" s="1"/>
       <c r="B911" s="1"/>
       <c r="C911" s="1"/>
@@ -44619,7 +44620,7 @@
       <c r="AN911" s="1"/>
       <c r="AO911" s="1"/>
     </row>
-    <row r="912" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A912" s="1"/>
       <c r="B912" s="1"/>
       <c r="C912" s="1"/>
@@ -44662,7 +44663,7 @@
       <c r="AN912" s="1"/>
       <c r="AO912" s="1"/>
     </row>
-    <row r="913" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A913" s="1"/>
       <c r="B913" s="1"/>
       <c r="C913" s="1"/>
@@ -44705,7 +44706,7 @@
       <c r="AN913" s="1"/>
       <c r="AO913" s="1"/>
     </row>
-    <row r="914" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A914" s="1"/>
       <c r="B914" s="1"/>
       <c r="C914" s="1"/>
@@ -44748,7 +44749,7 @@
       <c r="AN914" s="1"/>
       <c r="AO914" s="1"/>
     </row>
-    <row r="915" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A915" s="1"/>
       <c r="B915" s="1"/>
       <c r="C915" s="1"/>
@@ -44791,7 +44792,7 @@
       <c r="AN915" s="1"/>
       <c r="AO915" s="1"/>
     </row>
-    <row r="916" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A916" s="1"/>
       <c r="B916" s="1"/>
       <c r="C916" s="1"/>
@@ -44834,7 +44835,7 @@
       <c r="AN916" s="1"/>
       <c r="AO916" s="1"/>
     </row>
-    <row r="917" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A917" s="1"/>
       <c r="B917" s="1"/>
       <c r="C917" s="1"/>
@@ -44877,7 +44878,7 @@
       <c r="AN917" s="1"/>
       <c r="AO917" s="1"/>
     </row>
-    <row r="918" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A918" s="1"/>
       <c r="B918" s="1"/>
       <c r="C918" s="1"/>
@@ -44920,7 +44921,7 @@
       <c r="AN918" s="1"/>
       <c r="AO918" s="1"/>
     </row>
-    <row r="919" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A919" s="1"/>
       <c r="B919" s="1"/>
       <c r="C919" s="1"/>
@@ -44963,7 +44964,7 @@
       <c r="AN919" s="1"/>
       <c r="AO919" s="1"/>
     </row>
-    <row r="920" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A920" s="1"/>
       <c r="B920" s="1"/>
       <c r="C920" s="1"/>
@@ -45006,7 +45007,7 @@
       <c r="AN920" s="1"/>
       <c r="AO920" s="1"/>
     </row>
-    <row r="921" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A921" s="1"/>
       <c r="B921" s="1"/>
       <c r="C921" s="1"/>
@@ -45049,7 +45050,7 @@
       <c r="AN921" s="1"/>
       <c r="AO921" s="1"/>
     </row>
-    <row r="922" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A922" s="1"/>
       <c r="B922" s="1"/>
       <c r="C922" s="1"/>
@@ -45092,7 +45093,7 @@
       <c r="AN922" s="1"/>
       <c r="AO922" s="1"/>
     </row>
-    <row r="923" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A923" s="1"/>
       <c r="B923" s="1"/>
       <c r="C923" s="1"/>
@@ -45135,7 +45136,7 @@
       <c r="AN923" s="1"/>
       <c r="AO923" s="1"/>
     </row>
-    <row r="924" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A924" s="1"/>
       <c r="B924" s="1"/>
       <c r="C924" s="1"/>
@@ -45178,7 +45179,7 @@
       <c r="AN924" s="1"/>
       <c r="AO924" s="1"/>
     </row>
-    <row r="925" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A925" s="1"/>
       <c r="B925" s="1"/>
       <c r="C925" s="1"/>
@@ -45221,7 +45222,7 @@
       <c r="AN925" s="1"/>
       <c r="AO925" s="1"/>
     </row>
-    <row r="926" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A926" s="1"/>
       <c r="B926" s="1"/>
       <c r="C926" s="1"/>
@@ -45264,7 +45265,7 @@
       <c r="AN926" s="1"/>
       <c r="AO926" s="1"/>
     </row>
-    <row r="927" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A927" s="1"/>
       <c r="B927" s="1"/>
       <c r="C927" s="1"/>
@@ -45307,7 +45308,7 @@
       <c r="AN927" s="1"/>
       <c r="AO927" s="1"/>
     </row>
-    <row r="928" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A928" s="1"/>
       <c r="B928" s="1"/>
       <c r="C928" s="1"/>
@@ -45350,7 +45351,7 @@
       <c r="AN928" s="1"/>
       <c r="AO928" s="1"/>
     </row>
-    <row r="929" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A929" s="1"/>
       <c r="B929" s="1"/>
       <c r="C929" s="1"/>
@@ -45393,7 +45394,7 @@
       <c r="AN929" s="1"/>
       <c r="AO929" s="1"/>
     </row>
-    <row r="930" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A930" s="1"/>
       <c r="B930" s="1"/>
       <c r="C930" s="1"/>
@@ -45436,7 +45437,7 @@
       <c r="AN930" s="1"/>
       <c r="AO930" s="1"/>
     </row>
-    <row r="931" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A931" s="1"/>
       <c r="B931" s="1"/>
       <c r="C931" s="1"/>
@@ -45479,7 +45480,7 @@
       <c r="AN931" s="1"/>
       <c r="AO931" s="1"/>
     </row>
-    <row r="932" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A932" s="1"/>
       <c r="B932" s="1"/>
       <c r="C932" s="1"/>
@@ -45522,7 +45523,7 @@
       <c r="AN932" s="1"/>
       <c r="AO932" s="1"/>
     </row>
-    <row r="933" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A933" s="1"/>
       <c r="B933" s="1"/>
       <c r="C933" s="1"/>
@@ -45565,7 +45566,7 @@
       <c r="AN933" s="1"/>
       <c r="AO933" s="1"/>
     </row>
-    <row r="934" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A934" s="1"/>
       <c r="B934" s="1"/>
       <c r="C934" s="1"/>
@@ -45608,7 +45609,7 @@
       <c r="AN934" s="1"/>
       <c r="AO934" s="1"/>
     </row>
-    <row r="935" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A935" s="1"/>
       <c r="B935" s="1"/>
       <c r="C935" s="1"/>
@@ -45651,7 +45652,7 @@
       <c r="AN935" s="1"/>
       <c r="AO935" s="1"/>
     </row>
-    <row r="936" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A936" s="1"/>
       <c r="B936" s="1"/>
       <c r="C936" s="1"/>
@@ -45694,7 +45695,7 @@
       <c r="AN936" s="1"/>
       <c r="AO936" s="1"/>
     </row>
-    <row r="937" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A937" s="1"/>
       <c r="B937" s="1"/>
       <c r="C937" s="1"/>
@@ -45737,7 +45738,7 @@
       <c r="AN937" s="1"/>
       <c r="AO937" s="1"/>
     </row>
-    <row r="938" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A938" s="1"/>
       <c r="B938" s="1"/>
       <c r="C938" s="1"/>
@@ -45780,7 +45781,7 @@
       <c r="AN938" s="1"/>
       <c r="AO938" s="1"/>
     </row>
-    <row r="939" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A939" s="1"/>
       <c r="B939" s="1"/>
       <c r="C939" s="1"/>
@@ -45823,7 +45824,7 @@
       <c r="AN939" s="1"/>
       <c r="AO939" s="1"/>
     </row>
-    <row r="940" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A940" s="1"/>
       <c r="B940" s="1"/>
       <c r="C940" s="1"/>
@@ -45866,7 +45867,7 @@
       <c r="AN940" s="1"/>
       <c r="AO940" s="1"/>
     </row>
-    <row r="941" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A941" s="1"/>
       <c r="B941" s="1"/>
       <c r="C941" s="1"/>
@@ -45909,7 +45910,7 @@
       <c r="AN941" s="1"/>
       <c r="AO941" s="1"/>
     </row>
-    <row r="942" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A942" s="1"/>
       <c r="B942" s="1"/>
       <c r="C942" s="1"/>
@@ -45952,7 +45953,7 @@
       <c r="AN942" s="1"/>
       <c r="AO942" s="1"/>
     </row>
-    <row r="943" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A943" s="1"/>
       <c r="B943" s="1"/>
       <c r="C943" s="1"/>
@@ -45995,7 +45996,7 @@
       <c r="AN943" s="1"/>
       <c r="AO943" s="1"/>
     </row>
-    <row r="944" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A944" s="1"/>
       <c r="B944" s="1"/>
       <c r="C944" s="1"/>
@@ -46038,7 +46039,7 @@
       <c r="AN944" s="1"/>
       <c r="AO944" s="1"/>
     </row>
-    <row r="945" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A945" s="1"/>
       <c r="B945" s="1"/>
       <c r="C945" s="1"/>
@@ -46081,7 +46082,7 @@
       <c r="AN945" s="1"/>
       <c r="AO945" s="1"/>
     </row>
-    <row r="946" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A946" s="1"/>
       <c r="B946" s="1"/>
       <c r="C946" s="1"/>
@@ -46124,7 +46125,7 @@
       <c r="AN946" s="1"/>
       <c r="AO946" s="1"/>
     </row>
-    <row r="947" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A947" s="1"/>
       <c r="B947" s="1"/>
       <c r="C947" s="1"/>
@@ -46167,7 +46168,7 @@
       <c r="AN947" s="1"/>
       <c r="AO947" s="1"/>
     </row>
-    <row r="948" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A948" s="1"/>
       <c r="B948" s="1"/>
       <c r="C948" s="1"/>
@@ -46210,7 +46211,7 @@
       <c r="AN948" s="1"/>
       <c r="AO948" s="1"/>
     </row>
-    <row r="949" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A949" s="1"/>
       <c r="B949" s="1"/>
       <c r="C949" s="1"/>
@@ -46253,7 +46254,7 @@
       <c r="AN949" s="1"/>
       <c r="AO949" s="1"/>
     </row>
-    <row r="950" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A950" s="1"/>
       <c r="B950" s="1"/>
       <c r="C950" s="1"/>
@@ -46296,7 +46297,7 @@
       <c r="AN950" s="1"/>
       <c r="AO950" s="1"/>
     </row>
-    <row r="951" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A951" s="1"/>
       <c r="B951" s="1"/>
       <c r="C951" s="1"/>
@@ -46339,7 +46340,7 @@
       <c r="AN951" s="1"/>
       <c r="AO951" s="1"/>
     </row>
-    <row r="952" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="952" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A952" s="1"/>
       <c r="B952" s="1"/>
       <c r="C952" s="1"/>
@@ -46382,7 +46383,7 @@
       <c r="AN952" s="1"/>
       <c r="AO952" s="1"/>
     </row>
-    <row r="953" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A953" s="1"/>
       <c r="B953" s="1"/>
       <c r="C953" s="1"/>
@@ -46425,7 +46426,7 @@
       <c r="AN953" s="1"/>
       <c r="AO953" s="1"/>
     </row>
-    <row r="954" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A954" s="1"/>
       <c r="B954" s="1"/>
       <c r="C954" s="1"/>
@@ -46468,7 +46469,7 @@
       <c r="AN954" s="1"/>
       <c r="AO954" s="1"/>
     </row>
-    <row r="955" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="955" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A955" s="1"/>
       <c r="B955" s="1"/>
       <c r="C955" s="1"/>
@@ -46511,7 +46512,7 @@
       <c r="AN955" s="1"/>
       <c r="AO955" s="1"/>
     </row>
-    <row r="956" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="956" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A956" s="1"/>
       <c r="B956" s="1"/>
       <c r="C956" s="1"/>
@@ -46554,7 +46555,7 @@
       <c r="AN956" s="1"/>
       <c r="AO956" s="1"/>
     </row>
-    <row r="957" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="957" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A957" s="1"/>
       <c r="B957" s="1"/>
       <c r="C957" s="1"/>
@@ -46597,7 +46598,7 @@
       <c r="AN957" s="1"/>
       <c r="AO957" s="1"/>
     </row>
-    <row r="958" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="958" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A958" s="1"/>
       <c r="B958" s="1"/>
       <c r="C958" s="1"/>
@@ -46640,7 +46641,7 @@
       <c r="AN958" s="1"/>
       <c r="AO958" s="1"/>
     </row>
-    <row r="959" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="959" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A959" s="1"/>
       <c r="B959" s="1"/>
       <c r="C959" s="1"/>
@@ -46683,7 +46684,7 @@
       <c r="AN959" s="1"/>
       <c r="AO959" s="1"/>
     </row>
-    <row r="960" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A960" s="1"/>
       <c r="B960" s="1"/>
       <c r="C960" s="1"/>
@@ -46726,7 +46727,7 @@
       <c r="AN960" s="1"/>
       <c r="AO960" s="1"/>
     </row>
-    <row r="961" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="961" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A961" s="1"/>
       <c r="B961" s="1"/>
       <c r="C961" s="1"/>
@@ -46769,7 +46770,7 @@
       <c r="AN961" s="1"/>
       <c r="AO961" s="1"/>
     </row>
-    <row r="962" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A962" s="1"/>
       <c r="B962" s="1"/>
       <c r="C962" s="1"/>
@@ -46812,7 +46813,7 @@
       <c r="AN962" s="1"/>
       <c r="AO962" s="1"/>
     </row>
-    <row r="963" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A963" s="1"/>
       <c r="B963" s="1"/>
       <c r="C963" s="1"/>
@@ -46855,7 +46856,7 @@
       <c r="AN963" s="1"/>
       <c r="AO963" s="1"/>
     </row>
-    <row r="964" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="964" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A964" s="1"/>
       <c r="B964" s="1"/>
       <c r="C964" s="1"/>
@@ -46898,7 +46899,7 @@
       <c r="AN964" s="1"/>
       <c r="AO964" s="1"/>
     </row>
-    <row r="965" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="965" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A965" s="1"/>
       <c r="B965" s="1"/>
       <c r="C965" s="1"/>
@@ -46941,7 +46942,7 @@
       <c r="AN965" s="1"/>
       <c r="AO965" s="1"/>
     </row>
-    <row r="966" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="966" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A966" s="1"/>
       <c r="B966" s="1"/>
       <c r="C966" s="1"/>
@@ -46984,7 +46985,7 @@
       <c r="AN966" s="1"/>
       <c r="AO966" s="1"/>
     </row>
-    <row r="967" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="967" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A967" s="1"/>
       <c r="B967" s="1"/>
       <c r="C967" s="1"/>
@@ -47027,7 +47028,7 @@
       <c r="AN967" s="1"/>
       <c r="AO967" s="1"/>
     </row>
-    <row r="968" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A968" s="1"/>
       <c r="B968" s="1"/>
       <c r="C968" s="1"/>
@@ -47070,7 +47071,7 @@
       <c r="AN968" s="1"/>
       <c r="AO968" s="1"/>
     </row>
-    <row r="969" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="969" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A969" s="1"/>
       <c r="B969" s="1"/>
       <c r="C969" s="1"/>
@@ -47113,7 +47114,7 @@
       <c r="AN969" s="1"/>
       <c r="AO969" s="1"/>
     </row>
-    <row r="970" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="970" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A970" s="1"/>
       <c r="B970" s="1"/>
       <c r="C970" s="1"/>
@@ -47156,7 +47157,7 @@
       <c r="AN970" s="1"/>
       <c r="AO970" s="1"/>
     </row>
-    <row r="971" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="971" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A971" s="1"/>
       <c r="B971" s="1"/>
       <c r="C971" s="1"/>
@@ -47199,7 +47200,7 @@
       <c r="AN971" s="1"/>
       <c r="AO971" s="1"/>
     </row>
-    <row r="972" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="972" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A972" s="1"/>
       <c r="B972" s="1"/>
       <c r="C972" s="1"/>
@@ -47242,7 +47243,7 @@
       <c r="AN972" s="1"/>
       <c r="AO972" s="1"/>
     </row>
-    <row r="973" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="973" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A973" s="1"/>
       <c r="B973" s="1"/>
       <c r="C973" s="1"/>
@@ -47285,7 +47286,7 @@
       <c r="AN973" s="1"/>
       <c r="AO973" s="1"/>
     </row>
-    <row r="974" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="974" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A974" s="1"/>
       <c r="B974" s="1"/>
       <c r="C974" s="1"/>
@@ -47328,7 +47329,7 @@
       <c r="AN974" s="1"/>
       <c r="AO974" s="1"/>
     </row>
-    <row r="975" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="975" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A975" s="1"/>
       <c r="B975" s="1"/>
       <c r="C975" s="1"/>
@@ -47371,7 +47372,7 @@
       <c r="AN975" s="1"/>
       <c r="AO975" s="1"/>
     </row>
-    <row r="976" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A976" s="1"/>
       <c r="B976" s="1"/>
       <c r="C976" s="1"/>
@@ -47414,7 +47415,7 @@
       <c r="AN976" s="1"/>
       <c r="AO976" s="1"/>
     </row>
-    <row r="977" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A977" s="1"/>
       <c r="B977" s="1"/>
       <c r="C977" s="1"/>
@@ -47457,7 +47458,7 @@
       <c r="AN977" s="1"/>
       <c r="AO977" s="1"/>
     </row>
-    <row r="978" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A978" s="1"/>
       <c r="B978" s="1"/>
       <c r="C978" s="1"/>
@@ -47500,7 +47501,7 @@
       <c r="AN978" s="1"/>
       <c r="AO978" s="1"/>
     </row>
-    <row r="979" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="979" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A979" s="1"/>
       <c r="B979" s="1"/>
       <c r="C979" s="1"/>
@@ -47543,7 +47544,7 @@
       <c r="AN979" s="1"/>
       <c r="AO979" s="1"/>
     </row>
-    <row r="980" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="980" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A980" s="1"/>
       <c r="B980" s="1"/>
       <c r="C980" s="1"/>
@@ -47586,7 +47587,7 @@
       <c r="AN980" s="1"/>
       <c r="AO980" s="1"/>
     </row>
-    <row r="981" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="981" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A981" s="1"/>
       <c r="B981" s="1"/>
       <c r="C981" s="1"/>
@@ -47629,7 +47630,7 @@
       <c r="AN981" s="1"/>
       <c r="AO981" s="1"/>
     </row>
-    <row r="982" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="982" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A982" s="1"/>
       <c r="B982" s="1"/>
       <c r="C982" s="1"/>
@@ -47672,7 +47673,7 @@
       <c r="AN982" s="1"/>
       <c r="AO982" s="1"/>
     </row>
-    <row r="983" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="983" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A983" s="1"/>
       <c r="B983" s="1"/>
       <c r="C983" s="1"/>
@@ -47715,7 +47716,7 @@
       <c r="AN983" s="1"/>
       <c r="AO983" s="1"/>
     </row>
-    <row r="984" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A984" s="1"/>
       <c r="B984" s="1"/>
       <c r="C984" s="1"/>
@@ -47758,65 +47759,86 @@
       <c r="AN984" s="1"/>
       <c r="AO984" s="1"/>
     </row>
-    <row r="985" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A985" s="1"/>
     </row>
-    <row r="986" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A986" s="1"/>
     </row>
-    <row r="987" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="987" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A987" s="1"/>
     </row>
-    <row r="988" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A988" s="1"/>
     </row>
-    <row r="989" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="989" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A989" s="1"/>
     </row>
-    <row r="990" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A990" s="1"/>
     </row>
-    <row r="991" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="991" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A991" s="1"/>
     </row>
-    <row r="992" spans="1:41" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="992" spans="1:41" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A992" s="1"/>
     </row>
-    <row r="993" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A993" s="1"/>
     </row>
-    <row r="994" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A994" s="1"/>
     </row>
-    <row r="995" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A995" s="1"/>
     </row>
-    <row r="996" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="996" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A996" s="1"/>
     </row>
-    <row r="997" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="997" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A997" s="1"/>
     </row>
-    <row r="998" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="998" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A998" s="1"/>
     </row>
-    <row r="999" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="999" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A999" s="1"/>
     </row>
-    <row r="1000" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1000" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1000" s="1"/>
     </row>
-    <row r="1001" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1001" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1001" s="1"/>
     </row>
-    <row r="1002" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1002" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1002" s="1"/>
     </row>
-    <row r="1003" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1003" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1003" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="G6:M6"/>
+    <mergeCell ref="N6:T6"/>
+    <mergeCell ref="D1:J1"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="K3:R3"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="K4:R4"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="AP6:AV6"/>
+    <mergeCell ref="AW6:BC6"/>
+    <mergeCell ref="BD6:BJ6"/>
+    <mergeCell ref="BK6:BQ6"/>
+    <mergeCell ref="U6:AA6"/>
+    <mergeCell ref="AB6:AH6"/>
+    <mergeCell ref="AI6:AO6"/>
     <mergeCell ref="DA6:DG6"/>
     <mergeCell ref="DH6:DN6"/>
     <mergeCell ref="DO6:DU6"/>
@@ -47826,27 +47848,6 @@
     <mergeCell ref="CF6:CL6"/>
     <mergeCell ref="CM6:CS6"/>
     <mergeCell ref="CT6:CZ6"/>
-    <mergeCell ref="AP6:AV6"/>
-    <mergeCell ref="AW6:BC6"/>
-    <mergeCell ref="BD6:BJ6"/>
-    <mergeCell ref="BK6:BQ6"/>
-    <mergeCell ref="U6:AA6"/>
-    <mergeCell ref="AB6:AH6"/>
-    <mergeCell ref="AI6:AO6"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:M6"/>
-    <mergeCell ref="N6:T6"/>
-    <mergeCell ref="D1:J1"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="K3:R3"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="K4:R4"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
